--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhmgo\Desktop\野球15\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EB4CA26-C3EE-4684-A84B-A99790C4B5AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6EF4C4A-EDCF-4BC9-AEAB-9ACBA2A46CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1900" yWindow="1900" windowWidth="28800" windowHeight="15370" xr2:uid="{B57D1550-4E85-435D-BD6F-1B13E635EA51}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="94">
   <si>
     <t>野手・打者</t>
   </si>
@@ -249,10 +249,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>タイラ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>フジナミ</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -355,6 +351,30 @@
   </si>
   <si>
     <t>トーケルソン</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>フィリップス</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ヤマオカ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ゴールドシュミット</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アクーニャJr.</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Y.ディアス</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>E.ディアス</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -737,7 +757,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C402B4-0E60-4338-B3CD-2DB7A1A076E1}">
-  <dimension ref="B2:AA72"/>
+  <dimension ref="B2:AA76"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="14.75" customWidth="1"/>
@@ -791,26 +811,26 @@
         <v>9</v>
       </c>
       <c r="E5" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F5" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G5" s="3">
         <v>4</v>
       </c>
       <c r="H5" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I5" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J5" s="3">
         <v>9</v>
       </c>
       <c r="K5">
         <f>SUM(D5:I5)</f>
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.55000000000000004">
@@ -902,14 +922,14 @@
         <v>2</v>
       </c>
       <c r="I8" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J8" s="3">
         <v>6</v>
       </c>
       <c r="K8">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.55000000000000004">
@@ -926,7 +946,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G9" s="3">
         <v>1</v>
@@ -942,7 +962,7 @@
       </c>
       <c r="K9">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.55000000000000004">
@@ -1439,7 +1459,7 @@
         <v>5</v>
       </c>
       <c r="K24">
-        <f t="shared" ref="K24:K31" si="1">SUM(D24:I24)</f>
+        <f t="shared" ref="K24:K30" si="1">SUM(D24:I24)</f>
         <v>26</v>
       </c>
     </row>
@@ -1476,9 +1496,9 @@
         <v>39</v>
       </c>
     </row>
-    <row r="26" spans="2:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="2:27" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B26" s="3" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>44</v>
@@ -1487,31 +1507,31 @@
         <v>7</v>
       </c>
       <c r="E26" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F26" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G26" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H26" s="3">
         <v>2</v>
       </c>
       <c r="I26" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J26" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K26">
-        <f>SUM(D26:I26)</f>
-        <v>23</v>
+        <f>SUM(D26:J26)</f>
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="2:27" x14ac:dyDescent="0.55000000000000004">
       <c r="B27" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>52</v>
@@ -1544,7 +1564,7 @@
     </row>
     <row r="28" spans="2:27" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>52</v>
@@ -1577,7 +1597,7 @@
     </row>
     <row r="29" spans="2:27" x14ac:dyDescent="0.55000000000000004">
       <c r="B29" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>44</v>
@@ -1610,7 +1630,7 @@
     </row>
     <row r="30" spans="2:27" x14ac:dyDescent="0.55000000000000004">
       <c r="B30" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>52</v>
@@ -1643,7 +1663,7 @@
     </row>
     <row r="31" spans="2:27" x14ac:dyDescent="0.55000000000000004">
       <c r="B31" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>52</v>
@@ -1676,7 +1696,7 @@
     </row>
     <row r="32" spans="2:27" x14ac:dyDescent="0.55000000000000004">
       <c r="B32" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>52</v>
@@ -1703,13 +1723,13 @@
         <v>4</v>
       </c>
       <c r="K32">
-        <f t="shared" ref="K32:K35" si="2">SUM(D32:I32)</f>
+        <f t="shared" ref="K32:K34" si="2">SUM(D32:I32)</f>
         <v>23</v>
       </c>
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B33" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>52</v>
@@ -1742,7 +1762,7 @@
     </row>
     <row r="34" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B34" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>52</v>
@@ -1775,7 +1795,7 @@
     </row>
     <row r="35" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B35" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>44</v>
@@ -1807,550 +1827,528 @@
       </c>
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D36" s="3">
+        <v>6</v>
+      </c>
+      <c r="E36" s="3">
+        <v>6</v>
+      </c>
+      <c r="F36" s="3">
+        <v>10</v>
+      </c>
+      <c r="G36" s="3">
+        <v>2</v>
+      </c>
+      <c r="H36" s="3">
+        <v>3</v>
+      </c>
+      <c r="I36" s="3">
+        <v>8</v>
+      </c>
+      <c r="J36" s="3">
+        <v>7</v>
+      </c>
+      <c r="K36">
+        <f>SUM(D36:J36)</f>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B37" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D37" s="3">
+        <v>5</v>
+      </c>
+      <c r="E37" s="3">
+        <v>9</v>
+      </c>
+      <c r="F37" s="3">
+        <v>4</v>
+      </c>
+      <c r="G37" s="3">
+        <v>1</v>
+      </c>
+      <c r="H37" s="3">
+        <v>2</v>
+      </c>
+      <c r="I37" s="3">
+        <v>3</v>
+      </c>
+      <c r="J37" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B38" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J36" s="3"/>
-    </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B38" s="2" t="s">
+      <c r="J38" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B40" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C40" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="D40" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="E40" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F38" s="2" t="s">
+      <c r="F40" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G38" s="2" t="s">
+      <c r="G40" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H38" s="2" t="s">
+      <c r="H40" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I38" s="2" t="s">
+      <c r="I40" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="J38" s="2" t="s">
+      <c r="J40" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="L38" s="2" t="s">
+      <c r="K40" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L40" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N38" s="2" t="s">
+      <c r="M40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N40" s="2" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B39" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D39" s="3">
-        <v>165</v>
-      </c>
-      <c r="E39" s="3">
-        <v>9</v>
-      </c>
-      <c r="F39" s="3">
-        <v>4</v>
-      </c>
-      <c r="G39" s="3">
-        <v>8</v>
-      </c>
-      <c r="H39" s="3">
-        <v>7</v>
-      </c>
-      <c r="I39" s="3">
-        <v>5</v>
-      </c>
-      <c r="J39" s="3">
-        <v>8</v>
-      </c>
-      <c r="K39" s="3">
-        <v>6</v>
-      </c>
-      <c r="L39" s="3">
-        <v>7</v>
-      </c>
-      <c r="M39" s="3">
-        <v>8</v>
-      </c>
-      <c r="N39">
-        <f>SUM(E39:L39)</f>
-        <v>54</v>
-      </c>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B40" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D40" s="3">
-        <v>157</v>
-      </c>
-      <c r="E40" s="3">
-        <v>8</v>
-      </c>
-      <c r="F40" s="3">
-        <v>3</v>
-      </c>
-      <c r="G40" s="3">
-        <v>7</v>
-      </c>
-      <c r="H40" s="3">
-        <v>7</v>
-      </c>
-      <c r="I40" s="3">
-        <v>8</v>
-      </c>
-      <c r="J40" s="3">
-        <v>7</v>
-      </c>
-      <c r="K40" s="3">
-        <v>6</v>
-      </c>
-      <c r="L40" s="3">
-        <v>7</v>
-      </c>
-      <c r="M40" s="3">
-        <v>8</v>
-      </c>
-      <c r="N40">
-        <f t="shared" ref="N40:N61" si="3">SUM(E40:L40)</f>
-        <v>53</v>
       </c>
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B41" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D41" s="3">
+        <v>165</v>
+      </c>
+      <c r="E41" s="3">
+        <v>9</v>
+      </c>
+      <c r="F41" s="3">
+        <v>5</v>
+      </c>
+      <c r="G41" s="3">
+        <v>9</v>
+      </c>
+      <c r="H41" s="3">
+        <v>8</v>
+      </c>
+      <c r="I41" s="3">
+        <v>6</v>
+      </c>
+      <c r="J41" s="3">
+        <v>9</v>
+      </c>
+      <c r="K41" s="3">
+        <v>7</v>
+      </c>
+      <c r="L41" s="3">
+        <v>8</v>
+      </c>
+      <c r="M41" s="3">
+        <v>9</v>
+      </c>
+      <c r="N41">
+        <f>SUM(E41:L41)</f>
+        <v>61</v>
+      </c>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B42" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D42" s="3">
+        <v>157</v>
+      </c>
+      <c r="E42" s="3">
+        <v>8</v>
+      </c>
+      <c r="F42" s="3">
+        <v>3</v>
+      </c>
+      <c r="G42" s="3">
+        <v>7</v>
+      </c>
+      <c r="H42" s="3">
+        <v>7</v>
+      </c>
+      <c r="I42" s="3">
+        <v>8</v>
+      </c>
+      <c r="J42" s="3">
+        <v>7</v>
+      </c>
+      <c r="K42" s="3">
+        <v>6</v>
+      </c>
+      <c r="L42" s="3">
+        <v>7</v>
+      </c>
+      <c r="M42" s="3">
+        <v>8</v>
+      </c>
+      <c r="N42">
+        <f t="shared" ref="N42:N63" si="3">SUM(E42:L42)</f>
+        <v>53</v>
+      </c>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B43" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D43" s="3">
         <v>155</v>
       </c>
-      <c r="E41" s="3">
-        <v>5</v>
-      </c>
-      <c r="F41" s="3">
-        <v>2</v>
-      </c>
-      <c r="G41" s="3">
+      <c r="E43" s="3">
+        <v>5</v>
+      </c>
+      <c r="F43" s="3">
+        <v>2</v>
+      </c>
+      <c r="G43" s="3">
         <v>10</v>
       </c>
-      <c r="H41" s="3">
-        <v>6</v>
-      </c>
-      <c r="I41" s="3">
-        <v>6</v>
-      </c>
-      <c r="J41" s="3">
-        <v>6</v>
-      </c>
-      <c r="K41" s="3">
-        <v>5</v>
-      </c>
-      <c r="L41" s="3">
-        <v>7</v>
-      </c>
-      <c r="M41" s="3">
-        <v>6</v>
-      </c>
-      <c r="N41">
+      <c r="H43" s="3">
+        <v>6</v>
+      </c>
+      <c r="I43" s="3">
+        <v>6</v>
+      </c>
+      <c r="J43" s="3">
+        <v>6</v>
+      </c>
+      <c r="K43" s="3">
+        <v>5</v>
+      </c>
+      <c r="L43" s="3">
+        <v>7</v>
+      </c>
+      <c r="M43" s="3">
+        <v>6</v>
+      </c>
+      <c r="N43">
         <f t="shared" si="3"/>
         <v>47</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B42" s="3" t="s">
+    <row r="44" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B44" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C44" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D42" s="3">
+      <c r="D44" s="3">
         <v>148</v>
       </c>
-      <c r="E42" s="3">
-        <v>4</v>
-      </c>
-      <c r="F42" s="3">
+      <c r="E44" s="3">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3">
         <v>10</v>
       </c>
-      <c r="G42" s="3">
-        <v>6</v>
-      </c>
-      <c r="H42" s="3">
-        <v>4</v>
-      </c>
-      <c r="I42" s="3">
-        <v>8</v>
-      </c>
-      <c r="J42" s="3">
-        <v>5</v>
-      </c>
-      <c r="K42" s="3">
-        <v>4</v>
-      </c>
-      <c r="L42" s="3">
-        <v>5</v>
-      </c>
-      <c r="M42" s="3">
-        <v>6</v>
-      </c>
-      <c r="N42">
+      <c r="G44" s="3">
+        <v>6</v>
+      </c>
+      <c r="H44" s="3">
+        <v>4</v>
+      </c>
+      <c r="I44" s="3">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3">
+        <v>5</v>
+      </c>
+      <c r="K44" s="3">
+        <v>4</v>
+      </c>
+      <c r="L44" s="3">
+        <v>5</v>
+      </c>
+      <c r="M44" s="3">
+        <v>6</v>
+      </c>
+      <c r="N44">
         <f t="shared" si="3"/>
         <v>46</v>
       </c>
     </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B43" s="3" t="s">
+    <row r="45" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B45" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C45" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D45" s="3">
         <v>220</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E45" s="3">
         <v>1</v>
       </c>
-      <c r="F43" s="3">
+      <c r="F45" s="3">
         <v>1</v>
       </c>
-      <c r="G43" s="3">
-        <v>9</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="G45" s="3">
+        <v>9</v>
+      </c>
+      <c r="H45" s="3">
         <v>1</v>
       </c>
-      <c r="I43" s="3">
-        <v>3</v>
-      </c>
-      <c r="J43" s="3">
-        <v>6</v>
-      </c>
-      <c r="K43" s="3">
-        <v>4</v>
-      </c>
-      <c r="L43" s="3">
-        <v>6</v>
-      </c>
-      <c r="M43" s="3">
-        <v>5</v>
-      </c>
-      <c r="N43">
+      <c r="I45" s="3">
+        <v>3</v>
+      </c>
+      <c r="J45" s="3">
+        <v>6</v>
+      </c>
+      <c r="K45" s="3">
+        <v>4</v>
+      </c>
+      <c r="L45" s="3">
+        <v>6</v>
+      </c>
+      <c r="M45" s="3">
+        <v>5</v>
+      </c>
+      <c r="N45">
         <f t="shared" si="3"/>
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B44" s="3" t="s">
+    <row r="46" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B46" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C46" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D46" s="3">
         <v>100</v>
       </c>
-      <c r="E44" s="3">
-        <v>9</v>
-      </c>
-      <c r="F44" s="3">
-        <v>9</v>
-      </c>
-      <c r="G44" s="3">
-        <v>9</v>
-      </c>
-      <c r="H44" s="3">
-        <v>9</v>
-      </c>
-      <c r="I44" s="3">
-        <v>9</v>
-      </c>
-      <c r="J44" s="3">
-        <v>6</v>
-      </c>
-      <c r="K44" s="3">
-        <v>8</v>
-      </c>
-      <c r="L44" s="3">
-        <v>4</v>
-      </c>
-      <c r="M44" s="3">
-        <v>5</v>
-      </c>
-      <c r="N44">
+      <c r="E46" s="3">
+        <v>9</v>
+      </c>
+      <c r="F46" s="3">
+        <v>9</v>
+      </c>
+      <c r="G46" s="3">
+        <v>9</v>
+      </c>
+      <c r="H46" s="3">
+        <v>9</v>
+      </c>
+      <c r="I46" s="3">
+        <v>9</v>
+      </c>
+      <c r="J46" s="3">
+        <v>6</v>
+      </c>
+      <c r="K46" s="3">
+        <v>8</v>
+      </c>
+      <c r="L46" s="3">
+        <v>4</v>
+      </c>
+      <c r="M46" s="3">
+        <v>5</v>
+      </c>
+      <c r="N46">
         <f t="shared" si="3"/>
         <v>63</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B45" s="3" t="s">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B47" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D47" s="3">
         <v>149</v>
       </c>
-      <c r="E45" s="3">
-        <v>3</v>
-      </c>
-      <c r="F45" s="3">
-        <v>6</v>
-      </c>
-      <c r="G45" s="3">
-        <v>5</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="E47" s="3">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3">
+        <v>6</v>
+      </c>
+      <c r="G47" s="3">
+        <v>5</v>
+      </c>
+      <c r="H47" s="3">
         <v>10</v>
       </c>
-      <c r="I45" s="3">
-        <v>5</v>
-      </c>
-      <c r="J45" s="3">
-        <v>8</v>
-      </c>
-      <c r="K45" s="3">
-        <v>5</v>
-      </c>
-      <c r="L45" s="3">
-        <v>6</v>
-      </c>
-      <c r="M45" s="3">
-        <v>6</v>
-      </c>
-      <c r="N45">
+      <c r="I47" s="3">
+        <v>5</v>
+      </c>
+      <c r="J47" s="3">
+        <v>8</v>
+      </c>
+      <c r="K47" s="3">
+        <v>5</v>
+      </c>
+      <c r="L47" s="3">
+        <v>6</v>
+      </c>
+      <c r="M47" s="3">
+        <v>6</v>
+      </c>
+      <c r="N47">
         <f t="shared" si="3"/>
         <v>48</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B46" s="3" t="s">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B48" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C48" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D48" s="3">
         <v>158</v>
       </c>
-      <c r="E46" s="3">
-        <v>7</v>
-      </c>
-      <c r="F46" s="3">
-        <v>6</v>
-      </c>
-      <c r="G46" s="3">
-        <v>6</v>
-      </c>
-      <c r="H46" s="3">
-        <v>5</v>
-      </c>
-      <c r="I46" s="3">
-        <v>7</v>
-      </c>
-      <c r="J46" s="3">
-        <v>4</v>
-      </c>
-      <c r="K46" s="3">
-        <v>5</v>
-      </c>
-      <c r="L46" s="3">
-        <v>5</v>
-      </c>
-      <c r="M46" s="3">
-        <v>7</v>
-      </c>
-      <c r="N46">
+      <c r="E48" s="3">
+        <v>7</v>
+      </c>
+      <c r="F48" s="3">
+        <v>6</v>
+      </c>
+      <c r="G48" s="3">
+        <v>6</v>
+      </c>
+      <c r="H48" s="3">
+        <v>5</v>
+      </c>
+      <c r="I48" s="3">
+        <v>7</v>
+      </c>
+      <c r="J48" s="3">
+        <v>4</v>
+      </c>
+      <c r="K48" s="3">
+        <v>5</v>
+      </c>
+      <c r="L48" s="3">
+        <v>5</v>
+      </c>
+      <c r="M48" s="3">
+        <v>7</v>
+      </c>
+      <c r="N48">
         <f t="shared" si="3"/>
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B47" s="3" t="s">
+    <row r="49" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B49" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C49" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D49" s="3">
         <v>172</v>
       </c>
-      <c r="E47" s="3">
-        <v>9</v>
-      </c>
-      <c r="F47" s="3">
-        <v>8</v>
-      </c>
-      <c r="G47" s="3">
-        <v>6</v>
-      </c>
-      <c r="H47" s="3">
-        <v>9</v>
-      </c>
-      <c r="I47" s="3">
-        <v>7</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="E49" s="3">
+        <v>9</v>
+      </c>
+      <c r="F49" s="3">
+        <v>8</v>
+      </c>
+      <c r="G49" s="3">
+        <v>6</v>
+      </c>
+      <c r="H49" s="3">
+        <v>9</v>
+      </c>
+      <c r="I49" s="3">
+        <v>7</v>
+      </c>
+      <c r="J49" s="3">
         <v>11</v>
       </c>
-      <c r="K47" s="3">
-        <v>8</v>
-      </c>
-      <c r="L47" s="3">
+      <c r="K49" s="3">
+        <v>8</v>
+      </c>
+      <c r="L49" s="3">
         <v>12</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M49" s="3">
         <v>15</v>
       </c>
-      <c r="N47">
+      <c r="N49">
         <f t="shared" si="3"/>
         <v>70</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B48" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D48" s="3">
-        <v>171</v>
-      </c>
-      <c r="E48" s="3">
-        <v>8</v>
-      </c>
-      <c r="F48" s="3">
-        <v>6</v>
-      </c>
-      <c r="G48" s="3">
-        <v>8</v>
-      </c>
-      <c r="H48" s="3">
-        <v>3</v>
-      </c>
-      <c r="I48" s="3">
-        <v>6</v>
-      </c>
-      <c r="J48" s="3">
-        <v>8</v>
-      </c>
-      <c r="K48" s="3">
-        <v>6</v>
-      </c>
-      <c r="L48" s="3">
-        <v>2</v>
-      </c>
-      <c r="M48" s="3">
-        <v>4</v>
-      </c>
-      <c r="N48">
-        <f t="shared" si="3"/>
-        <v>47</v>
-      </c>
-    </row>
-    <row r="49" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B49" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D49" s="3">
-        <v>143</v>
-      </c>
-      <c r="E49" s="3">
-        <v>4</v>
-      </c>
-      <c r="F49" s="3">
-        <v>4</v>
-      </c>
-      <c r="G49" s="3">
-        <v>5</v>
-      </c>
-      <c r="H49" s="3">
-        <v>5</v>
-      </c>
-      <c r="I49" s="3">
-        <v>10</v>
-      </c>
-      <c r="J49" s="3">
-        <v>7</v>
-      </c>
-      <c r="K49" s="3">
-        <v>8</v>
-      </c>
-      <c r="L49" s="3">
-        <v>6</v>
-      </c>
-      <c r="M49" s="3">
-        <v>6</v>
-      </c>
-      <c r="N49">
-        <f t="shared" si="3"/>
-        <v>49</v>
-      </c>
-    </row>
     <row r="50" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B50" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="D50" s="3">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E50" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F50" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G50" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H50" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I50" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J50" s="3">
         <v>8</v>
       </c>
       <c r="K50" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L50" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M50" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N50">
         <f t="shared" si="3"/>
@@ -2359,160 +2357,160 @@
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B51" s="3" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="D51" s="3">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="E51" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F51" s="3">
+        <v>4</v>
+      </c>
+      <c r="G51" s="3">
+        <v>5</v>
+      </c>
+      <c r="H51" s="3">
+        <v>5</v>
+      </c>
+      <c r="I51" s="3">
         <v>10</v>
       </c>
-      <c r="G51" s="3">
-        <v>2</v>
-      </c>
-      <c r="H51" s="3">
-        <v>2</v>
-      </c>
-      <c r="I51" s="3">
-        <v>5</v>
-      </c>
       <c r="J51" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K51" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L51" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M51" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N51">
         <f t="shared" si="3"/>
-        <v>30</v>
+        <v>49</v>
       </c>
     </row>
     <row r="52" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B52" s="3" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D52" s="3">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="E52" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F52" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G52" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H52" s="3">
         <v>7</v>
       </c>
       <c r="I52" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J52" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K52" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L52" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M52" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N52">
         <f t="shared" si="3"/>
-        <v>36</v>
+        <v>47</v>
       </c>
     </row>
     <row r="53" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B53" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D53" s="3">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="E53" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F53" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G53" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H53" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I53" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J53" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K53" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L53" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M53" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N53">
         <f t="shared" si="3"/>
-        <v>37</v>
+        <v>30</v>
       </c>
     </row>
     <row r="54" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B54" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D54" s="3">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="E54" s="3">
         <v>2</v>
       </c>
       <c r="F54" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G54" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H54" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I54" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J54" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K54" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L54" s="3">
         <v>2</v>
@@ -2522,66 +2520,66 @@
       </c>
       <c r="N54">
         <f t="shared" si="3"/>
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="55" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B55" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D55" s="3">
-        <v>125</v>
+        <v>165</v>
       </c>
       <c r="E55" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F55" s="3">
         <v>2</v>
       </c>
       <c r="G55" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H55" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I55" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J55" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K55" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L55" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M55" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N55">
         <f t="shared" si="3"/>
-        <v>19</v>
+        <v>37</v>
       </c>
     </row>
     <row r="56" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B56" s="3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D56" s="3">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="E56" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F56" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G56" s="3">
         <v>5</v>
@@ -2590,196 +2588,196 @@
         <v>5</v>
       </c>
       <c r="I56" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J56" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K56" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L56" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M56" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N56">
         <f t="shared" si="3"/>
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="57" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B57" s="3" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D57" s="3">
-        <v>164</v>
+        <v>125</v>
       </c>
       <c r="E57" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F57" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G57" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H57" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I57" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J57" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K57" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L57" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M57" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="N57">
         <f t="shared" si="3"/>
-        <v>45</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B58" s="3" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D58" s="3">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E58" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F58" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G58" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H58" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I58" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J58" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K58" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L58" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M58" s="3">
         <v>5</v>
       </c>
       <c r="N58">
         <f t="shared" si="3"/>
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="59" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B59" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="E59" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F59" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G59" s="3">
         <v>8</v>
       </c>
       <c r="H59" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I59" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J59" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K59" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L59" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M59" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N59">
         <f t="shared" si="3"/>
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="60" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B60" s="3" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="E60" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F60" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G60" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H60" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I60" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J60" s="3">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="K60" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L60" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M60" s="3">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="N60">
         <f t="shared" si="3"/>
-        <v>78</v>
+        <v>30</v>
       </c>
     </row>
     <row r="61" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B61" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>44</v>
@@ -2788,265 +2786,449 @@
         <v>155</v>
       </c>
       <c r="E61" s="3">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="F61" s="3">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G61" s="3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H61" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I61" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J61" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K61" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L61" s="3">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="M61" s="3">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="N61">
         <f t="shared" si="3"/>
-        <v>86</v>
+        <v>46</v>
       </c>
     </row>
     <row r="62" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B62" s="3"/>
-      <c r="C62" s="3"/>
-      <c r="D62" s="3"/>
-      <c r="E62" s="3"/>
-      <c r="F62" s="3"/>
-      <c r="G62" s="3"/>
-      <c r="H62" s="3"/>
-      <c r="I62" s="3"/>
-      <c r="J62" s="3"/>
-      <c r="K62" s="3"/>
-      <c r="L62" s="3"/>
-      <c r="M62" s="3"/>
+      <c r="B62" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D62" s="3">
+        <v>175</v>
+      </c>
+      <c r="E62" s="3">
+        <v>10</v>
+      </c>
+      <c r="F62" s="3">
+        <v>9</v>
+      </c>
+      <c r="G62" s="3">
+        <v>9</v>
+      </c>
+      <c r="H62" s="3">
+        <v>10</v>
+      </c>
+      <c r="I62" s="3">
+        <v>9</v>
+      </c>
+      <c r="J62" s="3">
+        <v>11</v>
+      </c>
+      <c r="K62" s="3">
+        <v>8</v>
+      </c>
+      <c r="L62" s="3">
+        <v>12</v>
+      </c>
+      <c r="M62" s="3">
+        <v>18</v>
+      </c>
+      <c r="N62">
+        <f t="shared" si="3"/>
+        <v>78</v>
+      </c>
     </row>
     <row r="63" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B63" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D63" s="3">
+        <v>155</v>
+      </c>
+      <c r="E63" s="3">
+        <v>14</v>
+      </c>
+      <c r="F63" s="3">
+        <v>12</v>
+      </c>
+      <c r="G63" s="3">
+        <v>11</v>
+      </c>
+      <c r="H63" s="3">
+        <v>10</v>
+      </c>
+      <c r="I63" s="3">
+        <v>11</v>
+      </c>
+      <c r="J63" s="3">
+        <v>10</v>
+      </c>
+      <c r="K63" s="3">
+        <v>7</v>
+      </c>
+      <c r="L63" s="3">
+        <v>11</v>
+      </c>
+      <c r="M63" s="3">
+        <v>17</v>
+      </c>
+      <c r="N63">
+        <f t="shared" si="3"/>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="64" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B64" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D64" s="3">
+        <v>158</v>
+      </c>
+      <c r="E64" s="3">
+        <v>9</v>
+      </c>
+      <c r="F64" s="3">
+        <v>3</v>
+      </c>
+      <c r="G64" s="3">
+        <v>3</v>
+      </c>
+      <c r="H64" s="3">
+        <v>3</v>
+      </c>
+      <c r="I64" s="3">
+        <v>4</v>
+      </c>
+      <c r="J64" s="3">
+        <v>6</v>
+      </c>
+      <c r="K64" s="3">
+        <v>5</v>
+      </c>
+      <c r="L64" s="3">
+        <v>2</v>
+      </c>
+      <c r="M64" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="B65" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D65" s="3">
+        <v>152</v>
+      </c>
+      <c r="E65" s="3">
+        <v>9</v>
+      </c>
+      <c r="F65" s="3">
+        <v>3</v>
+      </c>
+      <c r="G65" s="3">
+        <v>7</v>
+      </c>
+      <c r="H65" s="3">
+        <v>3</v>
+      </c>
+      <c r="I65" s="3">
+        <v>5</v>
+      </c>
+      <c r="J65" s="3">
+        <v>7</v>
+      </c>
+      <c r="K65" s="3">
+        <v>6</v>
+      </c>
+      <c r="L65" s="3">
+        <v>7</v>
+      </c>
+      <c r="M65" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="B66" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D66" s="3">
+        <v>163</v>
+      </c>
+      <c r="E66" s="3">
+        <v>8</v>
+      </c>
+      <c r="F66" s="3">
+        <v>1</v>
+      </c>
+      <c r="G66" s="3">
+        <v>4</v>
+      </c>
+      <c r="H66" s="3">
+        <v>9</v>
+      </c>
+      <c r="I66" s="3">
+        <v>5</v>
+      </c>
+      <c r="J66" s="3">
+        <v>10</v>
+      </c>
+      <c r="K66" s="3">
+        <v>5</v>
+      </c>
+      <c r="L66" s="3">
+        <v>2</v>
+      </c>
+      <c r="M66" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="B67" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="B68" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="B69" t="s">
+        <v>70</v>
+      </c>
+      <c r="C69" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="64" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B64" s="2" t="s">
+      <c r="D69">
+        <v>8</v>
+      </c>
+      <c r="E69">
+        <v>2</v>
+      </c>
+      <c r="F69">
+        <v>3</v>
+      </c>
+      <c r="I69">
+        <v>7</v>
+      </c>
+      <c r="J69">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="B70" t="s">
+        <v>67</v>
+      </c>
+      <c r="C70" t="s">
+        <v>66</v>
+      </c>
+      <c r="D70">
+        <v>4</v>
+      </c>
+      <c r="E70">
+        <v>6</v>
+      </c>
+      <c r="F70">
+        <v>4</v>
+      </c>
+      <c r="I70">
+        <v>5</v>
+      </c>
+      <c r="J70">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="B71" t="s">
+        <v>68</v>
+      </c>
+      <c r="C71" t="s">
+        <v>66</v>
+      </c>
+      <c r="D71">
+        <v>10</v>
+      </c>
+      <c r="E71">
+        <v>10</v>
+      </c>
+      <c r="F71">
+        <v>5</v>
+      </c>
+      <c r="I71">
+        <v>10</v>
+      </c>
+      <c r="J71">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="B72" t="s">
+        <v>69</v>
+      </c>
+      <c r="C72" t="s">
+        <v>66</v>
+      </c>
+      <c r="D72">
+        <v>2</v>
+      </c>
+      <c r="E72">
+        <v>3</v>
+      </c>
+      <c r="F72">
+        <v>4</v>
+      </c>
+      <c r="I72">
+        <v>9</v>
+      </c>
+      <c r="J72">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="B73" t="s">
+        <v>58</v>
+      </c>
+      <c r="C73" t="s">
+        <v>66</v>
+      </c>
+      <c r="D73">
+        <v>7</v>
+      </c>
+      <c r="E73">
+        <v>3</v>
+      </c>
+      <c r="F73">
+        <v>3</v>
+      </c>
+      <c r="I73">
+        <v>7</v>
+      </c>
+      <c r="J73">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="B74" t="s">
+        <v>61</v>
+      </c>
+      <c r="C74" t="s">
+        <v>66</v>
+      </c>
+      <c r="D74">
+        <v>6</v>
+      </c>
+      <c r="E74">
         <v>1</v>
       </c>
-      <c r="C64" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G64" s="2"/>
-      <c r="H64" s="2"/>
-      <c r="I64" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J64" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K64" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="B65" t="s">
-        <v>71</v>
-      </c>
-      <c r="C65" t="s">
-        <v>67</v>
-      </c>
-      <c r="D65">
-        <v>8</v>
-      </c>
-      <c r="E65">
-        <v>2</v>
-      </c>
-      <c r="F65">
-        <v>3</v>
-      </c>
-      <c r="I65">
-        <v>7</v>
-      </c>
-      <c r="J65">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="B66" t="s">
-        <v>68</v>
-      </c>
-      <c r="C66" t="s">
-        <v>67</v>
-      </c>
-      <c r="D66">
-        <v>4</v>
-      </c>
-      <c r="E66">
-        <v>6</v>
-      </c>
-      <c r="F66">
-        <v>4</v>
-      </c>
-      <c r="I66">
-        <v>5</v>
-      </c>
-      <c r="J66">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="B67" t="s">
-        <v>69</v>
-      </c>
-      <c r="C67" t="s">
-        <v>67</v>
-      </c>
-      <c r="D67">
-        <v>10</v>
-      </c>
-      <c r="E67">
-        <v>10</v>
-      </c>
-      <c r="F67">
-        <v>5</v>
-      </c>
-      <c r="I67">
-        <v>10</v>
-      </c>
-      <c r="J67">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="B68" t="s">
-        <v>70</v>
-      </c>
-      <c r="C68" t="s">
-        <v>67</v>
-      </c>
-      <c r="D68">
-        <v>2</v>
-      </c>
-      <c r="E68">
-        <v>3</v>
-      </c>
-      <c r="F68">
-        <v>4</v>
-      </c>
-      <c r="I68">
-        <v>9</v>
-      </c>
-      <c r="J68">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="B69" t="s">
-        <v>58</v>
-      </c>
-      <c r="C69" t="s">
-        <v>67</v>
-      </c>
-      <c r="D69">
-        <v>7</v>
-      </c>
-      <c r="E69">
-        <v>3</v>
-      </c>
-      <c r="F69">
-        <v>3</v>
-      </c>
-      <c r="I69">
-        <v>7</v>
-      </c>
-      <c r="J69">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="B70" t="s">
-        <v>61</v>
-      </c>
-      <c r="C70" t="s">
-        <v>67</v>
-      </c>
-      <c r="D70">
-        <v>6</v>
-      </c>
-      <c r="E70">
-        <v>1</v>
-      </c>
-      <c r="F70">
-        <v>3</v>
-      </c>
-      <c r="I70">
-        <v>6</v>
-      </c>
-      <c r="J70">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="B71" t="s">
-        <v>78</v>
-      </c>
-      <c r="C71" t="s">
-        <v>67</v>
-      </c>
-      <c r="D71">
-        <v>9</v>
-      </c>
-      <c r="E71">
-        <v>9</v>
-      </c>
-      <c r="F71">
-        <v>5</v>
-      </c>
-      <c r="I71">
+      <c r="F74">
+        <v>3</v>
+      </c>
+      <c r="I74">
+        <v>6</v>
+      </c>
+      <c r="J74">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="B75" t="s">
+        <v>77</v>
+      </c>
+      <c r="C75" t="s">
+        <v>66</v>
+      </c>
+      <c r="D75">
+        <v>9</v>
+      </c>
+      <c r="E75">
+        <v>9</v>
+      </c>
+      <c r="F75">
+        <v>5</v>
+      </c>
+      <c r="I75">
         <v>13</v>
       </c>
-      <c r="J71">
+      <c r="J75">
         <v>16</v>
       </c>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="B72" t="s">
+    <row r="76" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="B76" t="s">
+        <v>83</v>
+      </c>
+      <c r="C76" t="s">
         <v>84</v>
       </c>
-      <c r="C72" t="s">
-        <v>85</v>
-      </c>
-      <c r="D72">
-        <v>6</v>
-      </c>
-      <c r="E72">
-        <v>3</v>
-      </c>
-      <c r="F72">
-        <v>3</v>
-      </c>
-      <c r="I72">
-        <v>4</v>
-      </c>
-      <c r="J72">
+      <c r="D76">
+        <v>6</v>
+      </c>
+      <c r="E76">
+        <v>3</v>
+      </c>
+      <c r="F76">
+        <v>3</v>
+      </c>
+      <c r="I76">
+        <v>4</v>
+      </c>
+      <c r="J76">
         <v>4</v>
       </c>
     </row>

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhmgo\Desktop\野球15\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6EF4C4A-EDCF-4BC9-AEAB-9ACBA2A46CB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BD29759-6550-4206-9533-252FF7092632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1900" yWindow="1900" windowWidth="28800" windowHeight="15370" xr2:uid="{B57D1550-4E85-435D-BD6F-1B13E635EA51}"/>
   </bookViews>
@@ -2912,7 +2912,7 @@
         <v>158</v>
       </c>
       <c r="E64" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F64" s="3">
         <v>3</v>
@@ -2947,10 +2947,10 @@
         <v>44</v>
       </c>
       <c r="D65" s="3">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E65" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F65" s="3">
         <v>3</v>
@@ -2959,13 +2959,13 @@
         <v>7</v>
       </c>
       <c r="H65" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I65" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J65" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K65" s="3">
         <v>6</v>
@@ -3000,7 +3000,7 @@
         <v>9</v>
       </c>
       <c r="I66" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J66" s="3">
         <v>10</v>

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhmgo\Desktop\野球15\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BD29759-6550-4206-9533-252FF7092632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0731764-3F3F-4789-A89B-39F1CD4D11C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="28800" windowHeight="15370" xr2:uid="{B57D1550-4E85-435D-BD6F-1B13E635EA51}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B57D1550-4E85-435D-BD6F-1B13E635EA51}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="97">
   <si>
     <t>野手・打者</t>
   </si>
@@ -375,6 +375,18 @@
   </si>
   <si>
     <t>E.ディアス</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ジャンセン</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ロハス</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>サマーズ</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -757,7 +769,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C402B4-0E60-4338-B3CD-2DB7A1A076E1}">
-  <dimension ref="B2:AA76"/>
+  <dimension ref="B2:AA79"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="14.75" customWidth="1"/>
@@ -889,14 +901,14 @@
         <v>4</v>
       </c>
       <c r="I7" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J7" s="3">
         <v>5</v>
       </c>
       <c r="K7">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.55000000000000004">
@@ -1420,14 +1432,14 @@
         <v>4</v>
       </c>
       <c r="I23" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J23" s="3">
         <v>8</v>
       </c>
       <c r="K23">
         <f>SUM(D23:I23)</f>
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="2:27" x14ac:dyDescent="0.55000000000000004">
@@ -1717,14 +1729,14 @@
         <v>3</v>
       </c>
       <c r="I32" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J32" s="3">
         <v>4</v>
       </c>
       <c r="K32">
         <f t="shared" ref="K32:K34" si="2">SUM(D32:I32)</f>
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -1783,14 +1795,14 @@
         <v>2</v>
       </c>
       <c r="I34" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J34" s="3">
         <v>5</v>
       </c>
       <c r="K34">
         <f t="shared" si="2"/>
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -1887,6 +1899,10 @@
       <c r="J37" s="3">
         <v>5</v>
       </c>
+      <c r="K37">
+        <f>SUM(D37:J37)</f>
+        <v>29</v>
+      </c>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B38" s="1" t="s">
@@ -2015,7 +2031,7 @@
         <v>8</v>
       </c>
       <c r="N42">
-        <f t="shared" ref="N42:N63" si="3">SUM(E42:L42)</f>
+        <f t="shared" ref="N42:N69" si="3">SUM(E42:L42)</f>
         <v>53</v>
       </c>
     </row>
@@ -2240,10 +2256,10 @@
         <v>158</v>
       </c>
       <c r="E48" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F48" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G48" s="3">
         <v>6</v>
@@ -2264,11 +2280,11 @@
         <v>5</v>
       </c>
       <c r="M48" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N48">
         <f t="shared" si="3"/>
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -2339,7 +2355,7 @@
         <v>6</v>
       </c>
       <c r="J50" s="3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K50" s="3">
         <v>6</v>
@@ -2352,7 +2368,7 @@
       </c>
       <c r="N50">
         <f t="shared" si="3"/>
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -2938,8 +2954,12 @@
       <c r="M64" s="3">
         <v>3</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="N64">
+        <f t="shared" si="3"/>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B65" s="3" t="s">
         <v>89</v>
       </c>
@@ -2956,16 +2976,16 @@
         <v>3</v>
       </c>
       <c r="G65" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H65" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I65" s="3">
         <v>6</v>
       </c>
       <c r="J65" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K65" s="3">
         <v>6</v>
@@ -2976,8 +2996,12 @@
       <c r="M65" s="3">
         <v>6</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="N65">
+        <f t="shared" si="3"/>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B66" s="3" t="s">
         <v>93</v>
       </c>
@@ -2985,7 +3009,7 @@
         <v>44</v>
       </c>
       <c r="D66" s="3">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E66" s="3">
         <v>8</v>
@@ -3003,10 +3027,10 @@
         <v>6</v>
       </c>
       <c r="J66" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K66" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L66" s="3">
         <v>2</v>
@@ -3014,221 +3038,351 @@
       <c r="M66" s="3">
         <v>4</v>
       </c>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+      <c r="N66">
+        <f t="shared" si="3"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B67" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D67" s="3">
+        <v>161</v>
+      </c>
+      <c r="E67" s="3">
+        <v>9</v>
+      </c>
+      <c r="F67" s="3">
+        <v>7</v>
+      </c>
+      <c r="G67" s="3">
+        <v>3</v>
+      </c>
+      <c r="H67" s="3">
+        <v>6</v>
+      </c>
+      <c r="I67" s="3">
+        <v>4</v>
+      </c>
+      <c r="J67" s="3">
+        <v>11</v>
+      </c>
+      <c r="K67" s="3">
+        <v>5</v>
+      </c>
+      <c r="L67" s="3">
+        <v>2</v>
+      </c>
+      <c r="M67" s="3">
+        <v>4</v>
+      </c>
+      <c r="N67">
+        <f t="shared" si="3"/>
+        <v>47</v>
+      </c>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B68" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D68" s="3">
+        <v>77</v>
+      </c>
+      <c r="E68" s="3">
+        <v>3</v>
+      </c>
+      <c r="F68" s="3">
+        <v>1</v>
+      </c>
+      <c r="G68" s="3">
+        <v>3</v>
+      </c>
+      <c r="H68" s="3">
+        <v>1</v>
+      </c>
+      <c r="I68" s="3">
+        <v>6</v>
+      </c>
+      <c r="J68" s="3">
+        <v>2</v>
+      </c>
+      <c r="K68" s="3">
+        <v>3</v>
+      </c>
+      <c r="L68" s="3">
+        <v>2</v>
+      </c>
+      <c r="M68" s="3">
+        <v>1</v>
+      </c>
+      <c r="N68">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B69" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D69" s="3">
+        <v>152</v>
+      </c>
+      <c r="E69" s="3">
+        <v>2</v>
+      </c>
+      <c r="F69" s="3">
+        <v>4</v>
+      </c>
+      <c r="G69" s="3">
+        <v>4</v>
+      </c>
+      <c r="H69" s="3">
+        <v>2</v>
+      </c>
+      <c r="I69" s="3">
+        <v>3</v>
+      </c>
+      <c r="J69" s="3">
+        <v>3</v>
+      </c>
+      <c r="K69" s="3">
+        <v>4</v>
+      </c>
+      <c r="L69" s="3">
+        <v>2</v>
+      </c>
+      <c r="M69" s="3">
+        <v>1</v>
+      </c>
+      <c r="N69">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B70" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="B68" s="2" t="s">
+    <row r="71" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B71" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C68" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G68" s="2"/>
-      <c r="H68" s="2"/>
-      <c r="I68" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J68" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K68" s="2" t="s">
+      <c r="C71" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
+      <c r="I71" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K71" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="B69" t="s">
+    <row r="72" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B72" t="s">
         <v>70</v>
-      </c>
-      <c r="C69" t="s">
-        <v>66</v>
-      </c>
-      <c r="D69">
-        <v>8</v>
-      </c>
-      <c r="E69">
-        <v>2</v>
-      </c>
-      <c r="F69">
-        <v>3</v>
-      </c>
-      <c r="I69">
-        <v>7</v>
-      </c>
-      <c r="J69">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="B70" t="s">
-        <v>67</v>
-      </c>
-      <c r="C70" t="s">
-        <v>66</v>
-      </c>
-      <c r="D70">
-        <v>4</v>
-      </c>
-      <c r="E70">
-        <v>6</v>
-      </c>
-      <c r="F70">
-        <v>4</v>
-      </c>
-      <c r="I70">
-        <v>5</v>
-      </c>
-      <c r="J70">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="B71" t="s">
-        <v>68</v>
-      </c>
-      <c r="C71" t="s">
-        <v>66</v>
-      </c>
-      <c r="D71">
-        <v>10</v>
-      </c>
-      <c r="E71">
-        <v>10</v>
-      </c>
-      <c r="F71">
-        <v>5</v>
-      </c>
-      <c r="I71">
-        <v>10</v>
-      </c>
-      <c r="J71">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="B72" t="s">
-        <v>69</v>
       </c>
       <c r="C72" t="s">
         <v>66</v>
       </c>
       <c r="D72">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F72">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I72">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J72">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B73" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="C73" t="s">
         <v>66</v>
       </c>
       <c r="D73">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E73">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F73">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I73">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J73">
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B74" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C74" t="s">
         <v>66</v>
       </c>
       <c r="D74">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E74">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F74">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I74">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J74">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.55000000000000004">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B75" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C75" t="s">
         <v>66</v>
       </c>
       <c r="D75">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="E75">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F75">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I75">
+        <v>9</v>
+      </c>
+      <c r="J75">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B76" t="s">
+        <v>58</v>
+      </c>
+      <c r="C76" t="s">
+        <v>66</v>
+      </c>
+      <c r="D76">
+        <v>7</v>
+      </c>
+      <c r="E76">
+        <v>3</v>
+      </c>
+      <c r="F76">
+        <v>3</v>
+      </c>
+      <c r="I76">
+        <v>7</v>
+      </c>
+      <c r="J76">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B77" t="s">
+        <v>61</v>
+      </c>
+      <c r="C77" t="s">
+        <v>66</v>
+      </c>
+      <c r="D77">
+        <v>6</v>
+      </c>
+      <c r="E77">
+        <v>1</v>
+      </c>
+      <c r="F77">
+        <v>3</v>
+      </c>
+      <c r="I77">
+        <v>6</v>
+      </c>
+      <c r="J77">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B78" t="s">
+        <v>77</v>
+      </c>
+      <c r="C78" t="s">
+        <v>66</v>
+      </c>
+      <c r="D78">
+        <v>9</v>
+      </c>
+      <c r="E78">
+        <v>9</v>
+      </c>
+      <c r="F78">
+        <v>5</v>
+      </c>
+      <c r="I78">
         <v>13</v>
       </c>
-      <c r="J75">
+      <c r="J78">
         <v>16</v>
       </c>
     </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.55000000000000004">
-      <c r="B76" t="s">
+    <row r="79" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B79" t="s">
         <v>83</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C79" t="s">
         <v>84</v>
       </c>
-      <c r="D76">
-        <v>6</v>
-      </c>
-      <c r="E76">
-        <v>3</v>
-      </c>
-      <c r="F76">
-        <v>3</v>
-      </c>
-      <c r="I76">
-        <v>4</v>
-      </c>
-      <c r="J76">
+      <c r="D79">
+        <v>6</v>
+      </c>
+      <c r="E79">
+        <v>3</v>
+      </c>
+      <c r="F79">
+        <v>3</v>
+      </c>
+      <c r="I79">
+        <v>4</v>
+      </c>
+      <c r="J79">
         <v>4</v>
       </c>
     </row>

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhmgo\Desktop\野球15\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0731764-3F3F-4789-A89B-39F1CD4D11C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A00D5BD2-C0F2-4BD9-AECC-520479C265E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B57D1550-4E85-435D-BD6F-1B13E635EA51}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="98">
   <si>
     <t>野手・打者</t>
   </si>
@@ -387,6 +387,10 @@
   </si>
   <si>
     <t>サマーズ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>エンリケス</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -769,7 +773,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C402B4-0E60-4338-B3CD-2DB7A1A076E1}">
-  <dimension ref="B2:AA79"/>
+  <dimension ref="B2:AA80"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="14.75" customWidth="1"/>
@@ -2031,7 +2035,7 @@
         <v>8</v>
       </c>
       <c r="N42">
-        <f t="shared" ref="N42:N69" si="3">SUM(E42:L42)</f>
+        <f t="shared" ref="N42:N70" si="3">SUM(E42:L42)</f>
         <v>53</v>
       </c>
     </row>
@@ -3171,218 +3175,260 @@
     </row>
     <row r="70" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B70" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D70" s="3">
+        <v>166</v>
+      </c>
+      <c r="E70" s="3">
+        <v>3</v>
+      </c>
+      <c r="F70" s="3">
+        <v>2</v>
+      </c>
+      <c r="G70" s="3">
+        <v>2</v>
+      </c>
+      <c r="H70" s="3">
+        <v>4</v>
+      </c>
+      <c r="I70" s="3">
+        <v>3</v>
+      </c>
+      <c r="J70" s="3">
+        <v>6</v>
+      </c>
+      <c r="K70" s="3">
+        <v>3</v>
+      </c>
+      <c r="L70" s="3">
+        <v>2</v>
+      </c>
+      <c r="M70" s="3">
+        <v>1</v>
+      </c>
+      <c r="N70">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B71" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B71" s="2" t="s">
+    <row r="72" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B72" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C71" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G71" s="2"/>
-      <c r="H71" s="2"/>
-      <c r="I71" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J71" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K71" s="2" t="s">
+      <c r="C72" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
+      <c r="I72" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K72" s="2" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B72" t="s">
-        <v>70</v>
-      </c>
-      <c r="C72" t="s">
-        <v>66</v>
-      </c>
-      <c r="D72">
-        <v>8</v>
-      </c>
-      <c r="E72">
-        <v>2</v>
-      </c>
-      <c r="F72">
-        <v>3</v>
-      </c>
-      <c r="I72">
-        <v>7</v>
-      </c>
-      <c r="J72">
-        <v>6</v>
       </c>
     </row>
     <row r="73" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B73" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C73" t="s">
         <v>66</v>
       </c>
       <c r="D73">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E73">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F73">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I73">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J73">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B74" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C74" t="s">
         <v>66</v>
       </c>
       <c r="D74">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E74">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F74">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I74">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J74">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B75" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C75" t="s">
         <v>66</v>
       </c>
       <c r="D75">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E75">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F75">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I75">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J75">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="76" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B76" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="C76" t="s">
         <v>66</v>
       </c>
       <c r="D76">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E76">
         <v>3</v>
       </c>
       <c r="F76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I76">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J76">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="77" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B77" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C77" t="s">
         <v>66</v>
       </c>
       <c r="D77">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E77">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F77">
         <v>3</v>
       </c>
       <c r="I77">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J77">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B78" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="C78" t="s">
         <v>66</v>
       </c>
       <c r="D78">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E78">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F78">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I78">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J78">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="79" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B79" t="s">
+        <v>77</v>
+      </c>
+      <c r="C79" t="s">
+        <v>66</v>
+      </c>
+      <c r="D79">
+        <v>9</v>
+      </c>
+      <c r="E79">
+        <v>9</v>
+      </c>
+      <c r="F79">
+        <v>5</v>
+      </c>
+      <c r="I79">
+        <v>13</v>
+      </c>
+      <c r="J79">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="80" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B80" t="s">
         <v>83</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C80" t="s">
         <v>84</v>
       </c>
-      <c r="D79">
-        <v>6</v>
-      </c>
-      <c r="E79">
-        <v>3</v>
-      </c>
-      <c r="F79">
-        <v>3</v>
-      </c>
-      <c r="I79">
-        <v>4</v>
-      </c>
-      <c r="J79">
+      <c r="D80">
+        <v>6</v>
+      </c>
+      <c r="E80">
+        <v>3</v>
+      </c>
+      <c r="F80">
+        <v>3</v>
+      </c>
+      <c r="I80">
+        <v>4</v>
+      </c>
+      <c r="J80">
         <v>4</v>
       </c>
     </row>

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhmgo\Desktop\野球15\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhmgo\Desktop\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A00D5BD2-C0F2-4BD9-AECC-520479C265E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46AB849E-E9D6-4D60-8A8D-80494083280D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B57D1550-4E85-435D-BD6F-1B13E635EA51}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{B57D1550-4E85-435D-BD6F-1B13E635EA51}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -992,7 +992,7 @@
         <v>2</v>
       </c>
       <c r="E10" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" s="3">
         <v>10</v>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="K10">
         <f>SUM(D10:I10)</f>
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.55000000000000004">
@@ -1022,10 +1022,10 @@
         <v>17</v>
       </c>
       <c r="D11" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11" s="3">
         <v>6</v>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="K11">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.55000000000000004">
@@ -1154,10 +1154,10 @@
         <v>17</v>
       </c>
       <c r="D15" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E15" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F15" s="3">
         <v>5</v>
@@ -1220,7 +1220,7 @@
         <v>44</v>
       </c>
       <c r="D17" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E17" s="3">
         <v>6</v>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="K17">
         <f t="shared" si="0"/>
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="2:27" x14ac:dyDescent="0.55000000000000004">
@@ -1556,7 +1556,7 @@
         <v>13</v>
       </c>
       <c r="E27" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F27" s="3">
         <v>8</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="K27">
         <f>SUM(D27:I27)</f>
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="2:27" x14ac:dyDescent="0.55000000000000004">
@@ -1972,7 +1972,7 @@
         <v>5</v>
       </c>
       <c r="G41" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H41" s="3">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>6</v>
       </c>
       <c r="J41" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K41" s="3">
         <v>7</v>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="N41">
         <f>SUM(E41:L41)</f>
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -2302,22 +2302,22 @@
         <v>172</v>
       </c>
       <c r="E49" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F49" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G49" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H49" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I49" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J49" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K49" s="3">
         <v>8</v>
@@ -2326,11 +2326,11 @@
         <v>12</v>
       </c>
       <c r="M49" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="N49">
         <f t="shared" si="3"/>
-        <v>70</v>
+        <v>82</v>
       </c>
     </row>
     <row r="50" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -2359,7 +2359,7 @@
         <v>6</v>
       </c>
       <c r="J50" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K50" s="3">
         <v>6</v>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="N50">
         <f t="shared" si="3"/>
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -2437,13 +2437,13 @@
         <v>5</v>
       </c>
       <c r="H52" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I52" s="3">
         <v>5</v>
       </c>
       <c r="J52" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K52" s="3">
         <v>4</v>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="N52">
         <f t="shared" si="3"/>
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="53" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -2494,7 +2494,7 @@
         <v>2</v>
       </c>
       <c r="M53" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N53">
         <f t="shared" si="3"/>
@@ -2848,22 +2848,22 @@
         <v>175</v>
       </c>
       <c r="E62" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F62" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G62" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H62" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I62" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J62" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K62" s="3">
         <v>8</v>
@@ -2872,11 +2872,11 @@
         <v>12</v>
       </c>
       <c r="M62" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N62">
         <f t="shared" si="3"/>
-        <v>78</v>
+        <v>90</v>
       </c>
     </row>
     <row r="63" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -2890,22 +2890,22 @@
         <v>155</v>
       </c>
       <c r="E63" s="3">
+        <v>16</v>
+      </c>
+      <c r="F63" s="3">
         <v>14</v>
       </c>
-      <c r="F63" s="3">
+      <c r="G63" s="3">
+        <v>13</v>
+      </c>
+      <c r="H63" s="3">
         <v>12</v>
       </c>
-      <c r="G63" s="3">
-        <v>11</v>
-      </c>
-      <c r="H63" s="3">
-        <v>10</v>
-      </c>
       <c r="I63" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J63" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K63" s="3">
         <v>7</v>
@@ -2914,11 +2914,11 @@
         <v>11</v>
       </c>
       <c r="M63" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N63">
         <f t="shared" si="3"/>
-        <v>86</v>
+        <v>98</v>
       </c>
     </row>
     <row r="64" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -2971,19 +2971,19 @@
         <v>44</v>
       </c>
       <c r="D65" s="3">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E65" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F65" s="3">
         <v>3</v>
       </c>
       <c r="G65" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H65" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I65" s="3">
         <v>6</v>
@@ -3031,7 +3031,7 @@
         <v>6</v>
       </c>
       <c r="J66" s="3">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K66" s="3">
         <v>6</v>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="N66">
         <f t="shared" si="3"/>
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="67" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -3073,7 +3073,7 @@
         <v>4</v>
       </c>
       <c r="J67" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K67" s="3">
         <v>5</v>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="N67">
         <f t="shared" si="3"/>
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="68" spans="2:14" x14ac:dyDescent="0.55000000000000004">

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhmgo\Desktop\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46AB849E-E9D6-4D60-8A8D-80494083280D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1213599-E17F-42CE-9352-14B2B93D929E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{B57D1550-4E85-435D-BD6F-1B13E635EA51}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B57D1550-4E85-435D-BD6F-1B13E635EA51}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2365,14 +2365,14 @@
         <v>6</v>
       </c>
       <c r="L50" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M50" s="3">
         <v>4</v>
       </c>
       <c r="N50">
         <f t="shared" si="3"/>
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -3037,14 +3037,14 @@
         <v>6</v>
       </c>
       <c r="L66" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M66" s="3">
         <v>4</v>
       </c>
       <c r="N66">
         <f t="shared" si="3"/>
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="67" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -3079,14 +3079,14 @@
         <v>5</v>
       </c>
       <c r="L67" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M67" s="3">
         <v>4</v>
       </c>
       <c r="N67">
         <f t="shared" si="3"/>
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="68" spans="2:14" x14ac:dyDescent="0.55000000000000004">

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhmgo\Desktop\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1213599-E17F-42CE-9352-14B2B93D929E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86593888-1B98-43E2-A10F-A09F42DBF44A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B57D1550-4E85-435D-BD6F-1B13E635EA51}"/>
   </bookViews>
@@ -857,10 +857,10 @@
         <v>10</v>
       </c>
       <c r="D6" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" s="3">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F6" s="3">
         <v>10</v>
@@ -869,17 +869,17 @@
         <v>3</v>
       </c>
       <c r="H6" s="3">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I6" s="3">
         <v>11</v>
       </c>
       <c r="J6" s="3">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="K6">
         <f t="shared" ref="K6:K19" si="0">SUM(D6:I6)</f>
-        <v>55</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.55000000000000004">
@@ -1034,17 +1034,17 @@
         <v>3</v>
       </c>
       <c r="H11" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I11" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J11" s="3">
         <v>4</v>
       </c>
       <c r="K11">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.55000000000000004">
@@ -1154,29 +1154,29 @@
         <v>17</v>
       </c>
       <c r="D15" s="3">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="E15" s="3">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F15" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G15" s="3">
         <v>3</v>
       </c>
       <c r="H15" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I15" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J15" s="3">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="K15">
         <f t="shared" si="0"/>
-        <v>47</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.55000000000000004">
@@ -1322,29 +1322,29 @@
         <v>44</v>
       </c>
       <c r="D20" s="3">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="E20" s="3">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F20" s="3">
         <v>8</v>
       </c>
       <c r="G20" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H20" s="3">
         <v>2</v>
       </c>
       <c r="I20" s="3">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J20" s="3">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="K20">
         <f>SUM(D20:I20)</f>
-        <v>50</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="2:27" x14ac:dyDescent="0.55000000000000004">
@@ -1553,10 +1553,10 @@
         <v>52</v>
       </c>
       <c r="D27" s="3">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E27" s="3">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F27" s="3">
         <v>8</v>
@@ -1565,17 +1565,17 @@
         <v>3</v>
       </c>
       <c r="H27" s="3">
+        <v>15</v>
+      </c>
+      <c r="I27" s="3">
         <v>10</v>
       </c>
-      <c r="I27" s="3">
-        <v>8</v>
-      </c>
       <c r="J27" s="3">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="K27">
         <f>SUM(D27:I27)</f>
-        <v>54</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" spans="2:27" x14ac:dyDescent="0.55000000000000004">
@@ -1685,10 +1685,10 @@
         <v>52</v>
       </c>
       <c r="D31" s="3">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="E31" s="3">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F31" s="3">
         <v>5</v>
@@ -1700,14 +1700,14 @@
         <v>2</v>
       </c>
       <c r="I31" s="3">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J31" s="3">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="K31">
         <f>SUM(D31:I31)</f>
-        <v>45</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32" spans="2:27" x14ac:dyDescent="0.55000000000000004">
@@ -2302,35 +2302,35 @@
         <v>172</v>
       </c>
       <c r="E49" s="3">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F49" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G49" s="3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H49" s="3">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I49" s="3">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J49" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="K49" s="3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L49" s="3">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M49" s="3">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="N49">
         <f t="shared" si="3"/>
-        <v>82</v>
+        <v>117</v>
       </c>
     </row>
     <row r="50" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -2848,35 +2848,35 @@
         <v>175</v>
       </c>
       <c r="E62" s="3">
+        <v>16</v>
+      </c>
+      <c r="F62" s="3">
+        <v>15</v>
+      </c>
+      <c r="G62" s="3">
+        <v>15</v>
+      </c>
+      <c r="H62" s="3">
+        <v>16</v>
+      </c>
+      <c r="I62" s="3">
+        <v>15</v>
+      </c>
+      <c r="J62" s="3">
+        <v>21</v>
+      </c>
+      <c r="K62" s="3">
         <v>12</v>
       </c>
-      <c r="F62" s="3">
-        <v>11</v>
-      </c>
-      <c r="G62" s="3">
-        <v>11</v>
-      </c>
-      <c r="H62" s="3">
-        <v>12</v>
-      </c>
-      <c r="I62" s="3">
-        <v>11</v>
-      </c>
-      <c r="J62" s="3">
-        <v>13</v>
-      </c>
-      <c r="K62" s="3">
-        <v>8</v>
-      </c>
       <c r="L62" s="3">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M62" s="3">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="N62">
         <f t="shared" si="3"/>
-        <v>90</v>
+        <v>126</v>
       </c>
     </row>
     <row r="63" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -2890,35 +2890,35 @@
         <v>155</v>
       </c>
       <c r="E63" s="3">
+        <v>20</v>
+      </c>
+      <c r="F63" s="3">
+        <v>18</v>
+      </c>
+      <c r="G63" s="3">
+        <v>17</v>
+      </c>
+      <c r="H63" s="3">
         <v>16</v>
       </c>
-      <c r="F63" s="3">
-        <v>14</v>
-      </c>
-      <c r="G63" s="3">
-        <v>13</v>
-      </c>
-      <c r="H63" s="3">
-        <v>12</v>
-      </c>
       <c r="I63" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J63" s="3">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K63" s="3">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L63" s="3">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="M63" s="3">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="N63">
         <f t="shared" si="3"/>
-        <v>98</v>
+        <v>134</v>
       </c>
     </row>
     <row r="64" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -3302,19 +3302,19 @@
         <v>66</v>
       </c>
       <c r="D75">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E75">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F75">
         <v>5</v>
       </c>
       <c r="I75">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J75">
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="76" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -3394,19 +3394,19 @@
         <v>66</v>
       </c>
       <c r="D79">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E79">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F79">
         <v>5</v>
       </c>
       <c r="I79">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J79">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="80" spans="2:14" x14ac:dyDescent="0.55000000000000004">

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhmgo\Desktop\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86593888-1B98-43E2-A10F-A09F42DBF44A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE66AEFE-987E-442D-A3A8-07B7B97E937C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B57D1550-4E85-435D-BD6F-1B13E635EA51}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{B57D1550-4E85-435D-BD6F-1B13E635EA51}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="100">
   <si>
     <t>野手・打者</t>
   </si>
@@ -391,6 +391,14 @@
   </si>
   <si>
     <t>エンリケス</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>グラスノー</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ロブレスキー</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -773,7 +781,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C402B4-0E60-4338-B3CD-2DB7A1A076E1}">
-  <dimension ref="B2:AA80"/>
+  <dimension ref="B2:AA83"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="14.75" customWidth="1"/>
@@ -1987,14 +1995,14 @@
         <v>7</v>
       </c>
       <c r="L41" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M41" s="3">
         <v>9</v>
       </c>
       <c r="N41">
         <f>SUM(E41:L41)</f>
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -2035,7 +2043,7 @@
         <v>8</v>
       </c>
       <c r="N42">
-        <f t="shared" ref="N42:N70" si="3">SUM(E42:L42)</f>
+        <f t="shared" ref="N42:N72" si="3">SUM(E42:L42)</f>
         <v>53</v>
       </c>
     </row>
@@ -2692,10 +2700,10 @@
         <v>5</v>
       </c>
       <c r="I58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J58" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K58" s="3">
         <v>3</v>
@@ -2708,7 +2716,7 @@
       </c>
       <c r="N58">
         <f t="shared" si="3"/>
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="59" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -2722,7 +2730,7 @@
         <v>164</v>
       </c>
       <c r="E59" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F59" s="3">
         <v>8</v>
@@ -2731,10 +2739,10 @@
         <v>8</v>
       </c>
       <c r="H59" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I59" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J59" s="3">
         <v>7</v>
@@ -2750,7 +2758,7 @@
       </c>
       <c r="N59">
         <f t="shared" si="3"/>
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="60" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -2980,7 +2988,7 @@
         <v>3</v>
       </c>
       <c r="G65" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H65" s="3">
         <v>9</v>
@@ -3002,7 +3010,7 @@
       </c>
       <c r="N65">
         <f t="shared" si="3"/>
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -3217,147 +3225,176 @@
     </row>
     <row r="71" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B71" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D71" s="3">
+        <v>158</v>
+      </c>
+      <c r="E71" s="3">
+        <v>8</v>
+      </c>
+      <c r="F71" s="3">
+        <v>3</v>
+      </c>
+      <c r="G71" s="3">
+        <v>8</v>
+      </c>
+      <c r="H71" s="3">
+        <v>4</v>
+      </c>
+      <c r="I71" s="3">
+        <v>2</v>
+      </c>
+      <c r="J71" s="3">
+        <v>7</v>
+      </c>
+      <c r="K71" s="3">
+        <v>7</v>
+      </c>
+      <c r="L71" s="3">
+        <v>6</v>
+      </c>
+      <c r="M71" s="3">
+        <v>6</v>
+      </c>
+      <c r="N71">
+        <f t="shared" si="3"/>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B72" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D72" s="3">
+        <v>156</v>
+      </c>
+      <c r="E72" s="3">
+        <v>3</v>
+      </c>
+      <c r="F72" s="3">
+        <v>6</v>
+      </c>
+      <c r="G72" s="3">
+        <v>4</v>
+      </c>
+      <c r="H72" s="3">
+        <v>3</v>
+      </c>
+      <c r="I72" s="3">
+        <v>7</v>
+      </c>
+      <c r="J72" s="3">
+        <v>4</v>
+      </c>
+      <c r="K72" s="3">
+        <v>7</v>
+      </c>
+      <c r="L72" s="3">
+        <v>7</v>
+      </c>
+      <c r="M72" s="3">
+        <v>5</v>
+      </c>
+      <c r="N72">
+        <f t="shared" si="3"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B73" s="3"/>
+      <c r="C73" s="3"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3"/>
+      <c r="G73" s="3"/>
+      <c r="H73" s="3"/>
+      <c r="I73" s="3"/>
+      <c r="J73" s="3"/>
+      <c r="K73" s="3"/>
+      <c r="L73" s="3"/>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B74" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B72" s="2" t="s">
+    <row r="75" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B75" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C72" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G72" s="2"/>
-      <c r="H72" s="2"/>
-      <c r="I72" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J72" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K72" s="2" t="s">
+      <c r="C75" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2"/>
+      <c r="I75" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K75" s="2" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B73" t="s">
-        <v>70</v>
-      </c>
-      <c r="C73" t="s">
-        <v>66</v>
-      </c>
-      <c r="D73">
-        <v>8</v>
-      </c>
-      <c r="E73">
-        <v>2</v>
-      </c>
-      <c r="F73">
-        <v>3</v>
-      </c>
-      <c r="I73">
-        <v>7</v>
-      </c>
-      <c r="J73">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B74" t="s">
-        <v>67</v>
-      </c>
-      <c r="C74" t="s">
-        <v>66</v>
-      </c>
-      <c r="D74">
-        <v>4</v>
-      </c>
-      <c r="E74">
-        <v>6</v>
-      </c>
-      <c r="F74">
-        <v>4</v>
-      </c>
-      <c r="I74">
-        <v>5</v>
-      </c>
-      <c r="J74">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B75" t="s">
-        <v>68</v>
-      </c>
-      <c r="C75" t="s">
-        <v>66</v>
-      </c>
-      <c r="D75">
-        <v>22</v>
-      </c>
-      <c r="E75">
-        <v>16</v>
-      </c>
-      <c r="F75">
-        <v>5</v>
-      </c>
-      <c r="I75">
-        <v>14</v>
-      </c>
-      <c r="J75">
-        <v>25</v>
       </c>
     </row>
     <row r="76" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B76" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C76" t="s">
         <v>66</v>
       </c>
       <c r="D76">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I76">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J76">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B77" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="C77" t="s">
         <v>66</v>
       </c>
       <c r="D77">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E77">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F77">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I77">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J77">
         <v>5</v>
@@ -3365,70 +3402,139 @@
     </row>
     <row r="78" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B78" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="C78" t="s">
         <v>66</v>
       </c>
       <c r="D78">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="E78">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="F78">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I78">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="J78">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="79" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B79" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C79" t="s">
         <v>66</v>
       </c>
       <c r="D79">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="E79">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="F79">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I79">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J79">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B80" t="s">
+        <v>58</v>
+      </c>
+      <c r="C80" t="s">
+        <v>66</v>
+      </c>
+      <c r="D80">
+        <v>7</v>
+      </c>
+      <c r="E80">
+        <v>3</v>
+      </c>
+      <c r="F80">
+        <v>3</v>
+      </c>
+      <c r="I80">
+        <v>7</v>
+      </c>
+      <c r="J80">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B81" t="s">
+        <v>61</v>
+      </c>
+      <c r="C81" t="s">
+        <v>66</v>
+      </c>
+      <c r="D81">
+        <v>6</v>
+      </c>
+      <c r="E81">
+        <v>1</v>
+      </c>
+      <c r="F81">
+        <v>3</v>
+      </c>
+      <c r="I81">
+        <v>6</v>
+      </c>
+      <c r="J81">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B82" t="s">
+        <v>77</v>
+      </c>
+      <c r="C82" t="s">
+        <v>66</v>
+      </c>
+      <c r="D82">
+        <v>24</v>
+      </c>
+      <c r="E82">
+        <v>17</v>
+      </c>
+      <c r="F82">
+        <v>5</v>
+      </c>
+      <c r="I82">
+        <v>16</v>
+      </c>
+      <c r="J82">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="83" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B83" t="s">
         <v>83</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C83" t="s">
         <v>84</v>
       </c>
-      <c r="D80">
-        <v>6</v>
-      </c>
-      <c r="E80">
-        <v>3</v>
-      </c>
-      <c r="F80">
-        <v>3</v>
-      </c>
-      <c r="I80">
-        <v>4</v>
-      </c>
-      <c r="J80">
+      <c r="D83">
+        <v>6</v>
+      </c>
+      <c r="E83">
+        <v>3</v>
+      </c>
+      <c r="F83">
+        <v>3</v>
+      </c>
+      <c r="I83">
+        <v>4</v>
+      </c>
+      <c r="J83">
         <v>4</v>
       </c>
     </row>

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhmgo\Desktop\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE66AEFE-987E-442D-A3A8-07B7B97E937C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D2BA221-8A5C-45E7-90D6-B17281CC1A94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{B57D1550-4E85-435D-BD6F-1B13E635EA51}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="105">
   <si>
     <t>野手・打者</t>
   </si>
@@ -399,6 +399,29 @@
   </si>
   <si>
     <t>ロブレスキー</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>クレメンス</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ジョンソン</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ローズ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>両</t>
+    <rPh sb="0" eb="1">
+      <t>リョウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ヘンダーソン</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -781,7 +804,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C402B4-0E60-4338-B3CD-2DB7A1A076E1}">
-  <dimension ref="B2:AA83"/>
+  <dimension ref="B2:AA87"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="14.75" customWidth="1"/>
@@ -886,7 +909,7 @@
         <v>28</v>
       </c>
       <c r="K6">
-        <f t="shared" ref="K6:K19" si="0">SUM(D6:I6)</f>
+        <f t="shared" ref="K6:K39" si="0">SUM(D6:I6)</f>
         <v>69</v>
       </c>
     </row>
@@ -1018,7 +1041,7 @@
         <v>5</v>
       </c>
       <c r="K10">
-        <f>SUM(D10:I10)</f>
+        <f t="shared" si="0"/>
         <v>34</v>
       </c>
     </row>
@@ -1162,7 +1185,7 @@
         <v>17</v>
       </c>
       <c r="D15" s="3">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="E15" s="3">
         <v>20</v>
@@ -1180,11 +1203,11 @@
         <v>4</v>
       </c>
       <c r="J15" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K15">
         <f t="shared" si="0"/>
-        <v>67</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.55000000000000004">
@@ -1282,7 +1305,7 @@
         <v>5</v>
       </c>
       <c r="K18">
-        <f>SUM(D18:I18)</f>
+        <f t="shared" si="0"/>
         <v>34</v>
       </c>
     </row>
@@ -1330,7 +1353,7 @@
         <v>44</v>
       </c>
       <c r="D20" s="3">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E20" s="3">
         <v>18</v>
@@ -1339,20 +1362,20 @@
         <v>8</v>
       </c>
       <c r="G20" s="3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H20" s="3">
         <v>2</v>
       </c>
       <c r="I20" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J20" s="3">
         <v>25</v>
       </c>
       <c r="K20">
-        <f>SUM(D20:I20)</f>
-        <v>81</v>
+        <f t="shared" si="0"/>
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="2:27" x14ac:dyDescent="0.55000000000000004">
@@ -1384,7 +1407,7 @@
         <v>5</v>
       </c>
       <c r="K21">
-        <f>SUM(D21:I21)</f>
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
     </row>
@@ -1417,8 +1440,8 @@
         <v>3</v>
       </c>
       <c r="K22">
-        <f>SUM(D22:J22)</f>
-        <v>25</v>
+        <f t="shared" si="0"/>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="2:27" x14ac:dyDescent="0.55000000000000004">
@@ -1450,7 +1473,7 @@
         <v>8</v>
       </c>
       <c r="K23">
-        <f>SUM(D23:I23)</f>
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
     </row>
@@ -1483,7 +1506,7 @@
         <v>5</v>
       </c>
       <c r="K24">
-        <f t="shared" ref="K24:K30" si="1">SUM(D24:I24)</f>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
     </row>
@@ -1516,7 +1539,7 @@
         <v>7</v>
       </c>
       <c r="K25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>39</v>
       </c>
     </row>
@@ -1549,8 +1572,8 @@
         <v>6</v>
       </c>
       <c r="K26">
-        <f>SUM(D26:J26)</f>
-        <v>39</v>
+        <f t="shared" si="0"/>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="2:27" x14ac:dyDescent="0.55000000000000004">
@@ -1561,7 +1584,7 @@
         <v>52</v>
       </c>
       <c r="D27" s="3">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="E27" s="3">
         <v>19</v>
@@ -1573,7 +1596,7 @@
         <v>3</v>
       </c>
       <c r="H27" s="3">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I27" s="3">
         <v>10</v>
@@ -1582,8 +1605,8 @@
         <v>28</v>
       </c>
       <c r="K27">
-        <f>SUM(D27:I27)</f>
-        <v>82</v>
+        <f t="shared" si="0"/>
+        <v>99</v>
       </c>
     </row>
     <row r="28" spans="2:27" x14ac:dyDescent="0.55000000000000004">
@@ -1615,7 +1638,7 @@
         <v>4</v>
       </c>
       <c r="K28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
     </row>
@@ -1648,7 +1671,7 @@
         <v>2</v>
       </c>
       <c r="K29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
     </row>
@@ -1681,7 +1704,7 @@
         <v>5</v>
       </c>
       <c r="K30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
     </row>
@@ -1693,7 +1716,7 @@
         <v>52</v>
       </c>
       <c r="D31" s="3">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="E31" s="3">
         <v>16</v>
@@ -1702,20 +1725,20 @@
         <v>5</v>
       </c>
       <c r="G31" s="3">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="H31" s="3">
         <v>2</v>
       </c>
       <c r="I31" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J31" s="3">
         <v>25</v>
       </c>
       <c r="K31">
-        <f>SUM(D31:I31)</f>
-        <v>74</v>
+        <f t="shared" si="0"/>
+        <v>90</v>
       </c>
     </row>
     <row r="32" spans="2:27" x14ac:dyDescent="0.55000000000000004">
@@ -1747,7 +1770,7 @@
         <v>4</v>
       </c>
       <c r="K32">
-        <f t="shared" ref="K32:K34" si="2">SUM(D32:I32)</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
     </row>
@@ -1780,7 +1803,7 @@
         <v>5</v>
       </c>
       <c r="K33">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
     </row>
@@ -1813,7 +1836,7 @@
         <v>5</v>
       </c>
       <c r="K34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
     </row>
@@ -1846,8 +1869,8 @@
         <v>4</v>
       </c>
       <c r="K35">
-        <f>SUM(D35:J35)</f>
-        <v>26</v>
+        <f t="shared" si="0"/>
+        <v>22</v>
       </c>
     </row>
     <row r="36" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -1879,8 +1902,8 @@
         <v>7</v>
       </c>
       <c r="K36">
-        <f>SUM(D36:J36)</f>
-        <v>42</v>
+        <f t="shared" si="0"/>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -1912,717 +1935,699 @@
         <v>5</v>
       </c>
       <c r="K37">
-        <f>SUM(D37:J37)</f>
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="38" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B38" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D38" s="3">
+        <v>4</v>
+      </c>
+      <c r="E38" s="3">
+        <v>26</v>
+      </c>
+      <c r="F38" s="3">
+        <v>6</v>
+      </c>
+      <c r="G38" s="3">
+        <v>12</v>
+      </c>
+      <c r="H38" s="3">
+        <v>12</v>
+      </c>
+      <c r="I38" s="3">
+        <v>9</v>
+      </c>
+      <c r="J38" s="3">
+        <v>26</v>
+      </c>
+      <c r="K38">
+        <f t="shared" si="0"/>
+        <v>69</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B39" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D39" s="3">
+        <v>25</v>
+      </c>
+      <c r="E39" s="3">
+        <v>20</v>
+      </c>
+      <c r="F39" s="3">
+        <v>16</v>
+      </c>
+      <c r="G39" s="3">
+        <v>3</v>
+      </c>
+      <c r="H39" s="3">
+        <v>10</v>
+      </c>
+      <c r="I39" s="3">
+        <v>8</v>
+      </c>
+      <c r="J39" s="3">
+        <v>24</v>
+      </c>
+      <c r="K39">
+        <f>SUM(D39:J39)</f>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B40" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J40" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B42" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I42" s="2" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B38" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J38" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B40" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="J40" s="2" t="s">
+      <c r="J42" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="K40" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="L40" s="2" t="s">
+      <c r="K42" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L42" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M40" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N40" s="2" t="s">
+      <c r="M42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N42" s="2" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B41" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D41" s="3">
-        <v>165</v>
-      </c>
-      <c r="E41" s="3">
-        <v>9</v>
-      </c>
-      <c r="F41" s="3">
-        <v>5</v>
-      </c>
-      <c r="G41" s="3">
-        <v>8</v>
-      </c>
-      <c r="H41" s="3">
-        <v>8</v>
-      </c>
-      <c r="I41" s="3">
-        <v>6</v>
-      </c>
-      <c r="J41" s="3">
-        <v>8</v>
-      </c>
-      <c r="K41" s="3">
-        <v>7</v>
-      </c>
-      <c r="L41" s="3">
-        <v>6</v>
-      </c>
-      <c r="M41" s="3">
-        <v>9</v>
-      </c>
-      <c r="N41">
-        <f>SUM(E41:L41)</f>
-        <v>57</v>
-      </c>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B42" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D42" s="3">
-        <v>157</v>
-      </c>
-      <c r="E42" s="3">
-        <v>8</v>
-      </c>
-      <c r="F42" s="3">
-        <v>3</v>
-      </c>
-      <c r="G42" s="3">
-        <v>7</v>
-      </c>
-      <c r="H42" s="3">
-        <v>7</v>
-      </c>
-      <c r="I42" s="3">
-        <v>8</v>
-      </c>
-      <c r="J42" s="3">
-        <v>7</v>
-      </c>
-      <c r="K42" s="3">
-        <v>6</v>
-      </c>
-      <c r="L42" s="3">
-        <v>7</v>
-      </c>
-      <c r="M42" s="3">
-        <v>8</v>
-      </c>
-      <c r="N42">
-        <f t="shared" ref="N42:N72" si="3">SUM(E42:L42)</f>
-        <v>53</v>
       </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B43" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D43" s="3">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="E43" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F43" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G43" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H43" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I43" s="3">
         <v>6</v>
       </c>
       <c r="J43" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K43" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L43" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M43" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N43">
-        <f t="shared" si="3"/>
-        <v>47</v>
+        <f>SUM(E43:L43)</f>
+        <v>57</v>
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B44" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D44" s="3">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="E44" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F44" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G44" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H44" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I44" s="3">
         <v>8</v>
       </c>
       <c r="J44" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K44" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L44" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M44" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N44">
-        <f t="shared" si="3"/>
-        <v>46</v>
+        <f t="shared" ref="N44:N76" si="1">SUM(E44:L44)</f>
+        <v>53</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D45" s="3">
+        <v>155</v>
+      </c>
+      <c r="E45" s="3">
+        <v>5</v>
+      </c>
+      <c r="F45" s="3">
+        <v>2</v>
+      </c>
+      <c r="G45" s="3">
         <v>10</v>
       </c>
-      <c r="D45" s="3">
-        <v>220</v>
-      </c>
-      <c r="E45" s="3">
-        <v>1</v>
-      </c>
-      <c r="F45" s="3">
-        <v>1</v>
-      </c>
-      <c r="G45" s="3">
-        <v>9</v>
-      </c>
       <c r="H45" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I45" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J45" s="3">
         <v>6</v>
       </c>
       <c r="K45" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L45" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M45" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N45">
-        <f t="shared" si="3"/>
-        <v>31</v>
+        <f t="shared" si="1"/>
+        <v>47</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B46" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D46" s="3">
-        <v>100</v>
+        <v>148</v>
       </c>
       <c r="E46" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F46" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G46" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H46" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I46" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J46" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K46" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L46" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M46" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N46">
-        <f t="shared" si="3"/>
-        <v>63</v>
+        <f t="shared" si="1"/>
+        <v>46</v>
       </c>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B47" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D47" s="3">
-        <v>149</v>
+        <v>220</v>
       </c>
       <c r="E47" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F47" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G47" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H47" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I47" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J47" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K47" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L47" s="3">
         <v>6</v>
       </c>
       <c r="M47" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N47">
-        <f t="shared" si="3"/>
-        <v>48</v>
+        <f t="shared" si="1"/>
+        <v>31</v>
       </c>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B48" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D48" s="3">
-        <v>158</v>
+        <v>100</v>
       </c>
       <c r="E48" s="3">
         <v>9</v>
       </c>
       <c r="F48" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G48" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H48" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I48" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J48" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K48" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L48" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M48" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N48">
-        <f t="shared" si="3"/>
-        <v>49</v>
+        <f t="shared" si="1"/>
+        <v>63</v>
       </c>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B49" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D49" s="3">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="E49" s="3">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="F49" s="3">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G49" s="3">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H49" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I49" s="3">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J49" s="3">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K49" s="3">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L49" s="3">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="M49" s="3">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="N49">
-        <f t="shared" si="3"/>
-        <v>117</v>
+        <f t="shared" si="1"/>
+        <v>48</v>
       </c>
     </row>
     <row r="50" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B50" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D50" s="3">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="E50" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F50" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G50" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H50" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I50" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J50" s="3">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="K50" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L50" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M50" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N50">
-        <f t="shared" si="3"/>
-        <v>54</v>
+        <f t="shared" si="1"/>
+        <v>49</v>
       </c>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B51" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D51" s="3">
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="E51" s="3">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="F51" s="3">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="G51" s="3">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="H51" s="3">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="I51" s="3">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="J51" s="3">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="K51" s="3">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="L51" s="3">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="M51" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="N51">
-        <f t="shared" si="3"/>
-        <v>49</v>
+        <f t="shared" si="1"/>
+        <v>206</v>
       </c>
     </row>
     <row r="52" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B52" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="D52" s="3">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E52" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F52" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G52" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H52" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I52" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J52" s="3">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K52" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L52" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M52" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N52">
-        <f t="shared" si="3"/>
-        <v>50</v>
+        <f t="shared" si="1"/>
+        <v>54</v>
       </c>
     </row>
     <row r="53" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B53" s="3" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="D53" s="3">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="E53" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F53" s="3">
+        <v>4</v>
+      </c>
+      <c r="G53" s="3">
+        <v>5</v>
+      </c>
+      <c r="H53" s="3">
+        <v>5</v>
+      </c>
+      <c r="I53" s="3">
         <v>10</v>
       </c>
-      <c r="G53" s="3">
-        <v>2</v>
-      </c>
-      <c r="H53" s="3">
-        <v>2</v>
-      </c>
-      <c r="I53" s="3">
-        <v>5</v>
-      </c>
       <c r="J53" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K53" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L53" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M53" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N53">
-        <f t="shared" si="3"/>
-        <v>30</v>
+        <f t="shared" si="1"/>
+        <v>49</v>
       </c>
     </row>
     <row r="54" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B54" s="3" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D54" s="3">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="E54" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F54" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G54" s="3">
+        <v>5</v>
+      </c>
+      <c r="H54" s="3">
         <v>9</v>
       </c>
-      <c r="H54" s="3">
-        <v>7</v>
-      </c>
       <c r="I54" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J54" s="3">
         <v>9</v>
       </c>
       <c r="K54" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L54" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M54" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N54">
-        <f t="shared" si="3"/>
-        <v>36</v>
+        <f t="shared" si="1"/>
+        <v>50</v>
       </c>
     </row>
     <row r="55" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B55" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D55" s="3">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="E55" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F55" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G55" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H55" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I55" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J55" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K55" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L55" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M55" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N55">
-        <f t="shared" si="3"/>
-        <v>37</v>
+        <f t="shared" si="1"/>
+        <v>30</v>
       </c>
     </row>
     <row r="56" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B56" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D56" s="3">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="E56" s="3">
         <v>2</v>
       </c>
       <c r="F56" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G56" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H56" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I56" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J56" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K56" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L56" s="3">
         <v>2</v>
@@ -2631,67 +2636,67 @@
         <v>3</v>
       </c>
       <c r="N56">
-        <f t="shared" si="3"/>
-        <v>34</v>
+        <f t="shared" si="1"/>
+        <v>36</v>
       </c>
     </row>
     <row r="57" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B57" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D57" s="3">
-        <v>125</v>
+        <v>165</v>
       </c>
       <c r="E57" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F57" s="3">
         <v>2</v>
       </c>
       <c r="G57" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H57" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I57" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J57" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K57" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L57" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M57" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N57">
-        <f t="shared" si="3"/>
-        <v>19</v>
+        <f t="shared" si="1"/>
+        <v>37</v>
       </c>
     </row>
     <row r="58" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B58" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D58" s="3">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="E58" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F58" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G58" s="3">
         <v>5</v>
@@ -2700,196 +2705,196 @@
         <v>5</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J58" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K58" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L58" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M58" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N58">
-        <f t="shared" si="3"/>
-        <v>37</v>
+        <f t="shared" si="1"/>
+        <v>34</v>
       </c>
     </row>
     <row r="59" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B59" s="3" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D59" s="3">
-        <v>164</v>
+        <v>125</v>
       </c>
       <c r="E59" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F59" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G59" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H59" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I59" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J59" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K59" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L59" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M59" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="N59">
-        <f t="shared" si="3"/>
-        <v>52</v>
+        <f t="shared" si="1"/>
+        <v>19</v>
       </c>
     </row>
     <row r="60" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B60" s="3" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D60" s="3">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E60" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F60" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G60" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H60" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I60" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J60" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K60" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L60" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M60" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N60">
-        <f t="shared" si="3"/>
-        <v>30</v>
+        <f t="shared" si="1"/>
+        <v>38</v>
       </c>
     </row>
     <row r="61" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B61" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D61" s="3">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="E61" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F61" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G61" s="3">
         <v>8</v>
       </c>
       <c r="H61" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I61" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J61" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K61" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L61" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M61" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N61">
-        <f t="shared" si="3"/>
-        <v>46</v>
+        <f t="shared" si="1"/>
+        <v>52</v>
       </c>
     </row>
     <row r="62" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B62" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D62" s="3">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="E62" s="3">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="F62" s="3">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G62" s="3">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="H62" s="3">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="I62" s="3">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="J62" s="3">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="K62" s="3">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L62" s="3">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="M62" s="3">
+        <v>3</v>
+      </c>
+      <c r="N62">
+        <f t="shared" si="1"/>
         <v>30</v>
-      </c>
-      <c r="N62">
-        <f t="shared" si="3"/>
-        <v>126</v>
       </c>
     </row>
     <row r="63" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B63" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>44</v>
@@ -2898,316 +2903,316 @@
         <v>155</v>
       </c>
       <c r="E63" s="3">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F63" s="3">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="G63" s="3">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H63" s="3">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="I63" s="3">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J63" s="3">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="K63" s="3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="L63" s="3">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="M63" s="3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="N63">
-        <f t="shared" si="3"/>
-        <v>134</v>
+        <f t="shared" si="1"/>
+        <v>46</v>
       </c>
     </row>
     <row r="64" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B64" s="3" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D64" s="3">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="E64" s="3">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="F64" s="3">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="G64" s="3">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="H64" s="3">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="I64" s="3">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="J64" s="3">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="K64" s="3">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="L64" s="3">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="M64" s="3">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="N64">
-        <f t="shared" si="3"/>
-        <v>33</v>
+        <f t="shared" si="1"/>
+        <v>215</v>
       </c>
     </row>
     <row r="65" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B65" s="3" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D65" s="3">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="E65" s="3">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="F65" s="3">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="G65" s="3">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="H65" s="3">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="I65" s="3">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="J65" s="3">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="K65" s="3">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="L65" s="3">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="M65" s="3">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="N65">
-        <f t="shared" si="3"/>
-        <v>54</v>
+        <f t="shared" si="1"/>
+        <v>223</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B66" s="3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D66" s="3">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="E66" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F66" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G66" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H66" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I66" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J66" s="3">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="K66" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L66" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M66" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N66">
-        <f t="shared" si="3"/>
-        <v>52</v>
+        <f t="shared" si="1"/>
+        <v>33</v>
       </c>
     </row>
     <row r="67" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B67" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D67" s="3">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="E67" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F67" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G67" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H67" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I67" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J67" s="3">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K67" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L67" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M67" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N67">
-        <f t="shared" si="3"/>
-        <v>50</v>
+        <f t="shared" si="1"/>
+        <v>52</v>
       </c>
     </row>
     <row r="68" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B68" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D68" s="3">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="E68" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F68" s="3">
         <v>1</v>
       </c>
       <c r="G68" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H68" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I68" s="3">
         <v>6</v>
       </c>
       <c r="J68" s="3">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="K68" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L68" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M68" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N68">
-        <f t="shared" si="3"/>
-        <v>21</v>
+        <f t="shared" si="1"/>
+        <v>52</v>
       </c>
     </row>
     <row r="69" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B69" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D69" s="3">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="E69" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F69" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G69" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H69" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I69" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J69" s="3">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K69" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L69" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M69" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N69">
-        <f t="shared" si="3"/>
-        <v>24</v>
+        <f t="shared" si="1"/>
+        <v>50</v>
       </c>
     </row>
     <row r="70" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B70" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D70" s="3">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="E70" s="3">
         <v>3</v>
       </c>
       <c r="F70" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G70" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H70" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I70" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J70" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K70" s="3">
         <v>3</v>
@@ -3219,245 +3224,321 @@
         <v>1</v>
       </c>
       <c r="N70">
-        <f t="shared" si="3"/>
-        <v>25</v>
+        <f t="shared" si="1"/>
+        <v>21</v>
       </c>
     </row>
     <row r="71" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B71" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D71" s="3">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="E71" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F71" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G71" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H71" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I71" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J71" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K71" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L71" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M71" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N71">
-        <f t="shared" si="3"/>
-        <v>45</v>
+        <f t="shared" si="1"/>
+        <v>24</v>
       </c>
     </row>
     <row r="72" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B72" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D72" s="3">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E72" s="3">
         <v>3</v>
       </c>
       <c r="F72" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G72" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H72" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I72" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J72" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K72" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L72" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M72" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N72">
-        <f t="shared" si="3"/>
-        <v>41</v>
+        <f t="shared" si="1"/>
+        <v>25</v>
       </c>
     </row>
     <row r="73" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B73" s="3"/>
-      <c r="C73" s="3"/>
-      <c r="D73" s="3"/>
-      <c r="E73" s="3"/>
-      <c r="F73" s="3"/>
-      <c r="G73" s="3"/>
-      <c r="H73" s="3"/>
-      <c r="I73" s="3"/>
-      <c r="J73" s="3"/>
-      <c r="K73" s="3"/>
-      <c r="L73" s="3"/>
-      <c r="M73" s="3"/>
+      <c r="B73" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D73" s="3">
+        <v>158</v>
+      </c>
+      <c r="E73" s="3">
+        <v>8</v>
+      </c>
+      <c r="F73" s="3">
+        <v>3</v>
+      </c>
+      <c r="G73" s="3">
+        <v>8</v>
+      </c>
+      <c r="H73" s="3">
+        <v>4</v>
+      </c>
+      <c r="I73" s="3">
+        <v>3</v>
+      </c>
+      <c r="J73" s="3">
+        <v>7</v>
+      </c>
+      <c r="K73" s="3">
+        <v>7</v>
+      </c>
+      <c r="L73" s="3">
+        <v>6</v>
+      </c>
+      <c r="M73" s="3">
+        <v>6</v>
+      </c>
+      <c r="N73">
+        <f t="shared" si="1"/>
+        <v>46</v>
+      </c>
     </row>
     <row r="74" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B74" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D74" s="3">
+        <v>156</v>
+      </c>
+      <c r="E74" s="3">
+        <v>3</v>
+      </c>
+      <c r="F74" s="3">
+        <v>6</v>
+      </c>
+      <c r="G74" s="3">
+        <v>4</v>
+      </c>
+      <c r="H74" s="3">
+        <v>3</v>
+      </c>
+      <c r="I74" s="3">
+        <v>7</v>
+      </c>
+      <c r="J74" s="3">
+        <v>4</v>
+      </c>
+      <c r="K74" s="3">
+        <v>7</v>
+      </c>
+      <c r="L74" s="3">
+        <v>7</v>
+      </c>
+      <c r="M74" s="3">
+        <v>5</v>
+      </c>
+      <c r="N74">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B75" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D75" s="3">
+        <v>161</v>
+      </c>
+      <c r="E75" s="3">
+        <v>28</v>
+      </c>
+      <c r="F75" s="3">
+        <v>23</v>
+      </c>
+      <c r="G75" s="3">
+        <v>32</v>
+      </c>
+      <c r="H75" s="3">
+        <v>24</v>
+      </c>
+      <c r="I75" s="3">
+        <v>30</v>
+      </c>
+      <c r="J75" s="3">
+        <v>31</v>
+      </c>
+      <c r="K75" s="3">
+        <v>23</v>
+      </c>
+      <c r="L75" s="3">
+        <v>21</v>
+      </c>
+      <c r="M75" s="3">
+        <v>30</v>
+      </c>
+      <c r="N75">
+        <f t="shared" si="1"/>
+        <v>212</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B76" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D76" s="3">
+        <v>164</v>
+      </c>
+      <c r="E76" s="3">
+        <v>10</v>
+      </c>
+      <c r="F76" s="3">
+        <v>40</v>
+      </c>
+      <c r="G76" s="3">
+        <v>10</v>
+      </c>
+      <c r="H76" s="3">
+        <v>27</v>
+      </c>
+      <c r="I76" s="3">
+        <v>27</v>
+      </c>
+      <c r="J76" s="3">
+        <v>33</v>
+      </c>
+      <c r="K76" s="3">
+        <v>23</v>
+      </c>
+      <c r="L76" s="3">
+        <v>20</v>
+      </c>
+      <c r="M76" s="3">
+        <v>29</v>
+      </c>
+      <c r="N76">
+        <f t="shared" si="1"/>
+        <v>190</v>
+      </c>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B77" s="3"/>
+      <c r="C77" s="3"/>
+      <c r="D77" s="3"/>
+      <c r="E77" s="3"/>
+      <c r="F77" s="3"/>
+      <c r="G77" s="3"/>
+      <c r="H77" s="3"/>
+      <c r="I77" s="3"/>
+      <c r="J77" s="3"/>
+      <c r="K77" s="3"/>
+      <c r="L77" s="3"/>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="78" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B78" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B75" s="2" t="s">
+    <row r="79" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B79" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C75" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G75" s="2"/>
-      <c r="H75" s="2"/>
-      <c r="I75" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J75" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K75" s="2" t="s">
+      <c r="C79" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2"/>
+      <c r="I79" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K79" s="2" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B76" t="s">
-        <v>70</v>
-      </c>
-      <c r="C76" t="s">
-        <v>66</v>
-      </c>
-      <c r="D76">
-        <v>8</v>
-      </c>
-      <c r="E76">
-        <v>2</v>
-      </c>
-      <c r="F76">
-        <v>3</v>
-      </c>
-      <c r="I76">
-        <v>7</v>
-      </c>
-      <c r="J76">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B77" t="s">
-        <v>67</v>
-      </c>
-      <c r="C77" t="s">
-        <v>66</v>
-      </c>
-      <c r="D77">
-        <v>4</v>
-      </c>
-      <c r="E77">
-        <v>6</v>
-      </c>
-      <c r="F77">
-        <v>4</v>
-      </c>
-      <c r="I77">
-        <v>5</v>
-      </c>
-      <c r="J77">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="78" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B78" t="s">
-        <v>68</v>
-      </c>
-      <c r="C78" t="s">
-        <v>66</v>
-      </c>
-      <c r="D78">
-        <v>22</v>
-      </c>
-      <c r="E78">
-        <v>16</v>
-      </c>
-      <c r="F78">
-        <v>5</v>
-      </c>
-      <c r="I78">
-        <v>14</v>
-      </c>
-      <c r="J78">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B79" t="s">
-        <v>69</v>
-      </c>
-      <c r="C79" t="s">
-        <v>66</v>
-      </c>
-      <c r="D79">
-        <v>2</v>
-      </c>
-      <c r="E79">
-        <v>3</v>
-      </c>
-      <c r="F79">
-        <v>4</v>
-      </c>
-      <c r="I79">
-        <v>9</v>
-      </c>
-      <c r="J79">
-        <v>4</v>
       </c>
     </row>
     <row r="80" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B80" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="C80" t="s">
         <v>66</v>
       </c>
       <c r="D80">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F80">
         <v>3</v>
@@ -3466,50 +3547,50 @@
         <v>7</v>
       </c>
       <c r="J80">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B81" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C81" t="s">
         <v>66</v>
       </c>
       <c r="D81">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E81">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F81">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I81">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J81">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B82" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C82" t="s">
         <v>66</v>
       </c>
       <c r="D82">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E82">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F82">
         <v>5</v>
       </c>
       <c r="I82">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J82">
         <v>27</v>
@@ -3517,24 +3598,116 @@
     </row>
     <row r="83" spans="2:10" x14ac:dyDescent="0.55000000000000004">
       <c r="B83" t="s">
+        <v>69</v>
+      </c>
+      <c r="C83" t="s">
+        <v>66</v>
+      </c>
+      <c r="D83">
+        <v>2</v>
+      </c>
+      <c r="E83">
+        <v>3</v>
+      </c>
+      <c r="F83">
+        <v>4</v>
+      </c>
+      <c r="I83">
+        <v>9</v>
+      </c>
+      <c r="J83">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B84" t="s">
+        <v>58</v>
+      </c>
+      <c r="C84" t="s">
+        <v>66</v>
+      </c>
+      <c r="D84">
+        <v>7</v>
+      </c>
+      <c r="E84">
+        <v>3</v>
+      </c>
+      <c r="F84">
+        <v>3</v>
+      </c>
+      <c r="I84">
+        <v>7</v>
+      </c>
+      <c r="J84">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B85" t="s">
+        <v>61</v>
+      </c>
+      <c r="C85" t="s">
+        <v>66</v>
+      </c>
+      <c r="D85">
+        <v>6</v>
+      </c>
+      <c r="E85">
+        <v>1</v>
+      </c>
+      <c r="F85">
+        <v>3</v>
+      </c>
+      <c r="I85">
+        <v>6</v>
+      </c>
+      <c r="J85">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B86" t="s">
+        <v>77</v>
+      </c>
+      <c r="C86" t="s">
+        <v>66</v>
+      </c>
+      <c r="D86">
+        <v>36</v>
+      </c>
+      <c r="E86">
+        <v>17</v>
+      </c>
+      <c r="F86">
+        <v>5</v>
+      </c>
+      <c r="I86">
+        <v>24</v>
+      </c>
+      <c r="J86">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="87" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B87" t="s">
         <v>83</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C87" t="s">
         <v>84</v>
       </c>
-      <c r="D83">
-        <v>6</v>
-      </c>
-      <c r="E83">
-        <v>3</v>
-      </c>
-      <c r="F83">
-        <v>3</v>
-      </c>
-      <c r="I83">
-        <v>4</v>
-      </c>
-      <c r="J83">
+      <c r="D87">
+        <v>6</v>
+      </c>
+      <c r="E87">
+        <v>3</v>
+      </c>
+      <c r="F87">
+        <v>3</v>
+      </c>
+      <c r="I87">
+        <v>4</v>
+      </c>
+      <c r="J87">
         <v>4</v>
       </c>
     </row>

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhmgo\Desktop\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D2BA221-8A5C-45E7-90D6-B17281CC1A94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50E7059D-02FD-46E5-9925-0659A5C48B5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{B57D1550-4E85-435D-BD6F-1B13E635EA51}"/>
+    <workbookView xWindow="4670" yWindow="5330" windowWidth="20900" windowHeight="13040" xr2:uid="{B57D1550-4E85-435D-BD6F-1B13E635EA51}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -909,7 +909,7 @@
         <v>28</v>
       </c>
       <c r="K6">
-        <f t="shared" ref="K6:K39" si="0">SUM(D6:I6)</f>
+        <f t="shared" ref="K6:K38" si="0">SUM(D6:I6)</f>
         <v>69</v>
       </c>
     </row>
@@ -1980,13 +1980,13 @@
         <v>44</v>
       </c>
       <c r="D39" s="3">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E39" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F39" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G39" s="3">
         <v>3</v>
@@ -2002,7 +2002,7 @@
       </c>
       <c r="K39">
         <f>SUM(D39:J39)</f>
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -2828,13 +2828,13 @@
         <v>8</v>
       </c>
       <c r="H61" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I61" s="3">
         <v>6</v>
       </c>
       <c r="J61" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K61" s="3">
         <v>5</v>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="N61">
         <f t="shared" si="1"/>
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="62" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -3083,13 +3083,13 @@
         <v>8</v>
       </c>
       <c r="I67" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J67" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K67" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L67" s="3">
         <v>7</v>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="N67">
         <f t="shared" si="1"/>
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="68" spans="2:14" x14ac:dyDescent="0.55000000000000004">

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhmgo\Desktop\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50E7059D-02FD-46E5-9925-0659A5C48B5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CA39FB2-C49C-4B0A-A3D6-486529B291D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4670" yWindow="5330" windowWidth="20900" windowHeight="13040" xr2:uid="{B57D1550-4E85-435D-BD6F-1B13E635EA51}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{B57D1550-4E85-435D-BD6F-1B13E635EA51}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1980,13 +1980,13 @@
         <v>44</v>
       </c>
       <c r="D39" s="3">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="E39" s="3">
         <v>22</v>
       </c>
       <c r="F39" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G39" s="3">
         <v>3</v>
@@ -2002,7 +2002,7 @@
       </c>
       <c r="K39">
         <f>SUM(D39:J39)</f>
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.55000000000000004">

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhmgo\Desktop\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CA39FB2-C49C-4B0A-A3D6-486529B291D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45173010-6728-41BB-89A4-B8A23FA505D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{B57D1550-4E85-435D-BD6F-1B13E635EA51}"/>
+    <workbookView xWindow="4670" yWindow="5330" windowWidth="20900" windowHeight="13040" xr2:uid="{B57D1550-4E85-435D-BD6F-1B13E635EA51}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3071,16 +3071,16 @@
         <v>145</v>
       </c>
       <c r="E67" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F67" s="3">
         <v>3</v>
       </c>
       <c r="G67" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H67" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I67" s="3">
         <v>5</v>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="N67">
         <f t="shared" si="1"/>
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="68" spans="2:14" x14ac:dyDescent="0.55000000000000004">

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhmgo\Desktop\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45173010-6728-41BB-89A4-B8A23FA505D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49FA3DC2-8EF6-4C85-8898-6B5C941CA1A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4670" yWindow="5330" windowWidth="20900" windowHeight="13040" xr2:uid="{B57D1550-4E85-435D-BD6F-1B13E635EA51}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{B57D1550-4E85-435D-BD6F-1B13E635EA51}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="108">
   <si>
     <t>野手・打者</t>
   </si>
@@ -422,6 +422,18 @@
   </si>
   <si>
     <t>ヘンダーソン</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>s</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ウィーラー</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>バルデス</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -804,7 +816,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C402B4-0E60-4338-B3CD-2DB7A1A076E1}">
-  <dimension ref="B2:AA87"/>
+  <dimension ref="B2:AA90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="14.75" customWidth="1"/>
@@ -2117,7 +2129,7 @@
         <v>7</v>
       </c>
       <c r="I44" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J44" s="3">
         <v>7</v>
@@ -2132,8 +2144,8 @@
         <v>8</v>
       </c>
       <c r="N44">
-        <f t="shared" ref="N44:N76" si="1">SUM(E44:L44)</f>
-        <v>53</v>
+        <f t="shared" ref="N44:N78" si="1">SUM(E44:L44)</f>
+        <v>54</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -3077,19 +3089,19 @@
         <v>3</v>
       </c>
       <c r="G67" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H67" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I67" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J67" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K67" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L67" s="3">
         <v>7</v>
@@ -3099,7 +3111,7 @@
       </c>
       <c r="N67">
         <f t="shared" si="1"/>
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="68" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -3481,234 +3493,309 @@
       </c>
     </row>
     <row r="77" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B77" s="3"/>
-      <c r="C77" s="3"/>
-      <c r="D77" s="3"/>
-      <c r="E77" s="3"/>
-      <c r="F77" s="3"/>
-      <c r="G77" s="3"/>
-      <c r="H77" s="3"/>
-      <c r="I77" s="3"/>
-      <c r="J77" s="3"/>
-      <c r="K77" s="3"/>
-      <c r="L77" s="3"/>
-      <c r="M77" s="3"/>
+      <c r="B77" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D77" s="3">
+        <v>159</v>
+      </c>
+      <c r="E77" s="3">
+        <v>8</v>
+      </c>
+      <c r="F77" s="3">
+        <v>8</v>
+      </c>
+      <c r="G77" s="3">
+        <v>5</v>
+      </c>
+      <c r="H77" s="3">
+        <v>6</v>
+      </c>
+      <c r="I77" s="3">
+        <v>6</v>
+      </c>
+      <c r="J77" s="3">
+        <v>8</v>
+      </c>
+      <c r="K77" s="3">
+        <v>5</v>
+      </c>
+      <c r="L77" s="3">
+        <v>7</v>
+      </c>
+      <c r="M77" s="3">
+        <v>7</v>
+      </c>
+      <c r="N77">
+        <f t="shared" si="1"/>
+        <v>53</v>
+      </c>
     </row>
     <row r="78" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B78" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D78" s="3">
+        <v>158</v>
+      </c>
+      <c r="E78" s="3">
+        <v>9</v>
+      </c>
+      <c r="F78" s="3">
+        <v>7</v>
+      </c>
+      <c r="G78" s="3">
+        <v>7</v>
+      </c>
+      <c r="H78" s="3">
+        <v>6</v>
+      </c>
+      <c r="I78" s="3">
+        <v>5</v>
+      </c>
+      <c r="J78" s="3">
+        <v>7</v>
+      </c>
+      <c r="K78" s="3">
+        <v>4</v>
+      </c>
+      <c r="L78" s="3">
+        <v>7</v>
+      </c>
+      <c r="M78" s="3">
+        <v>7</v>
+      </c>
+      <c r="N78">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B79" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B79" s="2" t="s">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B80" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C79" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G79" s="2"/>
-      <c r="H79" s="2"/>
-      <c r="I79" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J79" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K79" s="2" t="s">
+      <c r="C80" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G80" s="2"/>
+      <c r="H80" s="2"/>
+      <c r="I80" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K80" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B80" t="s">
+    <row r="81" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="B81" t="s">
         <v>70</v>
-      </c>
-      <c r="C80" t="s">
-        <v>66</v>
-      </c>
-      <c r="D80">
-        <v>8</v>
-      </c>
-      <c r="E80">
-        <v>2</v>
-      </c>
-      <c r="F80">
-        <v>3</v>
-      </c>
-      <c r="I80">
-        <v>7</v>
-      </c>
-      <c r="J80">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="B81" t="s">
-        <v>67</v>
       </c>
       <c r="C81" t="s">
         <v>66</v>
       </c>
       <c r="D81">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E81">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F81">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I81">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J81">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B82" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C82" t="s">
         <v>66</v>
       </c>
       <c r="D82">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="E82">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F82">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I82">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="J82">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B83" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C83" t="s">
         <v>66</v>
       </c>
       <c r="D83">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="E83">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F83">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I83">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="J83">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="84" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B84" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="C84" t="s">
         <v>66</v>
       </c>
       <c r="D84">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E84">
         <v>3</v>
       </c>
       <c r="F84">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I84">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J84">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B85" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C85" t="s">
         <v>66</v>
       </c>
       <c r="D85">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E85">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F85">
         <v>3</v>
       </c>
       <c r="I85">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J85">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B86" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="C86" t="s">
         <v>66</v>
       </c>
       <c r="D86">
+        <v>6</v>
+      </c>
+      <c r="E86">
+        <v>1</v>
+      </c>
+      <c r="F86">
+        <v>3</v>
+      </c>
+      <c r="I86">
+        <v>7</v>
+      </c>
+      <c r="J86">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="B87" t="s">
+        <v>77</v>
+      </c>
+      <c r="C87" t="s">
+        <v>66</v>
+      </c>
+      <c r="D87">
         <v>36</v>
       </c>
-      <c r="E86">
+      <c r="E87">
         <v>17</v>
       </c>
-      <c r="F86">
-        <v>5</v>
-      </c>
-      <c r="I86">
+      <c r="F87">
+        <v>5</v>
+      </c>
+      <c r="I87">
         <v>24</v>
       </c>
-      <c r="J86">
+      <c r="J87">
         <v>29</v>
       </c>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.55000000000000004">
-      <c r="B87" t="s">
+    <row r="88" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="B88" t="s">
         <v>83</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C88" t="s">
         <v>84</v>
       </c>
-      <c r="D87">
-        <v>6</v>
-      </c>
-      <c r="E87">
-        <v>3</v>
-      </c>
-      <c r="F87">
-        <v>3</v>
-      </c>
-      <c r="I87">
-        <v>4</v>
-      </c>
-      <c r="J87">
-        <v>4</v>
+      <c r="D88">
+        <v>6</v>
+      </c>
+      <c r="E88">
+        <v>3</v>
+      </c>
+      <c r="F88">
+        <v>3</v>
+      </c>
+      <c r="I88">
+        <v>6</v>
+      </c>
+      <c r="J88">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="K90" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhmgo\Desktop\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49FA3DC2-8EF6-4C85-8898-6B5C941CA1A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C63BA2E9-33BE-476F-969E-4EF246BC695E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{B57D1550-4E85-435D-BD6F-1B13E635EA51}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="109">
   <si>
     <t>野手・打者</t>
   </si>
@@ -425,15 +425,19 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>s</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ウィーラー</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>バルデス</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ワカツキ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ヨシダ</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -816,7 +820,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C402B4-0E60-4338-B3CD-2DB7A1A076E1}">
-  <dimension ref="B2:AA90"/>
+  <dimension ref="B2:N90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="14.75" customWidth="1"/>
@@ -1255,7 +1259,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="2:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B17" s="3" t="s">
         <v>46</v>
       </c>
@@ -1288,7 +1292,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="2:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B18" s="3" t="s">
         <v>47</v>
       </c>
@@ -1321,7 +1325,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="2:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B19" s="3" t="s">
         <v>48</v>
       </c>
@@ -1353,11 +1357,8 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="AA19" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="20" spans="2:27" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B20" s="3" t="s">
         <v>49</v>
       </c>
@@ -1390,7 +1391,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="21" spans="2:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B21" s="3" t="s">
         <v>55</v>
       </c>
@@ -1423,7 +1424,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="2:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B22" s="3" t="s">
         <v>61</v>
       </c>
@@ -1456,7 +1457,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="2:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B23" s="3" t="s">
         <v>59</v>
       </c>
@@ -1489,7 +1490,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="24" spans="2:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B24" s="3" t="s">
         <v>62</v>
       </c>
@@ -1522,7 +1523,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="2:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B25" s="3" t="s">
         <v>63</v>
       </c>
@@ -1555,7 +1556,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="26" spans="2:27" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="2:11" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B26" s="3" t="s">
         <v>90</v>
       </c>
@@ -1588,7 +1589,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="2:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B27" s="3" t="s">
         <v>78</v>
       </c>
@@ -1621,7 +1622,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="28" spans="2:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B28" s="3" t="s">
         <v>80</v>
       </c>
@@ -1654,7 +1655,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="2:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B29" s="3" t="s">
         <v>81</v>
       </c>
@@ -1687,7 +1688,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="2:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B30" s="3" t="s">
         <v>82</v>
       </c>
@@ -1720,7 +1721,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="2:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B31" s="3" t="s">
         <v>74</v>
       </c>
@@ -1753,7 +1754,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="32" spans="2:27" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B32" s="3" t="s">
         <v>85</v>
       </c>
@@ -2018,1784 +2019,1835 @@
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B40" s="1" t="s">
+      <c r="B40" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D40" s="3">
+        <v>3</v>
+      </c>
+      <c r="E40" s="3">
+        <v>7</v>
+      </c>
+      <c r="F40" s="3">
+        <v>4</v>
+      </c>
+      <c r="G40" s="3">
+        <v>1</v>
+      </c>
+      <c r="H40" s="3">
+        <v>3</v>
+      </c>
+      <c r="I40" s="3">
+        <v>4</v>
+      </c>
+      <c r="J40" s="3">
+        <v>4</v>
+      </c>
+      <c r="K40">
+        <f>SUM(D40:J40)</f>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B41" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J40" s="3"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B42" s="2" t="s">
+      <c r="J41" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B43" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C43" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="D43" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E42" s="2" t="s">
+      <c r="E43" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F42" s="2" t="s">
+      <c r="F43" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G42" s="2" t="s">
+      <c r="G43" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H42" s="2" t="s">
+      <c r="H43" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I42" s="2" t="s">
+      <c r="I43" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="J42" s="2" t="s">
+      <c r="J43" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="K42" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="L42" s="2" t="s">
+      <c r="K43" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L43" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M42" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N42" s="2" t="s">
+      <c r="M43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N43" s="2" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B43" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D43" s="3">
-        <v>165</v>
-      </c>
-      <c r="E43" s="3">
-        <v>9</v>
-      </c>
-      <c r="F43" s="3">
-        <v>5</v>
-      </c>
-      <c r="G43" s="3">
-        <v>8</v>
-      </c>
-      <c r="H43" s="3">
-        <v>8</v>
-      </c>
-      <c r="I43" s="3">
-        <v>6</v>
-      </c>
-      <c r="J43" s="3">
-        <v>8</v>
-      </c>
-      <c r="K43" s="3">
-        <v>7</v>
-      </c>
-      <c r="L43" s="3">
-        <v>6</v>
-      </c>
-      <c r="M43" s="3">
-        <v>9</v>
-      </c>
-      <c r="N43">
-        <f>SUM(E43:L43)</f>
-        <v>57</v>
       </c>
     </row>
     <row r="44" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B44" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D44" s="3">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="E44" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F44" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G44" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H44" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I44" s="3">
+        <v>6</v>
+      </c>
+      <c r="J44" s="3">
+        <v>8</v>
+      </c>
+      <c r="K44" s="3">
+        <v>7</v>
+      </c>
+      <c r="L44" s="3">
+        <v>6</v>
+      </c>
+      <c r="M44" s="3">
         <v>9</v>
       </c>
-      <c r="J44" s="3">
-        <v>7</v>
-      </c>
-      <c r="K44" s="3">
-        <v>6</v>
-      </c>
-      <c r="L44" s="3">
-        <v>7</v>
-      </c>
-      <c r="M44" s="3">
-        <v>8</v>
-      </c>
       <c r="N44">
-        <f t="shared" ref="N44:N78" si="1">SUM(E44:L44)</f>
-        <v>54</v>
+        <f>SUM(E44:L44)</f>
+        <v>57</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D45" s="3">
+        <v>157</v>
+      </c>
+      <c r="E45" s="3">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3">
+        <v>3</v>
+      </c>
+      <c r="G45" s="3">
+        <v>7</v>
+      </c>
+      <c r="H45" s="3">
+        <v>7</v>
+      </c>
+      <c r="I45" s="3">
+        <v>9</v>
+      </c>
+      <c r="J45" s="3">
+        <v>7</v>
+      </c>
+      <c r="K45" s="3">
+        <v>6</v>
+      </c>
+      <c r="L45" s="3">
+        <v>7</v>
+      </c>
+      <c r="M45" s="3">
+        <v>8</v>
+      </c>
+      <c r="N45">
+        <f t="shared" ref="N45:N79" si="1">SUM(E45:L45)</f>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B46" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D46" s="3">
         <v>155</v>
       </c>
-      <c r="E45" s="3">
-        <v>5</v>
-      </c>
-      <c r="F45" s="3">
-        <v>2</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="E46" s="3">
+        <v>5</v>
+      </c>
+      <c r="F46" s="3">
+        <v>2</v>
+      </c>
+      <c r="G46" s="3">
         <v>10</v>
       </c>
-      <c r="H45" s="3">
-        <v>6</v>
-      </c>
-      <c r="I45" s="3">
-        <v>6</v>
-      </c>
-      <c r="J45" s="3">
-        <v>6</v>
-      </c>
-      <c r="K45" s="3">
-        <v>5</v>
-      </c>
-      <c r="L45" s="3">
-        <v>7</v>
-      </c>
-      <c r="M45" s="3">
-        <v>6</v>
-      </c>
-      <c r="N45">
+      <c r="H46" s="3">
+        <v>6</v>
+      </c>
+      <c r="I46" s="3">
+        <v>6</v>
+      </c>
+      <c r="J46" s="3">
+        <v>6</v>
+      </c>
+      <c r="K46" s="3">
+        <v>5</v>
+      </c>
+      <c r="L46" s="3">
+        <v>7</v>
+      </c>
+      <c r="M46" s="3">
+        <v>6</v>
+      </c>
+      <c r="N46">
         <f t="shared" si="1"/>
         <v>47</v>
       </c>
     </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B46" s="3" t="s">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B47" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C47" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D47" s="3">
         <v>148</v>
       </c>
-      <c r="E46" s="3">
-        <v>4</v>
-      </c>
-      <c r="F46" s="3">
+      <c r="E47" s="3">
+        <v>4</v>
+      </c>
+      <c r="F47" s="3">
         <v>10</v>
       </c>
-      <c r="G46" s="3">
-        <v>6</v>
-      </c>
-      <c r="H46" s="3">
-        <v>4</v>
-      </c>
-      <c r="I46" s="3">
-        <v>8</v>
-      </c>
-      <c r="J46" s="3">
-        <v>5</v>
-      </c>
-      <c r="K46" s="3">
-        <v>4</v>
-      </c>
-      <c r="L46" s="3">
-        <v>5</v>
-      </c>
-      <c r="M46" s="3">
-        <v>6</v>
-      </c>
-      <c r="N46">
+      <c r="G47" s="3">
+        <v>6</v>
+      </c>
+      <c r="H47" s="3">
+        <v>4</v>
+      </c>
+      <c r="I47" s="3">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3">
+        <v>5</v>
+      </c>
+      <c r="K47" s="3">
+        <v>4</v>
+      </c>
+      <c r="L47" s="3">
+        <v>5</v>
+      </c>
+      <c r="M47" s="3">
+        <v>6</v>
+      </c>
+      <c r="N47">
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B47" s="3" t="s">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B48" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C48" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D48" s="3">
         <v>220</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E48" s="3">
         <v>1</v>
       </c>
-      <c r="F47" s="3">
+      <c r="F48" s="3">
         <v>1</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G48" s="3">
         <v>9</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H48" s="3">
         <v>1</v>
       </c>
-      <c r="I47" s="3">
-        <v>3</v>
-      </c>
-      <c r="J47" s="3">
-        <v>6</v>
-      </c>
-      <c r="K47" s="3">
-        <v>4</v>
-      </c>
-      <c r="L47" s="3">
-        <v>6</v>
-      </c>
-      <c r="M47" s="3">
-        <v>5</v>
-      </c>
-      <c r="N47">
+      <c r="I48" s="3">
+        <v>3</v>
+      </c>
+      <c r="J48" s="3">
+        <v>6</v>
+      </c>
+      <c r="K48" s="3">
+        <v>4</v>
+      </c>
+      <c r="L48" s="3">
+        <v>6</v>
+      </c>
+      <c r="M48" s="3">
+        <v>5</v>
+      </c>
+      <c r="N48">
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B48" s="3" t="s">
+    <row r="49" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B49" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C49" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D49" s="3">
         <v>100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E49" s="3">
         <v>9</v>
       </c>
-      <c r="F48" s="3">
+      <c r="F49" s="3">
         <v>9</v>
       </c>
-      <c r="G48" s="3">
+      <c r="G49" s="3">
         <v>9</v>
       </c>
-      <c r="H48" s="3">
+      <c r="H49" s="3">
         <v>9</v>
       </c>
-      <c r="I48" s="3">
+      <c r="I49" s="3">
         <v>9</v>
       </c>
-      <c r="J48" s="3">
-        <v>6</v>
-      </c>
-      <c r="K48" s="3">
-        <v>8</v>
-      </c>
-      <c r="L48" s="3">
-        <v>4</v>
-      </c>
-      <c r="M48" s="3">
-        <v>5</v>
-      </c>
-      <c r="N48">
+      <c r="J49" s="3">
+        <v>6</v>
+      </c>
+      <c r="K49" s="3">
+        <v>8</v>
+      </c>
+      <c r="L49" s="3">
+        <v>4</v>
+      </c>
+      <c r="M49" s="3">
+        <v>5</v>
+      </c>
+      <c r="N49">
         <f t="shared" si="1"/>
         <v>63</v>
       </c>
     </row>
-    <row r="49" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B49" s="3" t="s">
+    <row r="50" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B50" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C50" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D50" s="3">
         <v>149</v>
       </c>
-      <c r="E49" s="3">
-        <v>3</v>
-      </c>
-      <c r="F49" s="3">
-        <v>6</v>
-      </c>
-      <c r="G49" s="3">
-        <v>5</v>
-      </c>
-      <c r="H49" s="3">
+      <c r="E50" s="3">
+        <v>3</v>
+      </c>
+      <c r="F50" s="3">
+        <v>6</v>
+      </c>
+      <c r="G50" s="3">
+        <v>5</v>
+      </c>
+      <c r="H50" s="3">
         <v>10</v>
       </c>
-      <c r="I49" s="3">
-        <v>5</v>
-      </c>
-      <c r="J49" s="3">
-        <v>8</v>
-      </c>
-      <c r="K49" s="3">
-        <v>5</v>
-      </c>
-      <c r="L49" s="3">
-        <v>6</v>
-      </c>
-      <c r="M49" s="3">
-        <v>6</v>
-      </c>
-      <c r="N49">
+      <c r="I50" s="3">
+        <v>5</v>
+      </c>
+      <c r="J50" s="3">
+        <v>8</v>
+      </c>
+      <c r="K50" s="3">
+        <v>5</v>
+      </c>
+      <c r="L50" s="3">
+        <v>6</v>
+      </c>
+      <c r="M50" s="3">
+        <v>6</v>
+      </c>
+      <c r="N50">
         <f t="shared" si="1"/>
         <v>48</v>
       </c>
     </row>
-    <row r="50" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B50" s="3" t="s">
+    <row r="51" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B51" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C51" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D50" s="3">
+      <c r="D51" s="3">
         <v>158</v>
       </c>
-      <c r="E50" s="3">
+      <c r="E51" s="3">
         <v>9</v>
       </c>
-      <c r="F50" s="3">
-        <v>8</v>
-      </c>
-      <c r="G50" s="3">
-        <v>6</v>
-      </c>
-      <c r="H50" s="3">
-        <v>5</v>
-      </c>
-      <c r="I50" s="3">
-        <v>7</v>
-      </c>
-      <c r="J50" s="3">
-        <v>4</v>
-      </c>
-      <c r="K50" s="3">
-        <v>5</v>
-      </c>
-      <c r="L50" s="3">
-        <v>5</v>
-      </c>
-      <c r="M50" s="3">
-        <v>6</v>
-      </c>
-      <c r="N50">
+      <c r="F51" s="3">
+        <v>8</v>
+      </c>
+      <c r="G51" s="3">
+        <v>6</v>
+      </c>
+      <c r="H51" s="3">
+        <v>5</v>
+      </c>
+      <c r="I51" s="3">
+        <v>7</v>
+      </c>
+      <c r="J51" s="3">
+        <v>4</v>
+      </c>
+      <c r="K51" s="3">
+        <v>5</v>
+      </c>
+      <c r="L51" s="3">
+        <v>5</v>
+      </c>
+      <c r="M51" s="3">
+        <v>6</v>
+      </c>
+      <c r="N51">
         <f t="shared" si="1"/>
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B51" s="3" t="s">
+    <row r="52" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B52" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C52" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D51" s="3">
+      <c r="D52" s="3">
         <v>172</v>
       </c>
-      <c r="E51" s="3">
+      <c r="E52" s="3">
         <v>27</v>
       </c>
-      <c r="F51" s="3">
+      <c r="F52" s="3">
         <v>26</v>
       </c>
-      <c r="G51" s="3">
+      <c r="G52" s="3">
         <v>24</v>
       </c>
-      <c r="H51" s="3">
+      <c r="H52" s="3">
         <v>27</v>
       </c>
-      <c r="I51" s="3">
+      <c r="I52" s="3">
         <v>25</v>
       </c>
-      <c r="J51" s="3">
+      <c r="J52" s="3">
         <v>32</v>
       </c>
-      <c r="K51" s="3">
+      <c r="K52" s="3">
         <v>24</v>
       </c>
-      <c r="L51" s="3">
+      <c r="L52" s="3">
         <v>21</v>
       </c>
-      <c r="M51" s="3">
+      <c r="M52" s="3">
         <v>30</v>
       </c>
-      <c r="N51">
+      <c r="N52">
         <f t="shared" si="1"/>
         <v>206</v>
       </c>
     </row>
-    <row r="52" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B52" s="3" t="s">
+    <row r="53" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B53" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C53" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D53" s="3">
         <v>171</v>
       </c>
-      <c r="E52" s="3">
-        <v>8</v>
-      </c>
-      <c r="F52" s="3">
-        <v>6</v>
-      </c>
-      <c r="G52" s="3">
-        <v>8</v>
-      </c>
-      <c r="H52" s="3">
-        <v>3</v>
-      </c>
-      <c r="I52" s="3">
-        <v>6</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="E53" s="3">
+        <v>8</v>
+      </c>
+      <c r="F53" s="3">
+        <v>6</v>
+      </c>
+      <c r="G53" s="3">
+        <v>8</v>
+      </c>
+      <c r="H53" s="3">
+        <v>3</v>
+      </c>
+      <c r="I53" s="3">
+        <v>6</v>
+      </c>
+      <c r="J53" s="3">
         <v>14</v>
       </c>
-      <c r="K52" s="3">
-        <v>6</v>
-      </c>
-      <c r="L52" s="3">
-        <v>3</v>
-      </c>
-      <c r="M52" s="3">
-        <v>4</v>
-      </c>
-      <c r="N52">
+      <c r="K53" s="3">
+        <v>6</v>
+      </c>
+      <c r="L53" s="3">
+        <v>3</v>
+      </c>
+      <c r="M53" s="3">
+        <v>4</v>
+      </c>
+      <c r="N53">
         <f t="shared" si="1"/>
         <v>54</v>
       </c>
     </row>
-    <row r="53" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B53" s="3" t="s">
+    <row r="54" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B54" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C54" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D53" s="3">
+      <c r="D54" s="3">
         <v>143</v>
       </c>
-      <c r="E53" s="3">
-        <v>4</v>
-      </c>
-      <c r="F53" s="3">
-        <v>4</v>
-      </c>
-      <c r="G53" s="3">
-        <v>5</v>
-      </c>
-      <c r="H53" s="3">
-        <v>5</v>
-      </c>
-      <c r="I53" s="3">
+      <c r="E54" s="3">
+        <v>4</v>
+      </c>
+      <c r="F54" s="3">
+        <v>4</v>
+      </c>
+      <c r="G54" s="3">
+        <v>5</v>
+      </c>
+      <c r="H54" s="3">
+        <v>5</v>
+      </c>
+      <c r="I54" s="3">
         <v>10</v>
       </c>
-      <c r="J53" s="3">
-        <v>7</v>
-      </c>
-      <c r="K53" s="3">
-        <v>8</v>
-      </c>
-      <c r="L53" s="3">
-        <v>6</v>
-      </c>
-      <c r="M53" s="3">
-        <v>6</v>
-      </c>
-      <c r="N53">
+      <c r="J54" s="3">
+        <v>7</v>
+      </c>
+      <c r="K54" s="3">
+        <v>8</v>
+      </c>
+      <c r="L54" s="3">
+        <v>6</v>
+      </c>
+      <c r="M54" s="3">
+        <v>6</v>
+      </c>
+      <c r="N54">
         <f t="shared" si="1"/>
         <v>49</v>
       </c>
     </row>
-    <row r="54" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B54" s="3" t="s">
+    <row r="55" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B55" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C55" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D55" s="3">
         <v>169</v>
       </c>
-      <c r="E54" s="3">
-        <v>7</v>
-      </c>
-      <c r="F54" s="3">
-        <v>4</v>
-      </c>
-      <c r="G54" s="3">
-        <v>5</v>
-      </c>
-      <c r="H54" s="3">
+      <c r="E55" s="3">
+        <v>7</v>
+      </c>
+      <c r="F55" s="3">
+        <v>4</v>
+      </c>
+      <c r="G55" s="3">
+        <v>5</v>
+      </c>
+      <c r="H55" s="3">
         <v>9</v>
       </c>
-      <c r="I54" s="3">
-        <v>5</v>
-      </c>
-      <c r="J54" s="3">
+      <c r="I55" s="3">
+        <v>5</v>
+      </c>
+      <c r="J55" s="3">
         <v>9</v>
       </c>
-      <c r="K54" s="3">
-        <v>4</v>
-      </c>
-      <c r="L54" s="3">
-        <v>7</v>
-      </c>
-      <c r="M54" s="3">
-        <v>8</v>
-      </c>
-      <c r="N54">
+      <c r="K55" s="3">
+        <v>4</v>
+      </c>
+      <c r="L55" s="3">
+        <v>7</v>
+      </c>
+      <c r="M55" s="3">
+        <v>8</v>
+      </c>
+      <c r="N55">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
     </row>
-    <row r="55" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B55" s="3" t="s">
+    <row r="56" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B56" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C56" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D55" s="3">
+      <c r="D56" s="3">
         <v>156</v>
       </c>
-      <c r="E55" s="3">
-        <v>2</v>
-      </c>
-      <c r="F55" s="3">
+      <c r="E56" s="3">
+        <v>2</v>
+      </c>
+      <c r="F56" s="3">
         <v>10</v>
       </c>
-      <c r="G55" s="3">
-        <v>2</v>
-      </c>
-      <c r="H55" s="3">
-        <v>2</v>
-      </c>
-      <c r="I55" s="3">
-        <v>5</v>
-      </c>
-      <c r="J55" s="3">
-        <v>2</v>
-      </c>
-      <c r="K55" s="3">
-        <v>5</v>
-      </c>
-      <c r="L55" s="3">
-        <v>2</v>
-      </c>
-      <c r="M55" s="3">
+      <c r="G56" s="3">
+        <v>2</v>
+      </c>
+      <c r="H56" s="3">
+        <v>2</v>
+      </c>
+      <c r="I56" s="3">
+        <v>5</v>
+      </c>
+      <c r="J56" s="3">
+        <v>2</v>
+      </c>
+      <c r="K56" s="3">
+        <v>5</v>
+      </c>
+      <c r="L56" s="3">
+        <v>2</v>
+      </c>
+      <c r="M56" s="3">
         <v>1</v>
       </c>
-      <c r="N55">
+      <c r="N56">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
     </row>
-    <row r="56" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B56" s="3" t="s">
+    <row r="57" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B57" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C57" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D56" s="3">
+      <c r="D57" s="3">
         <v>158</v>
       </c>
-      <c r="E56" s="3">
-        <v>2</v>
-      </c>
-      <c r="F56" s="3">
+      <c r="E57" s="3">
+        <v>2</v>
+      </c>
+      <c r="F57" s="3">
         <v>1</v>
       </c>
-      <c r="G56" s="3">
+      <c r="G57" s="3">
         <v>9</v>
       </c>
-      <c r="H56" s="3">
-        <v>7</v>
-      </c>
-      <c r="I56" s="3">
-        <v>3</v>
-      </c>
-      <c r="J56" s="3">
+      <c r="H57" s="3">
+        <v>7</v>
+      </c>
+      <c r="I57" s="3">
+        <v>3</v>
+      </c>
+      <c r="J57" s="3">
         <v>9</v>
       </c>
-      <c r="K56" s="3">
-        <v>3</v>
-      </c>
-      <c r="L56" s="3">
-        <v>2</v>
-      </c>
-      <c r="M56" s="3">
-        <v>3</v>
-      </c>
-      <c r="N56">
+      <c r="K57" s="3">
+        <v>3</v>
+      </c>
+      <c r="L57" s="3">
+        <v>2</v>
+      </c>
+      <c r="M57" s="3">
+        <v>3</v>
+      </c>
+      <c r="N57">
         <f t="shared" si="1"/>
         <v>36</v>
       </c>
     </row>
-    <row r="57" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B57" s="3" t="s">
+    <row r="58" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B58" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C58" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D58" s="3">
         <v>165</v>
       </c>
-      <c r="E57" s="3">
-        <v>5</v>
-      </c>
-      <c r="F57" s="3">
-        <v>2</v>
-      </c>
-      <c r="G57" s="3">
-        <v>6</v>
-      </c>
-      <c r="H57" s="3">
-        <v>4</v>
-      </c>
-      <c r="I57" s="3">
-        <v>4</v>
-      </c>
-      <c r="J57" s="3">
-        <v>7</v>
-      </c>
-      <c r="K57" s="3">
-        <v>4</v>
-      </c>
-      <c r="L57" s="3">
-        <v>5</v>
-      </c>
-      <c r="M57" s="3">
-        <v>6</v>
-      </c>
-      <c r="N57">
+      <c r="E58" s="3">
+        <v>5</v>
+      </c>
+      <c r="F58" s="3">
+        <v>2</v>
+      </c>
+      <c r="G58" s="3">
+        <v>6</v>
+      </c>
+      <c r="H58" s="3">
+        <v>4</v>
+      </c>
+      <c r="I58" s="3">
+        <v>4</v>
+      </c>
+      <c r="J58" s="3">
+        <v>7</v>
+      </c>
+      <c r="K58" s="3">
+        <v>4</v>
+      </c>
+      <c r="L58" s="3">
+        <v>5</v>
+      </c>
+      <c r="M58" s="3">
+        <v>6</v>
+      </c>
+      <c r="N58">
         <f t="shared" si="1"/>
         <v>37</v>
       </c>
     </row>
-    <row r="58" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B58" s="3" t="s">
+    <row r="59" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B59" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C59" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D59" s="3">
         <v>150</v>
       </c>
-      <c r="E58" s="3">
-        <v>2</v>
-      </c>
-      <c r="F58" s="3">
-        <v>5</v>
-      </c>
-      <c r="G58" s="3">
-        <v>5</v>
-      </c>
-      <c r="H58" s="3">
-        <v>5</v>
-      </c>
-      <c r="I58" s="3">
-        <v>5</v>
-      </c>
-      <c r="J58" s="3">
-        <v>5</v>
-      </c>
-      <c r="K58" s="3">
-        <v>5</v>
-      </c>
-      <c r="L58" s="3">
-        <v>2</v>
-      </c>
-      <c r="M58" s="3">
-        <v>3</v>
-      </c>
-      <c r="N58">
+      <c r="E59" s="3">
+        <v>2</v>
+      </c>
+      <c r="F59" s="3">
+        <v>5</v>
+      </c>
+      <c r="G59" s="3">
+        <v>5</v>
+      </c>
+      <c r="H59" s="3">
+        <v>5</v>
+      </c>
+      <c r="I59" s="3">
+        <v>5</v>
+      </c>
+      <c r="J59" s="3">
+        <v>5</v>
+      </c>
+      <c r="K59" s="3">
+        <v>5</v>
+      </c>
+      <c r="L59" s="3">
+        <v>2</v>
+      </c>
+      <c r="M59" s="3">
+        <v>3</v>
+      </c>
+      <c r="N59">
         <f t="shared" si="1"/>
         <v>34</v>
       </c>
     </row>
-    <row r="59" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B59" s="3" t="s">
+    <row r="60" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B60" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="C60" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D60" s="3">
         <v>125</v>
       </c>
-      <c r="E59" s="3">
-        <v>2</v>
-      </c>
-      <c r="F59" s="3">
-        <v>2</v>
-      </c>
-      <c r="G59" s="3">
-        <v>3</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="E60" s="3">
+        <v>2</v>
+      </c>
+      <c r="F60" s="3">
+        <v>2</v>
+      </c>
+      <c r="G60" s="3">
+        <v>3</v>
+      </c>
+      <c r="H60" s="3">
         <v>1</v>
       </c>
-      <c r="I59" s="3">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3">
-        <v>3</v>
-      </c>
-      <c r="K59" s="3">
-        <v>3</v>
-      </c>
-      <c r="L59" s="3">
-        <v>2</v>
-      </c>
-      <c r="M59" s="3">
-        <v>3</v>
-      </c>
-      <c r="N59">
+      <c r="I60" s="3">
+        <v>3</v>
+      </c>
+      <c r="J60" s="3">
+        <v>3</v>
+      </c>
+      <c r="K60" s="3">
+        <v>3</v>
+      </c>
+      <c r="L60" s="3">
+        <v>2</v>
+      </c>
+      <c r="M60" s="3">
+        <v>3</v>
+      </c>
+      <c r="N60">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
     </row>
-    <row r="60" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B60" s="3" t="s">
+    <row r="61" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B61" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="C61" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D61" s="3">
         <v>159</v>
       </c>
-      <c r="E60" s="3">
-        <v>7</v>
-      </c>
-      <c r="F60" s="3">
-        <v>3</v>
-      </c>
-      <c r="G60" s="3">
-        <v>5</v>
-      </c>
-      <c r="H60" s="3">
-        <v>5</v>
-      </c>
-      <c r="I60" s="3">
+      <c r="E61" s="3">
+        <v>7</v>
+      </c>
+      <c r="F61" s="3">
+        <v>3</v>
+      </c>
+      <c r="G61" s="3">
+        <v>5</v>
+      </c>
+      <c r="H61" s="3">
+        <v>5</v>
+      </c>
+      <c r="I61" s="3">
         <v>0</v>
       </c>
-      <c r="J60" s="3">
+      <c r="J61" s="3">
         <v>9</v>
       </c>
-      <c r="K60" s="3">
-        <v>3</v>
-      </c>
-      <c r="L60" s="3">
-        <v>6</v>
-      </c>
-      <c r="M60" s="3">
-        <v>5</v>
-      </c>
-      <c r="N60">
+      <c r="K61" s="3">
+        <v>3</v>
+      </c>
+      <c r="L61" s="3">
+        <v>6</v>
+      </c>
+      <c r="M61" s="3">
+        <v>5</v>
+      </c>
+      <c r="N61">
         <f t="shared" si="1"/>
         <v>38</v>
       </c>
     </row>
-    <row r="61" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B61" s="3" t="s">
+    <row r="62" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B62" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="C62" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D61" s="3">
+      <c r="D62" s="3">
         <v>164</v>
       </c>
-      <c r="E61" s="3">
-        <v>6</v>
-      </c>
-      <c r="F61" s="3">
-        <v>8</v>
-      </c>
-      <c r="G61" s="3">
-        <v>8</v>
-      </c>
-      <c r="H61" s="3">
-        <v>6</v>
-      </c>
-      <c r="I61" s="3">
-        <v>6</v>
-      </c>
-      <c r="J61" s="3">
-        <v>8</v>
-      </c>
-      <c r="K61" s="3">
-        <v>5</v>
-      </c>
-      <c r="L61" s="3">
-        <v>7</v>
-      </c>
-      <c r="M61" s="3">
-        <v>8</v>
-      </c>
-      <c r="N61">
+      <c r="E62" s="3">
+        <v>6</v>
+      </c>
+      <c r="F62" s="3">
+        <v>8</v>
+      </c>
+      <c r="G62" s="3">
+        <v>8</v>
+      </c>
+      <c r="H62" s="3">
+        <v>6</v>
+      </c>
+      <c r="I62" s="3">
+        <v>6</v>
+      </c>
+      <c r="J62" s="3">
+        <v>8</v>
+      </c>
+      <c r="K62" s="3">
+        <v>5</v>
+      </c>
+      <c r="L62" s="3">
+        <v>7</v>
+      </c>
+      <c r="M62" s="3">
+        <v>8</v>
+      </c>
+      <c r="N62">
         <f t="shared" si="1"/>
         <v>54</v>
       </c>
     </row>
-    <row r="62" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B62" s="3" t="s">
+    <row r="63" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B63" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="C63" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D63" s="3">
         <v>157</v>
       </c>
-      <c r="E62" s="3">
-        <v>3</v>
-      </c>
-      <c r="F62" s="3">
-        <v>5</v>
-      </c>
-      <c r="G62" s="3">
-        <v>3</v>
-      </c>
-      <c r="H62" s="3">
-        <v>3</v>
-      </c>
-      <c r="I62" s="3">
-        <v>3</v>
-      </c>
-      <c r="J62" s="3">
-        <v>4</v>
-      </c>
-      <c r="K62" s="3">
-        <v>5</v>
-      </c>
-      <c r="L62" s="3">
-        <v>4</v>
-      </c>
-      <c r="M62" s="3">
-        <v>3</v>
-      </c>
-      <c r="N62">
+      <c r="E63" s="3">
+        <v>3</v>
+      </c>
+      <c r="F63" s="3">
+        <v>5</v>
+      </c>
+      <c r="G63" s="3">
+        <v>3</v>
+      </c>
+      <c r="H63" s="3">
+        <v>3</v>
+      </c>
+      <c r="I63" s="3">
+        <v>3</v>
+      </c>
+      <c r="J63" s="3">
+        <v>4</v>
+      </c>
+      <c r="K63" s="3">
+        <v>5</v>
+      </c>
+      <c r="L63" s="3">
+        <v>4</v>
+      </c>
+      <c r="M63" s="3">
+        <v>3</v>
+      </c>
+      <c r="N63">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
     </row>
-    <row r="63" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B63" s="3" t="s">
+    <row r="64" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B64" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="C64" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D63" s="3">
+      <c r="D64" s="3">
         <v>155</v>
       </c>
-      <c r="E63" s="3">
-        <v>4</v>
-      </c>
-      <c r="F63" s="3">
-        <v>3</v>
-      </c>
-      <c r="G63" s="3">
-        <v>8</v>
-      </c>
-      <c r="H63" s="3">
-        <v>3</v>
-      </c>
-      <c r="I63" s="3">
+      <c r="E64" s="3">
+        <v>4</v>
+      </c>
+      <c r="F64" s="3">
+        <v>3</v>
+      </c>
+      <c r="G64" s="3">
+        <v>8</v>
+      </c>
+      <c r="H64" s="3">
+        <v>3</v>
+      </c>
+      <c r="I64" s="3">
         <v>9</v>
       </c>
-      <c r="J63" s="3">
-        <v>5</v>
-      </c>
-      <c r="K63" s="3">
-        <v>8</v>
-      </c>
-      <c r="L63" s="3">
-        <v>6</v>
-      </c>
-      <c r="M63" s="3">
-        <v>6</v>
-      </c>
-      <c r="N63">
+      <c r="J64" s="3">
+        <v>5</v>
+      </c>
+      <c r="K64" s="3">
+        <v>8</v>
+      </c>
+      <c r="L64" s="3">
+        <v>6</v>
+      </c>
+      <c r="M64" s="3">
+        <v>6</v>
+      </c>
+      <c r="N64">
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
     </row>
-    <row r="64" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B64" s="3" t="s">
+    <row r="65" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B65" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C64" s="3" t="s">
+      <c r="C65" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D64" s="3">
+      <c r="D65" s="3">
         <v>175</v>
       </c>
-      <c r="E64" s="3">
+      <c r="E65" s="3">
         <v>28</v>
       </c>
-      <c r="F64" s="3">
+      <c r="F65" s="3">
         <v>27</v>
       </c>
-      <c r="G64" s="3">
+      <c r="G65" s="3">
         <v>27</v>
       </c>
-      <c r="H64" s="3">
+      <c r="H65" s="3">
         <v>28</v>
       </c>
-      <c r="I64" s="3">
+      <c r="I65" s="3">
         <v>27</v>
       </c>
-      <c r="J64" s="3">
+      <c r="J65" s="3">
         <v>33</v>
       </c>
-      <c r="K64" s="3">
+      <c r="K65" s="3">
         <v>24</v>
       </c>
-      <c r="L64" s="3">
+      <c r="L65" s="3">
         <v>21</v>
       </c>
-      <c r="M64" s="3">
+      <c r="M65" s="3">
         <v>32</v>
       </c>
-      <c r="N64">
+      <c r="N65">
         <f t="shared" si="1"/>
         <v>215</v>
       </c>
     </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B65" s="3" t="s">
+    <row r="66" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B66" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C65" s="3" t="s">
+      <c r="C66" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D65" s="3">
+      <c r="D66" s="3">
         <v>155</v>
       </c>
-      <c r="E65" s="3">
+      <c r="E66" s="3">
         <v>32</v>
       </c>
-      <c r="F65" s="3">
+      <c r="F66" s="3">
         <v>30</v>
       </c>
-      <c r="G65" s="3">
+      <c r="G66" s="3">
         <v>29</v>
       </c>
-      <c r="H65" s="3">
+      <c r="H66" s="3">
         <v>28</v>
       </c>
-      <c r="I65" s="3">
+      <c r="I66" s="3">
         <v>29</v>
       </c>
-      <c r="J65" s="3">
+      <c r="J66" s="3">
         <v>32</v>
       </c>
-      <c r="K65" s="3">
+      <c r="K66" s="3">
         <v>23</v>
       </c>
-      <c r="L65" s="3">
+      <c r="L66" s="3">
         <v>20</v>
       </c>
-      <c r="M65" s="3">
+      <c r="M66" s="3">
         <v>32</v>
       </c>
-      <c r="N65">
+      <c r="N66">
         <f t="shared" si="1"/>
         <v>223</v>
       </c>
     </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B66" s="3" t="s">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B67" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="C67" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D67" s="3">
         <v>158</v>
       </c>
-      <c r="E66" s="3">
-        <v>7</v>
-      </c>
-      <c r="F66" s="3">
-        <v>3</v>
-      </c>
-      <c r="G66" s="3">
-        <v>3</v>
-      </c>
-      <c r="H66" s="3">
-        <v>3</v>
-      </c>
-      <c r="I66" s="3">
-        <v>4</v>
-      </c>
-      <c r="J66" s="3">
-        <v>6</v>
-      </c>
-      <c r="K66" s="3">
-        <v>5</v>
-      </c>
-      <c r="L66" s="3">
-        <v>2</v>
-      </c>
-      <c r="M66" s="3">
-        <v>3</v>
-      </c>
-      <c r="N66">
+      <c r="E67" s="3">
+        <v>7</v>
+      </c>
+      <c r="F67" s="3">
+        <v>3</v>
+      </c>
+      <c r="G67" s="3">
+        <v>3</v>
+      </c>
+      <c r="H67" s="3">
+        <v>3</v>
+      </c>
+      <c r="I67" s="3">
+        <v>4</v>
+      </c>
+      <c r="J67" s="3">
+        <v>6</v>
+      </c>
+      <c r="K67" s="3">
+        <v>5</v>
+      </c>
+      <c r="L67" s="3">
+        <v>2</v>
+      </c>
+      <c r="M67" s="3">
+        <v>3</v>
+      </c>
+      <c r="N67">
         <f t="shared" si="1"/>
         <v>33</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B67" s="3" t="s">
+    <row r="68" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B68" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="C68" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D67" s="3">
+      <c r="D68" s="3">
         <v>145</v>
       </c>
-      <c r="E67" s="3">
-        <v>7</v>
-      </c>
-      <c r="F67" s="3">
-        <v>3</v>
-      </c>
-      <c r="G67" s="3">
-        <v>8</v>
-      </c>
-      <c r="H67" s="3">
-        <v>8</v>
-      </c>
-      <c r="I67" s="3">
-        <v>8</v>
-      </c>
-      <c r="J67" s="3">
-        <v>8</v>
-      </c>
-      <c r="K67" s="3">
-        <v>6</v>
-      </c>
-      <c r="L67" s="3">
-        <v>7</v>
-      </c>
-      <c r="M67" s="3">
-        <v>6</v>
-      </c>
-      <c r="N67">
+      <c r="E68" s="3">
+        <v>7</v>
+      </c>
+      <c r="F68" s="3">
+        <v>3</v>
+      </c>
+      <c r="G68" s="3">
+        <v>8</v>
+      </c>
+      <c r="H68" s="3">
+        <v>8</v>
+      </c>
+      <c r="I68" s="3">
+        <v>8</v>
+      </c>
+      <c r="J68" s="3">
+        <v>8</v>
+      </c>
+      <c r="K68" s="3">
+        <v>6</v>
+      </c>
+      <c r="L68" s="3">
+        <v>7</v>
+      </c>
+      <c r="M68" s="3">
+        <v>6</v>
+      </c>
+      <c r="N68">
         <f t="shared" si="1"/>
         <v>55</v>
       </c>
     </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B68" s="3" t="s">
+    <row r="69" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B69" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="C69" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D68" s="3">
+      <c r="D69" s="3">
         <v>164</v>
       </c>
-      <c r="E68" s="3">
-        <v>8</v>
-      </c>
-      <c r="F68" s="3">
+      <c r="E69" s="3">
+        <v>8</v>
+      </c>
+      <c r="F69" s="3">
         <v>1</v>
       </c>
-      <c r="G68" s="3">
-        <v>4</v>
-      </c>
-      <c r="H68" s="3">
+      <c r="G69" s="3">
+        <v>4</v>
+      </c>
+      <c r="H69" s="3">
         <v>9</v>
       </c>
-      <c r="I68" s="3">
-        <v>6</v>
-      </c>
-      <c r="J68" s="3">
+      <c r="I69" s="3">
+        <v>6</v>
+      </c>
+      <c r="J69" s="3">
         <v>15</v>
       </c>
-      <c r="K68" s="3">
-        <v>6</v>
-      </c>
-      <c r="L68" s="3">
-        <v>3</v>
-      </c>
-      <c r="M68" s="3">
-        <v>4</v>
-      </c>
-      <c r="N68">
+      <c r="K69" s="3">
+        <v>6</v>
+      </c>
+      <c r="L69" s="3">
+        <v>3</v>
+      </c>
+      <c r="M69" s="3">
+        <v>4</v>
+      </c>
+      <c r="N69">
         <f t="shared" si="1"/>
         <v>52</v>
       </c>
     </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B69" s="3" t="s">
+    <row r="70" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B70" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="C70" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D69" s="3">
+      <c r="D70" s="3">
         <v>161</v>
       </c>
-      <c r="E69" s="3">
+      <c r="E70" s="3">
         <v>9</v>
       </c>
-      <c r="F69" s="3">
-        <v>7</v>
-      </c>
-      <c r="G69" s="3">
-        <v>3</v>
-      </c>
-      <c r="H69" s="3">
-        <v>6</v>
-      </c>
-      <c r="I69" s="3">
-        <v>4</v>
-      </c>
-      <c r="J69" s="3">
+      <c r="F70" s="3">
+        <v>7</v>
+      </c>
+      <c r="G70" s="3">
+        <v>3</v>
+      </c>
+      <c r="H70" s="3">
+        <v>6</v>
+      </c>
+      <c r="I70" s="3">
+        <v>4</v>
+      </c>
+      <c r="J70" s="3">
         <v>13</v>
       </c>
-      <c r="K69" s="3">
-        <v>5</v>
-      </c>
-      <c r="L69" s="3">
-        <v>3</v>
-      </c>
-      <c r="M69" s="3">
-        <v>4</v>
-      </c>
-      <c r="N69">
+      <c r="K70" s="3">
+        <v>5</v>
+      </c>
+      <c r="L70" s="3">
+        <v>3</v>
+      </c>
+      <c r="M70" s="3">
+        <v>4</v>
+      </c>
+      <c r="N70">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
     </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B70" s="3" t="s">
+    <row r="71" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B71" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="C71" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D70" s="3">
+      <c r="D71" s="3">
         <v>77</v>
       </c>
-      <c r="E70" s="3">
-        <v>3</v>
-      </c>
-      <c r="F70" s="3">
+      <c r="E71" s="3">
+        <v>3</v>
+      </c>
+      <c r="F71" s="3">
         <v>1</v>
       </c>
-      <c r="G70" s="3">
-        <v>3</v>
-      </c>
-      <c r="H70" s="3">
+      <c r="G71" s="3">
+        <v>3</v>
+      </c>
+      <c r="H71" s="3">
         <v>1</v>
       </c>
-      <c r="I70" s="3">
-        <v>6</v>
-      </c>
-      <c r="J70" s="3">
-        <v>2</v>
-      </c>
-      <c r="K70" s="3">
-        <v>3</v>
-      </c>
-      <c r="L70" s="3">
-        <v>2</v>
-      </c>
-      <c r="M70" s="3">
+      <c r="I71" s="3">
+        <v>6</v>
+      </c>
+      <c r="J71" s="3">
+        <v>2</v>
+      </c>
+      <c r="K71" s="3">
+        <v>3</v>
+      </c>
+      <c r="L71" s="3">
+        <v>2</v>
+      </c>
+      <c r="M71" s="3">
         <v>1</v>
       </c>
-      <c r="N70">
+      <c r="N71">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
     </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B71" s="3" t="s">
+    <row r="72" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B72" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="C72" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D71" s="3">
+      <c r="D72" s="3">
         <v>152</v>
       </c>
-      <c r="E71" s="3">
-        <v>2</v>
-      </c>
-      <c r="F71" s="3">
-        <v>4</v>
-      </c>
-      <c r="G71" s="3">
-        <v>4</v>
-      </c>
-      <c r="H71" s="3">
-        <v>2</v>
-      </c>
-      <c r="I71" s="3">
-        <v>3</v>
-      </c>
-      <c r="J71" s="3">
-        <v>3</v>
-      </c>
-      <c r="K71" s="3">
-        <v>4</v>
-      </c>
-      <c r="L71" s="3">
-        <v>2</v>
-      </c>
-      <c r="M71" s="3">
+      <c r="E72" s="3">
+        <v>2</v>
+      </c>
+      <c r="F72" s="3">
+        <v>4</v>
+      </c>
+      <c r="G72" s="3">
+        <v>4</v>
+      </c>
+      <c r="H72" s="3">
+        <v>2</v>
+      </c>
+      <c r="I72" s="3">
+        <v>3</v>
+      </c>
+      <c r="J72" s="3">
+        <v>3</v>
+      </c>
+      <c r="K72" s="3">
+        <v>4</v>
+      </c>
+      <c r="L72" s="3">
+        <v>2</v>
+      </c>
+      <c r="M72" s="3">
         <v>1</v>
       </c>
-      <c r="N71">
+      <c r="N72">
         <f t="shared" si="1"/>
         <v>24</v>
       </c>
     </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B72" s="3" t="s">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B73" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="C73" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D73" s="3">
         <v>166</v>
       </c>
-      <c r="E72" s="3">
-        <v>3</v>
-      </c>
-      <c r="F72" s="3">
-        <v>2</v>
-      </c>
-      <c r="G72" s="3">
-        <v>2</v>
-      </c>
-      <c r="H72" s="3">
-        <v>4</v>
-      </c>
-      <c r="I72" s="3">
-        <v>3</v>
-      </c>
-      <c r="J72" s="3">
-        <v>6</v>
-      </c>
-      <c r="K72" s="3">
-        <v>3</v>
-      </c>
-      <c r="L72" s="3">
-        <v>2</v>
-      </c>
-      <c r="M72" s="3">
+      <c r="E73" s="3">
+        <v>3</v>
+      </c>
+      <c r="F73" s="3">
+        <v>2</v>
+      </c>
+      <c r="G73" s="3">
+        <v>2</v>
+      </c>
+      <c r="H73" s="3">
+        <v>4</v>
+      </c>
+      <c r="I73" s="3">
+        <v>3</v>
+      </c>
+      <c r="J73" s="3">
+        <v>6</v>
+      </c>
+      <c r="K73" s="3">
+        <v>3</v>
+      </c>
+      <c r="L73" s="3">
+        <v>2</v>
+      </c>
+      <c r="M73" s="3">
         <v>1</v>
       </c>
-      <c r="N72">
+      <c r="N73">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B73" s="3" t="s">
+    <row r="74" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B74" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="C74" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D73" s="3">
+      <c r="D74" s="3">
         <v>158</v>
       </c>
-      <c r="E73" s="3">
-        <v>8</v>
-      </c>
-      <c r="F73" s="3">
-        <v>3</v>
-      </c>
-      <c r="G73" s="3">
-        <v>8</v>
-      </c>
-      <c r="H73" s="3">
-        <v>4</v>
-      </c>
-      <c r="I73" s="3">
-        <v>3</v>
-      </c>
-      <c r="J73" s="3">
-        <v>7</v>
-      </c>
-      <c r="K73" s="3">
-        <v>7</v>
-      </c>
-      <c r="L73" s="3">
-        <v>6</v>
-      </c>
-      <c r="M73" s="3">
-        <v>6</v>
-      </c>
-      <c r="N73">
+      <c r="E74" s="3">
+        <v>8</v>
+      </c>
+      <c r="F74" s="3">
+        <v>3</v>
+      </c>
+      <c r="G74" s="3">
+        <v>8</v>
+      </c>
+      <c r="H74" s="3">
+        <v>4</v>
+      </c>
+      <c r="I74" s="3">
+        <v>3</v>
+      </c>
+      <c r="J74" s="3">
+        <v>7</v>
+      </c>
+      <c r="K74" s="3">
+        <v>7</v>
+      </c>
+      <c r="L74" s="3">
+        <v>6</v>
+      </c>
+      <c r="M74" s="3">
+        <v>6</v>
+      </c>
+      <c r="N74">
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
     </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B74" s="3" t="s">
+    <row r="75" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B75" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="C75" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D74" s="3">
+      <c r="D75" s="3">
         <v>156</v>
       </c>
-      <c r="E74" s="3">
-        <v>3</v>
-      </c>
-      <c r="F74" s="3">
-        <v>6</v>
-      </c>
-      <c r="G74" s="3">
-        <v>4</v>
-      </c>
-      <c r="H74" s="3">
-        <v>3</v>
-      </c>
-      <c r="I74" s="3">
-        <v>7</v>
-      </c>
-      <c r="J74" s="3">
-        <v>4</v>
-      </c>
-      <c r="K74" s="3">
-        <v>7</v>
-      </c>
-      <c r="L74" s="3">
-        <v>7</v>
-      </c>
-      <c r="M74" s="3">
-        <v>5</v>
-      </c>
-      <c r="N74">
+      <c r="E75" s="3">
+        <v>3</v>
+      </c>
+      <c r="F75" s="3">
+        <v>6</v>
+      </c>
+      <c r="G75" s="3">
+        <v>4</v>
+      </c>
+      <c r="H75" s="3">
+        <v>3</v>
+      </c>
+      <c r="I75" s="3">
+        <v>7</v>
+      </c>
+      <c r="J75" s="3">
+        <v>4</v>
+      </c>
+      <c r="K75" s="3">
+        <v>7</v>
+      </c>
+      <c r="L75" s="3">
+        <v>7</v>
+      </c>
+      <c r="M75" s="3">
+        <v>5</v>
+      </c>
+      <c r="N75">
         <f t="shared" si="1"/>
         <v>41</v>
       </c>
     </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B75" s="3" t="s">
+    <row r="76" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B76" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="C76" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D75" s="3">
+      <c r="D76" s="3">
         <v>161</v>
       </c>
-      <c r="E75" s="3">
+      <c r="E76" s="3">
         <v>28</v>
       </c>
-      <c r="F75" s="3">
+      <c r="F76" s="3">
         <v>23</v>
       </c>
-      <c r="G75" s="3">
+      <c r="G76" s="3">
         <v>32</v>
       </c>
-      <c r="H75" s="3">
+      <c r="H76" s="3">
         <v>24</v>
       </c>
-      <c r="I75" s="3">
+      <c r="I76" s="3">
         <v>30</v>
       </c>
-      <c r="J75" s="3">
+      <c r="J76" s="3">
         <v>31</v>
       </c>
-      <c r="K75" s="3">
+      <c r="K76" s="3">
         <v>23</v>
       </c>
-      <c r="L75" s="3">
+      <c r="L76" s="3">
         <v>21</v>
       </c>
-      <c r="M75" s="3">
+      <c r="M76" s="3">
         <v>30</v>
       </c>
-      <c r="N75">
+      <c r="N76">
         <f t="shared" si="1"/>
         <v>212</v>
       </c>
     </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B76" s="3" t="s">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B77" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="C77" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D77" s="3">
         <v>164</v>
       </c>
-      <c r="E76" s="3">
+      <c r="E77" s="3">
         <v>10</v>
       </c>
-      <c r="F76" s="3">
+      <c r="F77" s="3">
         <v>40</v>
       </c>
-      <c r="G76" s="3">
+      <c r="G77" s="3">
         <v>10</v>
       </c>
-      <c r="H76" s="3">
+      <c r="H77" s="3">
         <v>27</v>
       </c>
-      <c r="I76" s="3">
+      <c r="I77" s="3">
         <v>27</v>
       </c>
-      <c r="J76" s="3">
+      <c r="J77" s="3">
         <v>33</v>
       </c>
-      <c r="K76" s="3">
+      <c r="K77" s="3">
         <v>23</v>
       </c>
-      <c r="L76" s="3">
+      <c r="L77" s="3">
         <v>20</v>
       </c>
-      <c r="M76" s="3">
+      <c r="M77" s="3">
         <v>29</v>
       </c>
-      <c r="N76">
+      <c r="N77">
         <f t="shared" si="1"/>
         <v>190</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B77" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C77" s="3" t="s">
+    <row r="78" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B78" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C78" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D77" s="3">
+      <c r="D78" s="3">
         <v>159</v>
       </c>
-      <c r="E77" s="3">
-        <v>8</v>
-      </c>
-      <c r="F77" s="3">
-        <v>8</v>
-      </c>
-      <c r="G77" s="3">
-        <v>5</v>
-      </c>
-      <c r="H77" s="3">
-        <v>6</v>
-      </c>
-      <c r="I77" s="3">
-        <v>6</v>
-      </c>
-      <c r="J77" s="3">
-        <v>8</v>
-      </c>
-      <c r="K77" s="3">
-        <v>5</v>
-      </c>
-      <c r="L77" s="3">
-        <v>7</v>
-      </c>
-      <c r="M77" s="3">
-        <v>7</v>
-      </c>
-      <c r="N77">
+      <c r="E78" s="3">
+        <v>8</v>
+      </c>
+      <c r="F78" s="3">
+        <v>8</v>
+      </c>
+      <c r="G78" s="3">
+        <v>5</v>
+      </c>
+      <c r="H78" s="3">
+        <v>6</v>
+      </c>
+      <c r="I78" s="3">
+        <v>6</v>
+      </c>
+      <c r="J78" s="3">
+        <v>8</v>
+      </c>
+      <c r="K78" s="3">
+        <v>5</v>
+      </c>
+      <c r="L78" s="3">
+        <v>7</v>
+      </c>
+      <c r="M78" s="3">
+        <v>7</v>
+      </c>
+      <c r="N78">
         <f t="shared" si="1"/>
         <v>53</v>
       </c>
     </row>
-    <row r="78" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B78" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C78" s="3" t="s">
+    <row r="79" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B79" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C79" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D78" s="3">
+      <c r="D79" s="3">
         <v>158</v>
       </c>
-      <c r="E78" s="3">
+      <c r="E79" s="3">
         <v>9</v>
       </c>
-      <c r="F78" s="3">
-        <v>7</v>
-      </c>
-      <c r="G78" s="3">
-        <v>7</v>
-      </c>
-      <c r="H78" s="3">
-        <v>6</v>
-      </c>
-      <c r="I78" s="3">
-        <v>5</v>
-      </c>
-      <c r="J78" s="3">
-        <v>7</v>
-      </c>
-      <c r="K78" s="3">
-        <v>4</v>
-      </c>
-      <c r="L78" s="3">
-        <v>7</v>
-      </c>
-      <c r="M78" s="3">
-        <v>7</v>
-      </c>
-      <c r="N78">
+      <c r="F79" s="3">
+        <v>7</v>
+      </c>
+      <c r="G79" s="3">
+        <v>7</v>
+      </c>
+      <c r="H79" s="3">
+        <v>6</v>
+      </c>
+      <c r="I79" s="3">
+        <v>5</v>
+      </c>
+      <c r="J79" s="3">
+        <v>7</v>
+      </c>
+      <c r="K79" s="3">
+        <v>4</v>
+      </c>
+      <c r="L79" s="3">
+        <v>7</v>
+      </c>
+      <c r="M79" s="3">
+        <v>7</v>
+      </c>
+      <c r="N79">
         <f t="shared" si="1"/>
         <v>52</v>
       </c>
     </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B79" s="3" t="s">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B80" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B80" s="2" t="s">
+    <row r="81" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="B81" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C80" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F80" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G80" s="2"/>
-      <c r="H80" s="2"/>
-      <c r="I80" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K80" s="2" t="s">
+      <c r="C81" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G81" s="2"/>
+      <c r="H81" s="2"/>
+      <c r="I81" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K81" s="2" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="81" spans="2:11" x14ac:dyDescent="0.55000000000000004">
-      <c r="B81" t="s">
-        <v>70</v>
-      </c>
-      <c r="C81" t="s">
-        <v>66</v>
-      </c>
-      <c r="D81">
-        <v>8</v>
-      </c>
-      <c r="E81">
-        <v>2</v>
-      </c>
-      <c r="F81">
-        <v>3</v>
-      </c>
-      <c r="I81">
-        <v>8</v>
-      </c>
-      <c r="J81">
-        <v>6</v>
       </c>
     </row>
     <row r="82" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B82" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C82" t="s">
         <v>66</v>
       </c>
       <c r="D82">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E82">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F82">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I82">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J82">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B83" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C83" t="s">
         <v>66</v>
       </c>
       <c r="D83">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="E83">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F83">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I83">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="J83">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B84" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C84" t="s">
         <v>66</v>
       </c>
       <c r="D84">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="E84">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F84">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I84">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="J84">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B85" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="C85" t="s">
         <v>66</v>
       </c>
       <c r="D85">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E85">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F85">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I85">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J85">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B86" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C86" t="s">
         <v>66</v>
       </c>
       <c r="D86">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E86">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F86">
         <v>3</v>
       </c>
       <c r="I86">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J86">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B87" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="C87" t="s">
         <v>66</v>
       </c>
       <c r="D87">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="E87">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="F87">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I87">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="J87">
-        <v>29</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88" spans="2:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B88" t="s">
+        <v>77</v>
+      </c>
+      <c r="C88" t="s">
+        <v>66</v>
+      </c>
+      <c r="D88">
+        <v>36</v>
+      </c>
+      <c r="E88">
+        <v>17</v>
+      </c>
+      <c r="F88">
+        <v>5</v>
+      </c>
+      <c r="I88">
+        <v>24</v>
+      </c>
+      <c r="J88">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="89" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="B89" t="s">
         <v>83</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C89" t="s">
         <v>84</v>
       </c>
-      <c r="D88">
-        <v>6</v>
-      </c>
-      <c r="E88">
-        <v>3</v>
-      </c>
-      <c r="F88">
-        <v>3</v>
-      </c>
-      <c r="I88">
-        <v>6</v>
-      </c>
-      <c r="J88">
+      <c r="D89">
+        <v>6</v>
+      </c>
+      <c r="E89">
+        <v>3</v>
+      </c>
+      <c r="F89">
+        <v>3</v>
+      </c>
+      <c r="I89">
+        <v>6</v>
+      </c>
+      <c r="J89">
         <v>4</v>
       </c>
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.55000000000000004">
-      <c r="K90" t="s">
-        <v>105</v>
+      <c r="B90" t="s">
+        <v>107</v>
+      </c>
+      <c r="C90" t="s">
+        <v>66</v>
+      </c>
+      <c r="D90">
+        <v>3</v>
+      </c>
+      <c r="E90">
+        <v>3</v>
+      </c>
+      <c r="F90">
+        <v>3</v>
+      </c>
+      <c r="I90">
+        <v>5</v>
+      </c>
+      <c r="J90">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhmgo\Desktop\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C63BA2E9-33BE-476F-969E-4EF246BC695E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB3CFD2-676A-42A3-82A7-DC5123561923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{B57D1550-4E85-435D-BD6F-1B13E635EA51}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="110">
   <si>
     <t>野手・打者</t>
   </si>
@@ -438,6 +438,13 @@
   </si>
   <si>
     <t>ヨシダ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>試験用投手A</t>
+    <rPh sb="0" eb="5">
+      <t>シケンヨウトウシュ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -820,7 +827,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C402B4-0E60-4338-B3CD-2DB7A1A076E1}">
-  <dimension ref="B2:N90"/>
+  <dimension ref="B2:N92"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="14.75" customWidth="1"/>
@@ -1201,7 +1208,7 @@
         <v>17</v>
       </c>
       <c r="D15" s="3">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E15" s="3">
         <v>20</v>
@@ -1223,7 +1230,7 @@
       </c>
       <c r="K15">
         <f t="shared" si="0"/>
-        <v>79</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.55000000000000004">
@@ -1366,7 +1373,7 @@
         <v>44</v>
       </c>
       <c r="D20" s="3">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="E20" s="3">
         <v>18</v>
@@ -1388,7 +1395,7 @@
       </c>
       <c r="K20">
         <f t="shared" si="0"/>
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.55000000000000004">
@@ -1597,7 +1604,7 @@
         <v>52</v>
       </c>
       <c r="D27" s="3">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="E27" s="3">
         <v>19</v>
@@ -1619,7 +1626,7 @@
       </c>
       <c r="K27">
         <f t="shared" si="0"/>
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.55000000000000004">
@@ -1729,7 +1736,7 @@
         <v>52</v>
       </c>
       <c r="D31" s="3">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="E31" s="3">
         <v>16</v>
@@ -1751,7 +1758,7 @@
       </c>
       <c r="K31">
         <f t="shared" si="0"/>
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.55000000000000004">
@@ -2052,526 +2059,495 @@
       </c>
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="3"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B42" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J41" s="3"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B43" s="2" t="s">
+      <c r="J42" s="3"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B44" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C43" s="2" t="s">
+      <c r="C44" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="D44" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="E44" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F43" s="2" t="s">
+      <c r="F44" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G43" s="2" t="s">
+      <c r="G44" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H43" s="2" t="s">
+      <c r="H44" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I43" s="2" t="s">
+      <c r="I44" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="J43" s="2" t="s">
+      <c r="J44" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="K43" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="L43" s="2" t="s">
+      <c r="K44" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L44" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M43" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N43" s="2" t="s">
+      <c r="M44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N44" s="2" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B44" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D44" s="3">
-        <v>165</v>
-      </c>
-      <c r="E44" s="3">
-        <v>9</v>
-      </c>
-      <c r="F44" s="3">
-        <v>5</v>
-      </c>
-      <c r="G44" s="3">
-        <v>8</v>
-      </c>
-      <c r="H44" s="3">
-        <v>8</v>
-      </c>
-      <c r="I44" s="3">
-        <v>6</v>
-      </c>
-      <c r="J44" s="3">
-        <v>8</v>
-      </c>
-      <c r="K44" s="3">
-        <v>7</v>
-      </c>
-      <c r="L44" s="3">
-        <v>6</v>
-      </c>
-      <c r="M44" s="3">
-        <v>9</v>
-      </c>
-      <c r="N44">
-        <f>SUM(E44:L44)</f>
-        <v>57</v>
       </c>
     </row>
     <row r="45" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D45" s="3">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="E45" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F45" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G45" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H45" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I45" s="3">
+        <v>6</v>
+      </c>
+      <c r="J45" s="3">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
+        <v>7</v>
+      </c>
+      <c r="L45" s="3">
+        <v>6</v>
+      </c>
+      <c r="M45" s="3">
         <v>9</v>
       </c>
-      <c r="J45" s="3">
-        <v>7</v>
-      </c>
-      <c r="K45" s="3">
-        <v>6</v>
-      </c>
-      <c r="L45" s="3">
-        <v>7</v>
-      </c>
-      <c r="M45" s="3">
-        <v>8</v>
-      </c>
       <c r="N45">
-        <f t="shared" ref="N45:N79" si="1">SUM(E45:L45)</f>
-        <v>54</v>
+        <f>SUM(E45:L45)</f>
+        <v>57</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B46" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D46" s="3">
+        <v>157</v>
+      </c>
+      <c r="E46" s="3">
+        <v>8</v>
+      </c>
+      <c r="F46" s="3">
+        <v>3</v>
+      </c>
+      <c r="G46" s="3">
+        <v>7</v>
+      </c>
+      <c r="H46" s="3">
+        <v>7</v>
+      </c>
+      <c r="I46" s="3">
+        <v>9</v>
+      </c>
+      <c r="J46" s="3">
+        <v>7</v>
+      </c>
+      <c r="K46" s="3">
+        <v>6</v>
+      </c>
+      <c r="L46" s="3">
+        <v>7</v>
+      </c>
+      <c r="M46" s="3">
+        <v>8</v>
+      </c>
+      <c r="N46">
+        <f t="shared" ref="N46:N81" si="1">SUM(E46:L46)</f>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B47" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D47" s="3">
         <v>155</v>
       </c>
-      <c r="E46" s="3">
-        <v>5</v>
-      </c>
-      <c r="F46" s="3">
-        <v>2</v>
-      </c>
-      <c r="G46" s="3">
+      <c r="E47" s="3">
+        <v>5</v>
+      </c>
+      <c r="F47" s="3">
+        <v>2</v>
+      </c>
+      <c r="G47" s="3">
         <v>10</v>
       </c>
-      <c r="H46" s="3">
-        <v>6</v>
-      </c>
-      <c r="I46" s="3">
-        <v>6</v>
-      </c>
-      <c r="J46" s="3">
-        <v>6</v>
-      </c>
-      <c r="K46" s="3">
-        <v>5</v>
-      </c>
-      <c r="L46" s="3">
-        <v>7</v>
-      </c>
-      <c r="M46" s="3">
-        <v>6</v>
-      </c>
-      <c r="N46">
+      <c r="H47" s="3">
+        <v>6</v>
+      </c>
+      <c r="I47" s="3">
+        <v>6</v>
+      </c>
+      <c r="J47" s="3">
+        <v>6</v>
+      </c>
+      <c r="K47" s="3">
+        <v>5</v>
+      </c>
+      <c r="L47" s="3">
+        <v>7</v>
+      </c>
+      <c r="M47" s="3">
+        <v>6</v>
+      </c>
+      <c r="N47">
         <f t="shared" si="1"/>
         <v>47</v>
       </c>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B47" s="3" t="s">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B48" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C48" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D48" s="3">
         <v>148</v>
       </c>
-      <c r="E47" s="3">
-        <v>4</v>
-      </c>
-      <c r="F47" s="3">
+      <c r="E48" s="3">
+        <v>4</v>
+      </c>
+      <c r="F48" s="3">
         <v>10</v>
       </c>
-      <c r="G47" s="3">
-        <v>6</v>
-      </c>
-      <c r="H47" s="3">
-        <v>4</v>
-      </c>
-      <c r="I47" s="3">
-        <v>8</v>
-      </c>
-      <c r="J47" s="3">
-        <v>5</v>
-      </c>
-      <c r="K47" s="3">
-        <v>4</v>
-      </c>
-      <c r="L47" s="3">
-        <v>5</v>
-      </c>
-      <c r="M47" s="3">
-        <v>6</v>
-      </c>
-      <c r="N47">
+      <c r="G48" s="3">
+        <v>6</v>
+      </c>
+      <c r="H48" s="3">
+        <v>4</v>
+      </c>
+      <c r="I48" s="3">
+        <v>8</v>
+      </c>
+      <c r="J48" s="3">
+        <v>5</v>
+      </c>
+      <c r="K48" s="3">
+        <v>4</v>
+      </c>
+      <c r="L48" s="3">
+        <v>5</v>
+      </c>
+      <c r="M48" s="3">
+        <v>6</v>
+      </c>
+      <c r="N48">
         <f t="shared" si="1"/>
         <v>46</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B48" s="3" t="s">
+    <row r="49" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B49" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C49" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D49" s="3">
         <v>220</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E49" s="3">
         <v>1</v>
       </c>
-      <c r="F48" s="3">
+      <c r="F49" s="3">
         <v>1</v>
       </c>
-      <c r="G48" s="3">
+      <c r="G49" s="3">
         <v>9</v>
       </c>
-      <c r="H48" s="3">
+      <c r="H49" s="3">
         <v>1</v>
       </c>
-      <c r="I48" s="3">
-        <v>3</v>
-      </c>
-      <c r="J48" s="3">
-        <v>6</v>
-      </c>
-      <c r="K48" s="3">
-        <v>4</v>
-      </c>
-      <c r="L48" s="3">
-        <v>6</v>
-      </c>
-      <c r="M48" s="3">
-        <v>5</v>
-      </c>
-      <c r="N48">
+      <c r="I49" s="3">
+        <v>3</v>
+      </c>
+      <c r="J49" s="3">
+        <v>6</v>
+      </c>
+      <c r="K49" s="3">
+        <v>4</v>
+      </c>
+      <c r="L49" s="3">
+        <v>6</v>
+      </c>
+      <c r="M49" s="3">
+        <v>5</v>
+      </c>
+      <c r="N49">
         <f t="shared" si="1"/>
         <v>31</v>
       </c>
     </row>
-    <row r="49" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B49" s="3" t="s">
+    <row r="50" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B50" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C50" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D50" s="3">
         <v>100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="E50" s="3">
         <v>9</v>
       </c>
-      <c r="F49" s="3">
+      <c r="F50" s="3">
         <v>9</v>
       </c>
-      <c r="G49" s="3">
+      <c r="G50" s="3">
         <v>9</v>
       </c>
-      <c r="H49" s="3">
+      <c r="H50" s="3">
         <v>9</v>
       </c>
-      <c r="I49" s="3">
+      <c r="I50" s="3">
         <v>9</v>
       </c>
-      <c r="J49" s="3">
-        <v>6</v>
-      </c>
-      <c r="K49" s="3">
-        <v>8</v>
-      </c>
-      <c r="L49" s="3">
-        <v>4</v>
-      </c>
-      <c r="M49" s="3">
-        <v>5</v>
-      </c>
-      <c r="N49">
+      <c r="J50" s="3">
+        <v>6</v>
+      </c>
+      <c r="K50" s="3">
+        <v>8</v>
+      </c>
+      <c r="L50" s="3">
+        <v>4</v>
+      </c>
+      <c r="M50" s="3">
+        <v>5</v>
+      </c>
+      <c r="N50">
         <f t="shared" si="1"/>
         <v>63</v>
       </c>
     </row>
-    <row r="50" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B50" s="3" t="s">
+    <row r="51" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B51" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C51" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D50" s="3">
+      <c r="D51" s="3">
         <v>149</v>
       </c>
-      <c r="E50" s="3">
-        <v>3</v>
-      </c>
-      <c r="F50" s="3">
-        <v>6</v>
-      </c>
-      <c r="G50" s="3">
-        <v>5</v>
-      </c>
-      <c r="H50" s="3">
+      <c r="E51" s="3">
+        <v>3</v>
+      </c>
+      <c r="F51" s="3">
+        <v>6</v>
+      </c>
+      <c r="G51" s="3">
+        <v>5</v>
+      </c>
+      <c r="H51" s="3">
         <v>10</v>
       </c>
-      <c r="I50" s="3">
-        <v>5</v>
-      </c>
-      <c r="J50" s="3">
-        <v>8</v>
-      </c>
-      <c r="K50" s="3">
-        <v>5</v>
-      </c>
-      <c r="L50" s="3">
-        <v>6</v>
-      </c>
-      <c r="M50" s="3">
-        <v>6</v>
-      </c>
-      <c r="N50">
+      <c r="I51" s="3">
+        <v>5</v>
+      </c>
+      <c r="J51" s="3">
+        <v>8</v>
+      </c>
+      <c r="K51" s="3">
+        <v>5</v>
+      </c>
+      <c r="L51" s="3">
+        <v>6</v>
+      </c>
+      <c r="M51" s="3">
+        <v>6</v>
+      </c>
+      <c r="N51">
         <f t="shared" si="1"/>
         <v>48</v>
       </c>
     </row>
-    <row r="51" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B51" s="3" t="s">
+    <row r="52" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B52" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C52" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D51" s="3">
+      <c r="D52" s="3">
         <v>158</v>
       </c>
-      <c r="E51" s="3">
+      <c r="E52" s="3">
         <v>9</v>
       </c>
-      <c r="F51" s="3">
-        <v>8</v>
-      </c>
-      <c r="G51" s="3">
-        <v>6</v>
-      </c>
-      <c r="H51" s="3">
-        <v>5</v>
-      </c>
-      <c r="I51" s="3">
-        <v>7</v>
-      </c>
-      <c r="J51" s="3">
-        <v>4</v>
-      </c>
-      <c r="K51" s="3">
-        <v>5</v>
-      </c>
-      <c r="L51" s="3">
-        <v>5</v>
-      </c>
-      <c r="M51" s="3">
-        <v>6</v>
-      </c>
-      <c r="N51">
+      <c r="F52" s="3">
+        <v>8</v>
+      </c>
+      <c r="G52" s="3">
+        <v>6</v>
+      </c>
+      <c r="H52" s="3">
+        <v>5</v>
+      </c>
+      <c r="I52" s="3">
+        <v>7</v>
+      </c>
+      <c r="J52" s="3">
+        <v>4</v>
+      </c>
+      <c r="K52" s="3">
+        <v>5</v>
+      </c>
+      <c r="L52" s="3">
+        <v>5</v>
+      </c>
+      <c r="M52" s="3">
+        <v>6</v>
+      </c>
+      <c r="N52">
         <f t="shared" si="1"/>
         <v>49</v>
       </c>
     </row>
-    <row r="52" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B52" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D52" s="3">
-        <v>172</v>
-      </c>
-      <c r="E52" s="3">
-        <v>27</v>
-      </c>
-      <c r="F52" s="3">
-        <v>26</v>
-      </c>
-      <c r="G52" s="3">
-        <v>24</v>
-      </c>
-      <c r="H52" s="3">
-        <v>27</v>
-      </c>
-      <c r="I52" s="3">
-        <v>25</v>
-      </c>
-      <c r="J52" s="3">
-        <v>32</v>
-      </c>
-      <c r="K52" s="3">
-        <v>24</v>
-      </c>
-      <c r="L52" s="3">
-        <v>21</v>
-      </c>
-      <c r="M52" s="3">
-        <v>30</v>
-      </c>
-      <c r="N52">
-        <f t="shared" si="1"/>
-        <v>206</v>
-      </c>
-    </row>
     <row r="53" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B53" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D53" s="3">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E53" s="3">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F53" s="3">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G53" s="3">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="H53" s="3">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="I53" s="3">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="J53" s="3">
+        <v>32</v>
+      </c>
+      <c r="K53" s="3">
         <v>14</v>
       </c>
-      <c r="K53" s="3">
-        <v>6</v>
-      </c>
       <c r="L53" s="3">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="M53" s="3">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="N53">
         <f t="shared" si="1"/>
-        <v>54</v>
+        <v>161</v>
       </c>
     </row>
     <row r="54" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B54" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D54" s="3">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="E54" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F54" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G54" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H54" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I54" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J54" s="3">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K54" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L54" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M54" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N54">
         <f t="shared" si="1"/>
-        <v>49</v>
+        <v>54</v>
       </c>
     </row>
     <row r="55" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B55" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="D55" s="3">
-        <v>169</v>
+        <v>143</v>
       </c>
       <c r="E55" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F55" s="3">
         <v>4</v>
@@ -2580,226 +2556,226 @@
         <v>5</v>
       </c>
       <c r="H55" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I55" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J55" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K55" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L55" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M55" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N55">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="56" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B56" s="3" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D56" s="3">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="E56" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F56" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G56" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H56" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I56" s="3">
         <v>5</v>
       </c>
       <c r="J56" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K56" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L56" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M56" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N56">
         <f t="shared" si="1"/>
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="57" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B57" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D57" s="3">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E57" s="3">
         <v>2</v>
       </c>
       <c r="F57" s="3">
+        <v>10</v>
+      </c>
+      <c r="G57" s="3">
+        <v>2</v>
+      </c>
+      <c r="H57" s="3">
+        <v>2</v>
+      </c>
+      <c r="I57" s="3">
+        <v>5</v>
+      </c>
+      <c r="J57" s="3">
+        <v>2</v>
+      </c>
+      <c r="K57" s="3">
+        <v>5</v>
+      </c>
+      <c r="L57" s="3">
+        <v>2</v>
+      </c>
+      <c r="M57" s="3">
         <v>1</v>
-      </c>
-      <c r="G57" s="3">
-        <v>9</v>
-      </c>
-      <c r="H57" s="3">
-        <v>7</v>
-      </c>
-      <c r="I57" s="3">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3">
-        <v>9</v>
-      </c>
-      <c r="K57" s="3">
-        <v>3</v>
-      </c>
-      <c r="L57" s="3">
-        <v>2</v>
-      </c>
-      <c r="M57" s="3">
-        <v>3</v>
       </c>
       <c r="N57">
         <f t="shared" si="1"/>
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="58" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B58" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D58" s="3">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E58" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F58" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G58" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H58" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I58" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J58" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K58" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L58" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="M58" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N58">
         <f t="shared" si="1"/>
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="59" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B59" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D59" s="3">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="E59" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F59" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G59" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H59" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I59" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J59" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K59" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L59" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M59" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N59">
         <f t="shared" si="1"/>
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="60" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B60" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D60" s="3">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="E60" s="3">
         <v>2</v>
       </c>
       <c r="F60" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G60" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H60" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I60" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J60" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K60" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L60" s="3">
         <v>2</v>
@@ -2809,312 +2785,312 @@
       </c>
       <c r="N60">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>34</v>
       </c>
     </row>
     <row r="61" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B61" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D61" s="3">
-        <v>159</v>
+        <v>125</v>
       </c>
       <c r="E61" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F61" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G61" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H61" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J61" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K61" s="3">
         <v>3</v>
       </c>
       <c r="L61" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M61" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N61">
         <f t="shared" si="1"/>
-        <v>38</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B62" s="3" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D62" s="3">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E62" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F62" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G62" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H62" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I62" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J62" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K62" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L62" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M62" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N62">
         <f t="shared" si="1"/>
-        <v>54</v>
+        <v>38</v>
       </c>
     </row>
     <row r="63" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B63" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>52</v>
       </c>
       <c r="D63" s="3">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="E63" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F63" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G63" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H63" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I63" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J63" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K63" s="3">
         <v>5</v>
       </c>
       <c r="L63" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M63" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N63">
         <f t="shared" si="1"/>
-        <v>30</v>
+        <v>54</v>
       </c>
     </row>
     <row r="64" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B64" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D64" s="3">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E64" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F64" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G64" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H64" s="3">
         <v>3</v>
       </c>
       <c r="I64" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J64" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K64" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L64" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M64" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N64">
         <f t="shared" si="1"/>
-        <v>46</v>
+        <v>30</v>
       </c>
     </row>
     <row r="65" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B65" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D65" s="3">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="E65" s="3">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F65" s="3">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="G65" s="3">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="H65" s="3">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="I65" s="3">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="J65" s="3">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="K65" s="3">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="L65" s="3">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="M65" s="3">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="N65">
         <f t="shared" si="1"/>
-        <v>215</v>
+        <v>46</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B66" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D66" s="3">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="E66" s="3">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F66" s="3">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="G66" s="3">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H66" s="3">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I66" s="3">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J66" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K66" s="3">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="L66" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="M66" s="3">
         <v>32</v>
       </c>
       <c r="N66">
         <f t="shared" si="1"/>
-        <v>223</v>
+        <v>169</v>
       </c>
     </row>
     <row r="67" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B67" s="3" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D67" s="3">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E67" s="3">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="F67" s="3">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="G67" s="3">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="H67" s="3">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="I67" s="3">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="J67" s="3">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="K67" s="3">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="L67" s="3">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="M67" s="3">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="N67">
         <f t="shared" si="1"/>
-        <v>33</v>
+        <v>178</v>
       </c>
     </row>
     <row r="68" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B68" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D68" s="3">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="E68" s="3">
         <v>7</v>
@@ -3123,103 +3099,103 @@
         <v>3</v>
       </c>
       <c r="G68" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H68" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I68" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J68" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K68" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L68" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M68" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N68">
         <f t="shared" si="1"/>
-        <v>55</v>
+        <v>33</v>
       </c>
     </row>
     <row r="69" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B69" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D69" s="3">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="E69" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F69" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G69" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H69" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I69" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J69" s="3">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="K69" s="3">
         <v>6</v>
       </c>
       <c r="L69" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M69" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N69">
         <f t="shared" si="1"/>
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="70" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B70" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D70" s="3">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E70" s="3">
+        <v>8</v>
+      </c>
+      <c r="F70" s="3">
+        <v>1</v>
+      </c>
+      <c r="G70" s="3">
+        <v>4</v>
+      </c>
+      <c r="H70" s="3">
         <v>9</v>
       </c>
-      <c r="F70" s="3">
-        <v>7</v>
-      </c>
-      <c r="G70" s="3">
-        <v>3</v>
-      </c>
-      <c r="H70" s="3">
-        <v>6</v>
-      </c>
       <c r="I70" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J70" s="3">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K70" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L70" s="3">
         <v>3</v>
@@ -3229,81 +3205,81 @@
       </c>
       <c r="N70">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="71" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B71" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D71" s="3">
-        <v>77</v>
+        <v>161</v>
       </c>
       <c r="E71" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F71" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G71" s="3">
         <v>3</v>
       </c>
       <c r="H71" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I71" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J71" s="3">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="K71" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L71" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M71" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N71">
         <f t="shared" si="1"/>
-        <v>21</v>
+        <v>50</v>
       </c>
     </row>
     <row r="72" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B72" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D72" s="3">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="E72" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F72" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G72" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H72" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I72" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J72" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K72" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L72" s="3">
         <v>2</v>
@@ -3313,39 +3289,39 @@
       </c>
       <c r="N72">
         <f t="shared" si="1"/>
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="73" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B73" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D73" s="3">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="E73" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F73" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G73" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H73" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I73" s="3">
         <v>3</v>
       </c>
       <c r="J73" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K73" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L73" s="3">
         <v>2</v>
@@ -3355,27 +3331,27 @@
       </c>
       <c r="N73">
         <f t="shared" si="1"/>
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="74" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B74" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D74" s="3">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="E74" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F74" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G74" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H74" s="3">
         <v>4</v>
@@ -3384,220 +3360,220 @@
         <v>3</v>
       </c>
       <c r="J74" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K74" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L74" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M74" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N74">
         <f t="shared" si="1"/>
-        <v>46</v>
+        <v>25</v>
       </c>
     </row>
     <row r="75" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B75" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D75" s="3">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E75" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F75" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G75" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H75" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I75" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J75" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K75" s="3">
         <v>7</v>
       </c>
       <c r="L75" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M75" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N75">
         <f t="shared" si="1"/>
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="76" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B76" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D76" s="3">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="E76" s="3">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="F76" s="3">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="G76" s="3">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="H76" s="3">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="I76" s="3">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="J76" s="3">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="K76" s="3">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="L76" s="3">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="M76" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="N76">
         <f t="shared" si="1"/>
-        <v>212</v>
+        <v>41</v>
       </c>
     </row>
     <row r="77" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B77" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D77" s="3">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E77" s="3">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F77" s="3">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="G77" s="3">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="H77" s="3">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="I77" s="3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J77" s="3">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K77" s="3">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="L77" s="3">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="M77" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N77">
         <f t="shared" si="1"/>
-        <v>190</v>
+        <v>167</v>
       </c>
     </row>
     <row r="78" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B78" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D78" s="3">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="E78" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F78" s="3">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="G78" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H78" s="3">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I78" s="3">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="J78" s="3">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="K78" s="3">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="L78" s="3">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M78" s="3">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="N78">
         <f t="shared" si="1"/>
-        <v>53</v>
+        <v>165</v>
       </c>
     </row>
     <row r="79" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B79" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D79" s="3">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E79" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F79" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G79" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H79" s="3">
         <v>6</v>
       </c>
       <c r="I79" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J79" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K79" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L79" s="3">
         <v>7</v>
@@ -3607,246 +3583,330 @@
       </c>
       <c r="N79">
         <f t="shared" si="1"/>
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="80" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B80" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D80" s="3">
+        <v>158</v>
+      </c>
+      <c r="E80" s="3">
+        <v>9</v>
+      </c>
+      <c r="F80" s="3">
+        <v>7</v>
+      </c>
+      <c r="G80" s="3">
+        <v>7</v>
+      </c>
+      <c r="H80" s="3">
+        <v>6</v>
+      </c>
+      <c r="I80" s="3">
+        <v>5</v>
+      </c>
+      <c r="J80" s="3">
+        <v>7</v>
+      </c>
+      <c r="K80" s="3">
+        <v>4</v>
+      </c>
+      <c r="L80" s="3">
+        <v>7</v>
+      </c>
+      <c r="M80" s="3">
+        <v>7</v>
+      </c>
+      <c r="N80">
+        <f t="shared" si="1"/>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="81" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B81" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D81" s="3">
+        <v>150</v>
+      </c>
+      <c r="E81" s="3">
+        <v>5</v>
+      </c>
+      <c r="F81" s="3">
+        <v>5</v>
+      </c>
+      <c r="G81" s="3">
+        <v>5</v>
+      </c>
+      <c r="H81" s="3">
+        <v>5</v>
+      </c>
+      <c r="I81" s="3">
+        <v>5</v>
+      </c>
+      <c r="J81" s="3">
+        <v>4096</v>
+      </c>
+      <c r="K81" s="3">
+        <v>5</v>
+      </c>
+      <c r="L81" s="3">
+        <v>5</v>
+      </c>
+      <c r="M81" s="3">
+        <v>5</v>
+      </c>
+      <c r="N81">
+        <f t="shared" si="1"/>
+        <v>4131</v>
+      </c>
+    </row>
+    <row r="82" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B82" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="81" spans="2:11" x14ac:dyDescent="0.55000000000000004">
-      <c r="B81" s="2" t="s">
+    <row r="83" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B83" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C81" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F81" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G81" s="2"/>
-      <c r="H81" s="2"/>
-      <c r="I81" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J81" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K81" s="2" t="s">
+      <c r="C83" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G83" s="2"/>
+      <c r="H83" s="2"/>
+      <c r="I83" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J83" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K83" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="82" spans="2:11" x14ac:dyDescent="0.55000000000000004">
-      <c r="B82" t="s">
+    <row r="84" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B84" t="s">
         <v>70</v>
-      </c>
-      <c r="C82" t="s">
-        <v>66</v>
-      </c>
-      <c r="D82">
-        <v>8</v>
-      </c>
-      <c r="E82">
-        <v>2</v>
-      </c>
-      <c r="F82">
-        <v>3</v>
-      </c>
-      <c r="I82">
-        <v>8</v>
-      </c>
-      <c r="J82">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="83" spans="2:11" x14ac:dyDescent="0.55000000000000004">
-      <c r="B83" t="s">
-        <v>67</v>
-      </c>
-      <c r="C83" t="s">
-        <v>66</v>
-      </c>
-      <c r="D83">
-        <v>4</v>
-      </c>
-      <c r="E83">
-        <v>6</v>
-      </c>
-      <c r="F83">
-        <v>4</v>
-      </c>
-      <c r="I83">
-        <v>7</v>
-      </c>
-      <c r="J83">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="84" spans="2:11" x14ac:dyDescent="0.55000000000000004">
-      <c r="B84" t="s">
-        <v>68</v>
       </c>
       <c r="C84" t="s">
         <v>66</v>
       </c>
       <c r="D84">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="E84">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="F84">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I84">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="J84">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="85" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B85" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C85" t="s">
         <v>66</v>
       </c>
       <c r="D85">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E85">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F85">
         <v>4</v>
       </c>
       <c r="I85">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J85">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="86" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B86" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C86" t="s">
         <v>66</v>
       </c>
       <c r="D86">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="E86">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="F86">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I86">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="J86">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="87" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="87" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B87" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C87" t="s">
         <v>66</v>
       </c>
       <c r="D87">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E87">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F87">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I87">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J87">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="88" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B88" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="C88" t="s">
         <v>66</v>
       </c>
       <c r="D88">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="E88">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="F88">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I88">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="J88">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="89" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B89" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="C89" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="D89">
         <v>6</v>
       </c>
       <c r="E89">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F89">
         <v>3</v>
       </c>
       <c r="I89">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J89">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="90" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B90" t="s">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="C90" t="s">
         <v>66</v>
       </c>
       <c r="D90">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="E90">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="F90">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I90">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="J90">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="91" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B91" t="s">
+        <v>83</v>
+      </c>
+      <c r="C91" t="s">
+        <v>84</v>
+      </c>
+      <c r="D91">
+        <v>6</v>
+      </c>
+      <c r="E91">
+        <v>3</v>
+      </c>
+      <c r="F91">
+        <v>3</v>
+      </c>
+      <c r="I91">
+        <v>6</v>
+      </c>
+      <c r="J91">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B92" t="s">
+        <v>107</v>
+      </c>
+      <c r="C92" t="s">
+        <v>66</v>
+      </c>
+      <c r="D92">
+        <v>3</v>
+      </c>
+      <c r="E92">
+        <v>3</v>
+      </c>
+      <c r="F92">
+        <v>3</v>
+      </c>
+      <c r="I92">
+        <v>5</v>
+      </c>
+      <c r="J92">
         <v>2</v>
       </c>
     </row>

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhmgo\Desktop\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB3CFD2-676A-42A3-82A7-DC5123561923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DA90C7B-ECCC-46AE-ACA2-0D8835DFF3F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{B57D1550-4E85-435D-BD6F-1B13E635EA51}"/>
   </bookViews>
@@ -980,10 +980,10 @@
         <v>6</v>
       </c>
       <c r="E8" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F8" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G8" s="3">
         <v>7</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="K8">
         <f t="shared" si="0"/>
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.55000000000000004">
@@ -1274,10 +1274,10 @@
         <v>44</v>
       </c>
       <c r="D17" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E17" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F17" s="3">
         <v>6</v>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="K17">
         <f t="shared" si="0"/>
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.55000000000000004">
@@ -1409,7 +1409,7 @@
         <v>4</v>
       </c>
       <c r="E21" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F21" s="3">
         <v>5</v>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="K21">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.55000000000000004">
@@ -1937,7 +1937,7 @@
         <v>5</v>
       </c>
       <c r="E37" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F37" s="3">
         <v>4</v>
@@ -1956,7 +1956,7 @@
       </c>
       <c r="K37">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="2:14" x14ac:dyDescent="0.55000000000000004">

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhmgo\Desktop\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DA90C7B-ECCC-46AE-ACA2-0D8835DFF3F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87E59B4A-A960-4234-B829-9979CFFEF1D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{B57D1550-4E85-435D-BD6F-1B13E635EA51}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="112">
   <si>
     <t>野手・打者</t>
   </si>
@@ -441,10 +441,15 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>試験用投手A</t>
-    <rPh sb="0" eb="5">
-      <t>シケンヨウトウシュ</t>
-    </rPh>
+    <t>サブロウスキ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ケリー</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ｓ</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -827,7 +832,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C402B4-0E60-4338-B3CD-2DB7A1A076E1}">
-  <dimension ref="B2:N92"/>
+  <dimension ref="B2:N93"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="14.75" customWidth="1"/>
@@ -914,7 +919,7 @@
         <v>4</v>
       </c>
       <c r="E6" s="3">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F6" s="3">
         <v>10</v>
@@ -923,7 +928,7 @@
         <v>3</v>
       </c>
       <c r="H6" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I6" s="3">
         <v>11</v>
@@ -933,7 +938,7 @@
       </c>
       <c r="K6">
         <f t="shared" ref="K6:K38" si="0">SUM(D6:I6)</f>
-        <v>69</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.55000000000000004">
@@ -1208,10 +1213,10 @@
         <v>17</v>
       </c>
       <c r="D15" s="3">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="E15" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F15" s="3">
         <v>6</v>
@@ -1230,7 +1235,7 @@
       </c>
       <c r="K15">
         <f t="shared" si="0"/>
-        <v>69</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.55000000000000004">
@@ -1373,10 +1378,10 @@
         <v>44</v>
       </c>
       <c r="D20" s="3">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E20" s="3">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F20" s="3">
         <v>8</v>
@@ -1395,7 +1400,7 @@
       </c>
       <c r="K20">
         <f t="shared" si="0"/>
-        <v>80</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.55000000000000004">
@@ -1604,10 +1609,10 @@
         <v>52</v>
       </c>
       <c r="D27" s="3">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="E27" s="3">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F27" s="3">
         <v>8</v>
@@ -1616,7 +1621,7 @@
         <v>3</v>
       </c>
       <c r="H27" s="3">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I27" s="3">
         <v>10</v>
@@ -1626,7 +1631,7 @@
       </c>
       <c r="K27">
         <f t="shared" si="0"/>
-        <v>89</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.55000000000000004">
@@ -1736,10 +1741,10 @@
         <v>52</v>
       </c>
       <c r="D31" s="3">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="E31" s="3">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F31" s="3">
         <v>5</v>
@@ -1758,7 +1763,7 @@
       </c>
       <c r="K31">
         <f t="shared" si="0"/>
-        <v>80</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.55000000000000004">
@@ -1970,7 +1975,7 @@
         <v>4</v>
       </c>
       <c r="E38" s="3">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F38" s="3">
         <v>6</v>
@@ -1989,7 +1994,7 @@
       </c>
       <c r="K38">
         <f t="shared" si="0"/>
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="39" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -2003,7 +2008,7 @@
         <v>4</v>
       </c>
       <c r="E39" s="3">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F39" s="3">
         <v>20</v>
@@ -2022,7 +2027,7 @@
       </c>
       <c r="K39">
         <f>SUM(D39:J39)</f>
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -2196,7 +2201,7 @@
         <v>8</v>
       </c>
       <c r="N46">
-        <f t="shared" ref="N46:N81" si="1">SUM(E46:L46)</f>
+        <f t="shared" ref="N46:N82" si="1">SUM(E46:L46)</f>
         <v>54</v>
       </c>
     </row>
@@ -2652,14 +2657,14 @@
         <v>5</v>
       </c>
       <c r="L57" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M57" s="3">
         <v>1</v>
       </c>
       <c r="N57">
         <f t="shared" si="1"/>
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="58" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -2694,14 +2699,14 @@
         <v>3</v>
       </c>
       <c r="L58" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M58" s="3">
         <v>3</v>
       </c>
       <c r="N58">
         <f t="shared" si="1"/>
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="59" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -2778,14 +2783,14 @@
         <v>5</v>
       </c>
       <c r="L60" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M60" s="3">
         <v>3</v>
       </c>
       <c r="N60">
         <f t="shared" si="1"/>
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="61" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -2820,14 +2825,14 @@
         <v>3</v>
       </c>
       <c r="L61" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M61" s="3">
         <v>3</v>
       </c>
       <c r="N61">
         <f t="shared" si="1"/>
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -3114,14 +3119,14 @@
         <v>5</v>
       </c>
       <c r="L68" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M68" s="3">
         <v>3</v>
       </c>
       <c r="N68">
         <f t="shared" si="1"/>
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="69" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -3282,14 +3287,14 @@
         <v>3</v>
       </c>
       <c r="L72" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M72" s="3">
         <v>1</v>
       </c>
       <c r="N72">
         <f t="shared" si="1"/>
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="73" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -3324,14 +3329,14 @@
         <v>4</v>
       </c>
       <c r="L73" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M73" s="3">
         <v>1</v>
       </c>
       <c r="N73">
         <f t="shared" si="1"/>
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="74" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -3366,14 +3371,14 @@
         <v>3</v>
       </c>
       <c r="L74" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M74" s="3">
         <v>1</v>
       </c>
       <c r="N74">
         <f t="shared" si="1"/>
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="75" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -3633,280 +3638,322 @@
         <v>109</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D81" s="3">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E81" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F81" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G81" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H81" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I81" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J81" s="3">
-        <v>4096</v>
+        <v>10</v>
       </c>
       <c r="K81" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L81" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M81" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N81">
         <f t="shared" si="1"/>
-        <v>4131</v>
+        <v>51</v>
       </c>
     </row>
     <row r="82" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B82" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D82" s="3">
+        <v>148</v>
+      </c>
+      <c r="E82" s="3">
+        <v>5</v>
+      </c>
+      <c r="F82" s="3">
+        <v>3</v>
+      </c>
+      <c r="G82" s="3">
+        <v>5</v>
+      </c>
+      <c r="H82" s="3">
+        <v>4</v>
+      </c>
+      <c r="I82" s="3">
+        <v>6</v>
+      </c>
+      <c r="J82" s="3">
+        <v>4</v>
+      </c>
+      <c r="K82" s="3">
+        <v>5</v>
+      </c>
+      <c r="L82" s="3">
+        <v>9</v>
+      </c>
+      <c r="M82" s="3">
+        <v>5</v>
+      </c>
+      <c r="N82">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="83" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B83" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="83" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B83" s="2" t="s">
+    <row r="84" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B84" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C83" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F83" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G83" s="2"/>
-      <c r="H83" s="2"/>
-      <c r="I83" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J83" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K83" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="84" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B84" t="s">
-        <v>70</v>
-      </c>
-      <c r="C84" t="s">
-        <v>66</v>
-      </c>
-      <c r="D84">
-        <v>8</v>
-      </c>
-      <c r="E84">
-        <v>2</v>
-      </c>
-      <c r="F84">
-        <v>3</v>
-      </c>
-      <c r="I84">
-        <v>8</v>
-      </c>
-      <c r="J84">
-        <v>6</v>
+      <c r="C84" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G84" s="2"/>
+      <c r="H84" s="2"/>
+      <c r="I84" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K84" s="2" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="85" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B85" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C85" t="s">
         <v>66</v>
       </c>
       <c r="D85">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E85">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F85">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I85">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J85">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B86" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C86" t="s">
         <v>66</v>
       </c>
       <c r="D86">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="E86">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F86">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I86">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="J86">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B87" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C87" t="s">
         <v>66</v>
       </c>
       <c r="D87">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="E87">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F87">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I87">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="J87">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="88" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B88" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="C88" t="s">
         <v>66</v>
       </c>
       <c r="D88">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E88">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F88">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I88">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J88">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B89" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C89" t="s">
         <v>66</v>
       </c>
       <c r="D89">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E89">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F89">
         <v>3</v>
       </c>
       <c r="I89">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J89">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B90" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="C90" t="s">
         <v>66</v>
       </c>
       <c r="D90">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="E90">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="F90">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I90">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="J90">
-        <v>29</v>
+        <v>3</v>
       </c>
     </row>
     <row r="91" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B91" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C91" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="D91">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="E91">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="F91">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I91">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="J91">
-        <v>4</v>
+        <v>29</v>
       </c>
     </row>
     <row r="92" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B92" t="s">
+        <v>83</v>
+      </c>
+      <c r="C92" t="s">
+        <v>84</v>
+      </c>
+      <c r="D92">
+        <v>6</v>
+      </c>
+      <c r="E92">
+        <v>3</v>
+      </c>
+      <c r="F92">
+        <v>3</v>
+      </c>
+      <c r="I92">
+        <v>6</v>
+      </c>
+      <c r="J92">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B93" t="s">
         <v>107</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C93" t="s">
         <v>66</v>
       </c>
-      <c r="D92">
-        <v>3</v>
-      </c>
-      <c r="E92">
-        <v>3</v>
-      </c>
-      <c r="F92">
-        <v>3</v>
-      </c>
-      <c r="I92">
-        <v>5</v>
-      </c>
-      <c r="J92">
+      <c r="D93">
+        <v>3</v>
+      </c>
+      <c r="E93">
+        <v>3</v>
+      </c>
+      <c r="F93">
+        <v>3</v>
+      </c>
+      <c r="I93">
+        <v>5</v>
+      </c>
+      <c r="J93">
         <v>2</v>
       </c>
     </row>

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhmgo\Desktop\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87E59B4A-A960-4234-B829-9979CFFEF1D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12623EC4-321E-4B03-BC06-4A5B470C2193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{B57D1550-4E85-435D-BD6F-1B13E635EA51}"/>
+    <workbookView xWindow="4670" yWindow="5330" windowWidth="20900" windowHeight="13040" xr2:uid="{B57D1550-4E85-435D-BD6F-1B13E635EA51}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="111">
   <si>
     <t>野手・打者</t>
   </si>
@@ -446,10 +446,6 @@
   </si>
   <si>
     <t>ケリー</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ｓ</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2522,7 +2518,7 @@
         <v>3</v>
       </c>
       <c r="I54" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J54" s="3">
         <v>14</v>
@@ -2538,7 +2534,7 @@
       </c>
       <c r="N54">
         <f t="shared" si="1"/>
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="55" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -3146,10 +3142,10 @@
         <v>3</v>
       </c>
       <c r="G69" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H69" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I69" s="3">
         <v>8</v>
@@ -3194,7 +3190,7 @@
         <v>9</v>
       </c>
       <c r="I70" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J70" s="3">
         <v>15</v>
@@ -3210,7 +3206,7 @@
       </c>
       <c r="N70">
         <f t="shared" si="1"/>
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="71" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -3236,7 +3232,7 @@
         <v>6</v>
       </c>
       <c r="I71" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J71" s="3">
         <v>13</v>
@@ -3252,7 +3248,7 @@
       </c>
       <c r="N71">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="72" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -3746,9 +3742,7 @@
       <c r="J84" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K84" s="2" t="s">
-        <v>111</v>
-      </c>
+      <c r="K84" s="2"/>
     </row>
     <row r="85" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B85" t="s">

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhmgo\Desktop\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12623EC4-321E-4B03-BC06-4A5B470C2193}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DF0F9A6-2D4B-47FB-95E6-0C740B96E23D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4670" yWindow="5330" windowWidth="20900" windowHeight="13040" xr2:uid="{B57D1550-4E85-435D-BD6F-1B13E635EA51}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="112">
   <si>
     <t>野手・打者</t>
   </si>
@@ -446,6 +446,10 @@
   </si>
   <si>
     <t>ケリー</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ザイア・ホープ</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -828,7 +832,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C402B4-0E60-4338-B3CD-2DB7A1A076E1}">
-  <dimension ref="B2:N93"/>
+  <dimension ref="B2:N94"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="14.75" customWidth="1"/>
@@ -2055,542 +2059,533 @@
         <v>4</v>
       </c>
       <c r="K40">
-        <f>SUM(D40:J40)</f>
+        <f t="shared" ref="K40:K41" si="1">SUM(D40:J40)</f>
         <v>26</v>
       </c>
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B41" s="3"/>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
-      <c r="J41" s="3"/>
+      <c r="B41" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D41" s="3">
+        <v>4</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3</v>
+      </c>
+      <c r="F41" s="3">
+        <v>7</v>
+      </c>
+      <c r="G41" s="3">
+        <v>3</v>
+      </c>
+      <c r="H41" s="3">
+        <v>6</v>
+      </c>
+      <c r="I41" s="3">
+        <v>6</v>
+      </c>
+      <c r="J41" s="3">
+        <v>4</v>
+      </c>
+      <c r="K41">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B43" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J42" s="3"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B44" s="2" t="s">
+      <c r="J43" s="3"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B45" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="C45" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="D45" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E44" s="2" t="s">
+      <c r="E45" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F44" s="2" t="s">
+      <c r="F45" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G44" s="2" t="s">
+      <c r="G45" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H44" s="2" t="s">
+      <c r="H45" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I44" s="2" t="s">
+      <c r="I45" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="J44" s="2" t="s">
+      <c r="J45" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="K44" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="L44" s="2" t="s">
+      <c r="K45" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L45" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M44" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N44" s="2" t="s">
+      <c r="M45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="2" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B45" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D45" s="3">
-        <v>165</v>
-      </c>
-      <c r="E45" s="3">
-        <v>9</v>
-      </c>
-      <c r="F45" s="3">
-        <v>5</v>
-      </c>
-      <c r="G45" s="3">
-        <v>8</v>
-      </c>
-      <c r="H45" s="3">
-        <v>8</v>
-      </c>
-      <c r="I45" s="3">
-        <v>6</v>
-      </c>
-      <c r="J45" s="3">
-        <v>8</v>
-      </c>
-      <c r="K45" s="3">
-        <v>7</v>
-      </c>
-      <c r="L45" s="3">
-        <v>6</v>
-      </c>
-      <c r="M45" s="3">
-        <v>9</v>
-      </c>
-      <c r="N45">
-        <f>SUM(E45:L45)</f>
-        <v>57</v>
       </c>
     </row>
     <row r="46" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B46" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D46" s="3">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="E46" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F46" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G46" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H46" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I46" s="3">
+        <v>6</v>
+      </c>
+      <c r="J46" s="3">
+        <v>8</v>
+      </c>
+      <c r="K46" s="3">
+        <v>7</v>
+      </c>
+      <c r="L46" s="3">
+        <v>6</v>
+      </c>
+      <c r="M46" s="3">
         <v>9</v>
       </c>
-      <c r="J46" s="3">
-        <v>7</v>
-      </c>
-      <c r="K46" s="3">
-        <v>6</v>
-      </c>
-      <c r="L46" s="3">
-        <v>7</v>
-      </c>
-      <c r="M46" s="3">
-        <v>8</v>
-      </c>
       <c r="N46">
-        <f t="shared" ref="N46:N82" si="1">SUM(E46:L46)</f>
-        <v>54</v>
+        <f>SUM(E46:L46)</f>
+        <v>57</v>
       </c>
     </row>
     <row r="47" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B47" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D47" s="3">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E47" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F47" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G47" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H47" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I47" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J47" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K47" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L47" s="3">
         <v>7</v>
       </c>
       <c r="M47" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N47">
-        <f t="shared" si="1"/>
-        <v>47</v>
+        <f t="shared" ref="N47:N83" si="2">SUM(E47:L47)</f>
+        <v>54</v>
       </c>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B48" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D48" s="3">
+        <v>155</v>
+      </c>
+      <c r="E48" s="3">
+        <v>5</v>
+      </c>
+      <c r="F48" s="3">
+        <v>2</v>
+      </c>
+      <c r="G48" s="3">
         <v>10</v>
       </c>
-      <c r="D48" s="3">
-        <v>148</v>
-      </c>
-      <c r="E48" s="3">
-        <v>4</v>
-      </c>
-      <c r="F48" s="3">
-        <v>10</v>
-      </c>
-      <c r="G48" s="3">
-        <v>6</v>
-      </c>
       <c r="H48" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I48" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J48" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K48" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L48" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M48" s="3">
         <v>6</v>
       </c>
       <c r="N48">
-        <f t="shared" si="1"/>
-        <v>46</v>
+        <f t="shared" si="2"/>
+        <v>47</v>
       </c>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B49" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D49" s="3">
-        <v>220</v>
+        <v>148</v>
       </c>
       <c r="E49" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F49" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G49" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H49" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I49" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J49" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K49" s="3">
         <v>4</v>
       </c>
       <c r="L49" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M49" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N49">
-        <f t="shared" si="1"/>
-        <v>31</v>
+        <f t="shared" si="2"/>
+        <v>46</v>
       </c>
     </row>
     <row r="50" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B50" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D50" s="3">
-        <v>100</v>
+        <v>220</v>
       </c>
       <c r="E50" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F50" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G50" s="3">
         <v>9</v>
       </c>
       <c r="H50" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I50" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J50" s="3">
         <v>6</v>
       </c>
       <c r="K50" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L50" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M50" s="3">
         <v>5</v>
       </c>
       <c r="N50">
-        <f t="shared" si="1"/>
-        <v>63</v>
+        <f t="shared" si="2"/>
+        <v>31</v>
       </c>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B51" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D51" s="3">
-        <v>149</v>
+        <v>100</v>
       </c>
       <c r="E51" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F51" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G51" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H51" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I51" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J51" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K51" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L51" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M51" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N51">
-        <f t="shared" si="1"/>
-        <v>48</v>
+        <f t="shared" si="2"/>
+        <v>63</v>
       </c>
     </row>
     <row r="52" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B52" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D52" s="3">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="E52" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F52" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G52" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H52" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I52" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J52" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K52" s="3">
         <v>5</v>
       </c>
       <c r="L52" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M52" s="3">
         <v>6</v>
       </c>
       <c r="N52">
-        <f t="shared" si="1"/>
-        <v>49</v>
+        <f t="shared" si="2"/>
+        <v>48</v>
       </c>
     </row>
     <row r="53" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B53" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D53" s="3">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="E53" s="3">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F53" s="3">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="G53" s="3">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="H53" s="3">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="I53" s="3">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="J53" s="3">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="K53" s="3">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="L53" s="3">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="M53" s="3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="N53">
-        <f t="shared" si="1"/>
-        <v>161</v>
+        <f t="shared" si="2"/>
+        <v>49</v>
       </c>
     </row>
     <row r="54" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B54" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D54" s="3">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E54" s="3">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F54" s="3">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G54" s="3">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="H54" s="3">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="I54" s="3">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="J54" s="3">
+        <v>32</v>
+      </c>
+      <c r="K54" s="3">
         <v>14</v>
       </c>
-      <c r="K54" s="3">
-        <v>6</v>
-      </c>
       <c r="L54" s="3">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="M54" s="3">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="N54">
-        <f t="shared" si="1"/>
-        <v>56</v>
+        <f t="shared" si="2"/>
+        <v>161</v>
       </c>
     </row>
     <row r="55" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B55" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D55" s="3">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="E55" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F55" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G55" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H55" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I55" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J55" s="3">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K55" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L55" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M55" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N55">
-        <f t="shared" si="1"/>
-        <v>49</v>
+        <f t="shared" si="2"/>
+        <v>56</v>
       </c>
     </row>
     <row r="56" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B56" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="D56" s="3">
-        <v>169</v>
+        <v>143</v>
       </c>
       <c r="E56" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F56" s="3">
         <v>4</v>
@@ -2599,226 +2594,226 @@
         <v>5</v>
       </c>
       <c r="H56" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I56" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J56" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K56" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L56" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M56" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N56">
-        <f t="shared" si="1"/>
-        <v>50</v>
+        <f t="shared" si="2"/>
+        <v>49</v>
       </c>
     </row>
     <row r="57" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B57" s="3" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D57" s="3">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="E57" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F57" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G57" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H57" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I57" s="3">
         <v>5</v>
       </c>
       <c r="J57" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K57" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L57" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M57" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N57">
-        <f t="shared" si="1"/>
-        <v>31</v>
+        <f t="shared" si="2"/>
+        <v>50</v>
       </c>
     </row>
     <row r="58" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B58" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D58" s="3">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E58" s="3">
         <v>2</v>
       </c>
       <c r="F58" s="3">
+        <v>10</v>
+      </c>
+      <c r="G58" s="3">
+        <v>2</v>
+      </c>
+      <c r="H58" s="3">
+        <v>2</v>
+      </c>
+      <c r="I58" s="3">
+        <v>5</v>
+      </c>
+      <c r="J58" s="3">
+        <v>2</v>
+      </c>
+      <c r="K58" s="3">
+        <v>5</v>
+      </c>
+      <c r="L58" s="3">
+        <v>3</v>
+      </c>
+      <c r="M58" s="3">
         <v>1</v>
       </c>
-      <c r="G58" s="3">
-        <v>9</v>
-      </c>
-      <c r="H58" s="3">
-        <v>7</v>
-      </c>
-      <c r="I58" s="3">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3">
-        <v>9</v>
-      </c>
-      <c r="K58" s="3">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3">
-        <v>3</v>
-      </c>
-      <c r="M58" s="3">
-        <v>3</v>
-      </c>
       <c r="N58">
-        <f t="shared" si="1"/>
-        <v>37</v>
+        <f t="shared" si="2"/>
+        <v>31</v>
       </c>
     </row>
     <row r="59" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B59" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D59" s="3">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="E59" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F59" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G59" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H59" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I59" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J59" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K59" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L59" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M59" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N59">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>37</v>
       </c>
     </row>
     <row r="60" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B60" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D60" s="3">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="E60" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F60" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G60" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H60" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I60" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J60" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K60" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L60" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M60" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N60">
-        <f t="shared" si="1"/>
-        <v>35</v>
+        <f t="shared" si="2"/>
+        <v>37</v>
       </c>
     </row>
     <row r="61" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B61" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D61" s="3">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="E61" s="3">
         <v>2</v>
       </c>
       <c r="F61" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G61" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H61" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I61" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J61" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K61" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L61" s="3">
         <v>3</v>
@@ -2827,313 +2822,313 @@
         <v>3</v>
       </c>
       <c r="N61">
-        <f t="shared" si="1"/>
-        <v>20</v>
+        <f t="shared" si="2"/>
+        <v>35</v>
       </c>
     </row>
     <row r="62" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B62" s="3" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D62" s="3">
-        <v>159</v>
+        <v>125</v>
       </c>
       <c r="E62" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F62" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G62" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H62" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J62" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K62" s="3">
         <v>3</v>
       </c>
       <c r="L62" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M62" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N62">
-        <f t="shared" si="1"/>
-        <v>38</v>
+        <f t="shared" si="2"/>
+        <v>20</v>
       </c>
     </row>
     <row r="63" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B63" s="3" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D63" s="3">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="E63" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F63" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G63" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H63" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I63" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J63" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K63" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L63" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M63" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N63">
-        <f t="shared" si="1"/>
-        <v>54</v>
+        <f t="shared" si="2"/>
+        <v>38</v>
       </c>
     </row>
     <row r="64" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B64" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>52</v>
       </c>
       <c r="D64" s="3">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="E64" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F64" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G64" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H64" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I64" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J64" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K64" s="3">
         <v>5</v>
       </c>
       <c r="L64" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M64" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N64">
-        <f t="shared" si="1"/>
-        <v>30</v>
+        <f t="shared" si="2"/>
+        <v>54</v>
       </c>
     </row>
     <row r="65" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B65" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D65" s="3">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E65" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F65" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G65" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H65" s="3">
         <v>3</v>
       </c>
       <c r="I65" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J65" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K65" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L65" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M65" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N65">
-        <f t="shared" si="1"/>
-        <v>46</v>
+        <f t="shared" si="2"/>
+        <v>30</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B66" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D66" s="3">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="E66" s="3">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F66" s="3">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="G66" s="3">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="H66" s="3">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I66" s="3">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="J66" s="3">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="K66" s="3">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L66" s="3">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="M66" s="3">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="N66">
-        <f t="shared" si="1"/>
-        <v>169</v>
+        <f t="shared" si="2"/>
+        <v>46</v>
       </c>
     </row>
     <row r="67" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B67" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D67" s="3">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="E67" s="3">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F67" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G67" s="3">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H67" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I67" s="3">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J67" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K67" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L67" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M67" s="3">
         <v>32</v>
       </c>
       <c r="N67">
-        <f t="shared" si="1"/>
-        <v>178</v>
+        <f t="shared" si="2"/>
+        <v>169</v>
       </c>
     </row>
     <row r="68" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B68" s="3" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D68" s="3">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E68" s="3">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="F68" s="3">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="G68" s="3">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="H68" s="3">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="I68" s="3">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="J68" s="3">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="K68" s="3">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="L68" s="3">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="M68" s="3">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="N68">
-        <f t="shared" si="1"/>
-        <v>34</v>
+        <f t="shared" si="2"/>
+        <v>178</v>
       </c>
     </row>
     <row r="69" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B69" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D69" s="3">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="E69" s="3">
         <v>7</v>
@@ -3142,103 +3137,103 @@
         <v>3</v>
       </c>
       <c r="G69" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H69" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I69" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J69" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K69" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L69" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M69" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N69">
-        <f t="shared" si="1"/>
-        <v>55</v>
+        <f t="shared" si="2"/>
+        <v>34</v>
       </c>
     </row>
     <row r="70" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B70" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D70" s="3">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="E70" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F70" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G70" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H70" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I70" s="3">
         <v>8</v>
       </c>
       <c r="J70" s="3">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="K70" s="3">
         <v>6</v>
       </c>
       <c r="L70" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M70" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N70">
-        <f t="shared" si="1"/>
-        <v>54</v>
+        <f t="shared" si="2"/>
+        <v>55</v>
       </c>
     </row>
     <row r="71" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B71" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D71" s="3">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E71" s="3">
+        <v>8</v>
+      </c>
+      <c r="F71" s="3">
+        <v>1</v>
+      </c>
+      <c r="G71" s="3">
+        <v>4</v>
+      </c>
+      <c r="H71" s="3">
         <v>9</v>
       </c>
-      <c r="F71" s="3">
-        <v>7</v>
-      </c>
-      <c r="G71" s="3">
-        <v>3</v>
-      </c>
-      <c r="H71" s="3">
-        <v>6</v>
-      </c>
       <c r="I71" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J71" s="3">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K71" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L71" s="3">
         <v>3</v>
@@ -3247,82 +3242,82 @@
         <v>4</v>
       </c>
       <c r="N71">
-        <f t="shared" si="1"/>
-        <v>55</v>
+        <f t="shared" si="2"/>
+        <v>54</v>
       </c>
     </row>
     <row r="72" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B72" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D72" s="3">
-        <v>77</v>
+        <v>161</v>
       </c>
       <c r="E72" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F72" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G72" s="3">
         <v>3</v>
       </c>
       <c r="H72" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I72" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J72" s="3">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="K72" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L72" s="3">
         <v>3</v>
       </c>
       <c r="M72" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N72">
-        <f t="shared" si="1"/>
-        <v>22</v>
+        <f t="shared" si="2"/>
+        <v>55</v>
       </c>
     </row>
     <row r="73" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B73" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D73" s="3">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="E73" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F73" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G73" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H73" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I73" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J73" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K73" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L73" s="3">
         <v>3</v>
@@ -3331,40 +3326,40 @@
         <v>1</v>
       </c>
       <c r="N73">
-        <f t="shared" si="1"/>
-        <v>25</v>
+        <f t="shared" si="2"/>
+        <v>22</v>
       </c>
     </row>
     <row r="74" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B74" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D74" s="3">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="E74" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F74" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G74" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H74" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I74" s="3">
         <v>3</v>
       </c>
       <c r="J74" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K74" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L74" s="3">
         <v>3</v>
@@ -3373,28 +3368,28 @@
         <v>1</v>
       </c>
       <c r="N74">
-        <f t="shared" si="1"/>
-        <v>26</v>
+        <f t="shared" si="2"/>
+        <v>25</v>
       </c>
     </row>
     <row r="75" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B75" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D75" s="3">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="E75" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F75" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G75" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H75" s="3">
         <v>4</v>
@@ -3403,220 +3398,220 @@
         <v>3</v>
       </c>
       <c r="J75" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K75" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L75" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M75" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N75">
-        <f t="shared" si="1"/>
-        <v>46</v>
+        <f t="shared" si="2"/>
+        <v>26</v>
       </c>
     </row>
     <row r="76" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B76" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D76" s="3">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E76" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F76" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G76" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H76" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I76" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J76" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K76" s="3">
         <v>7</v>
       </c>
       <c r="L76" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M76" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N76">
-        <f t="shared" si="1"/>
-        <v>41</v>
+        <f t="shared" si="2"/>
+        <v>46</v>
       </c>
     </row>
     <row r="77" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B77" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D77" s="3">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="E77" s="3">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F77" s="3">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G77" s="3">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="H77" s="3">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="I77" s="3">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="J77" s="3">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="K77" s="3">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="L77" s="3">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="M77" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="N77">
-        <f t="shared" si="1"/>
-        <v>167</v>
+        <f t="shared" si="2"/>
+        <v>41</v>
       </c>
     </row>
     <row r="78" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B78" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D78" s="3">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E78" s="3">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F78" s="3">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="G78" s="3">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="H78" s="3">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I78" s="3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J78" s="3">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K78" s="3">
         <v>13</v>
       </c>
       <c r="L78" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M78" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="N78">
-        <f t="shared" si="1"/>
-        <v>165</v>
+        <f t="shared" si="2"/>
+        <v>167</v>
       </c>
     </row>
     <row r="79" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B79" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D79" s="3">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="E79" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F79" s="3">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="G79" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H79" s="3">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I79" s="3">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="J79" s="3">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="K79" s="3">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="L79" s="3">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M79" s="3">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="N79">
-        <f t="shared" si="1"/>
-        <v>53</v>
+        <f t="shared" si="2"/>
+        <v>165</v>
       </c>
     </row>
     <row r="80" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B80" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D80" s="3">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E80" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F80" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G80" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H80" s="3">
         <v>6</v>
       </c>
       <c r="I80" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J80" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K80" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L80" s="3">
         <v>7</v>
@@ -3625,329 +3620,371 @@
         <v>7</v>
       </c>
       <c r="N80">
-        <f t="shared" si="1"/>
-        <v>52</v>
+        <f t="shared" si="2"/>
+        <v>53</v>
       </c>
     </row>
     <row r="81" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B81" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>52</v>
       </c>
       <c r="D81" s="3">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="E81" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F81" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G81" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H81" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I81" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J81" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K81" s="3">
         <v>4</v>
       </c>
       <c r="L81" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M81" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N81">
-        <f t="shared" si="1"/>
-        <v>51</v>
+        <f t="shared" si="2"/>
+        <v>52</v>
       </c>
     </row>
     <row r="82" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B82" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D82" s="3">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E82" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F82" s="3">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G82" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H82" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I82" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J82" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K82" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L82" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="M82" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="N82">
-        <f t="shared" si="1"/>
-        <v>41</v>
+        <f t="shared" si="2"/>
+        <v>51</v>
       </c>
     </row>
     <row r="83" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B83" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D83" s="3">
+        <v>148</v>
+      </c>
+      <c r="E83" s="3">
+        <v>5</v>
+      </c>
+      <c r="F83" s="3">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3">
+        <v>5</v>
+      </c>
+      <c r="H83" s="3">
+        <v>4</v>
+      </c>
+      <c r="I83" s="3">
+        <v>6</v>
+      </c>
+      <c r="J83" s="3">
+        <v>4</v>
+      </c>
+      <c r="K83" s="3">
+        <v>5</v>
+      </c>
+      <c r="L83" s="3">
+        <v>9</v>
+      </c>
+      <c r="M83" s="3">
+        <v>5</v>
+      </c>
+      <c r="N83">
+        <f t="shared" si="2"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="84" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B84" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="84" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B84" s="2" t="s">
+    <row r="85" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B85" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C84" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E84" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F84" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G84" s="2"/>
-      <c r="H84" s="2"/>
-      <c r="I84" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J84" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K84" s="2"/>
-    </row>
-    <row r="85" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B85" t="s">
-        <v>70</v>
-      </c>
-      <c r="C85" t="s">
-        <v>66</v>
-      </c>
-      <c r="D85">
-        <v>8</v>
-      </c>
-      <c r="E85">
-        <v>2</v>
-      </c>
-      <c r="F85">
-        <v>3</v>
-      </c>
-      <c r="I85">
-        <v>8</v>
-      </c>
-      <c r="J85">
-        <v>6</v>
-      </c>
+      <c r="C85" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G85" s="2"/>
+      <c r="H85" s="2"/>
+      <c r="I85" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J85" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K85" s="2"/>
     </row>
     <row r="86" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B86" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C86" t="s">
         <v>66</v>
       </c>
       <c r="D86">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E86">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F86">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I86">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J86">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="87" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B87" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C87" t="s">
         <v>66</v>
       </c>
       <c r="D87">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="E87">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F87">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I87">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="J87">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B88" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C88" t="s">
         <v>66</v>
       </c>
       <c r="D88">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="E88">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F88">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I88">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="J88">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="89" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B89" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="C89" t="s">
         <v>66</v>
       </c>
       <c r="D89">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E89">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F89">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I89">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J89">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="90" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B90" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C90" t="s">
         <v>66</v>
       </c>
       <c r="D90">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E90">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F90">
         <v>3</v>
       </c>
       <c r="I90">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J90">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B91" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="C91" t="s">
         <v>66</v>
       </c>
       <c r="D91">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="E91">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="F91">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I91">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="J91">
-        <v>29</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B92" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C92" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="D92">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="E92">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="F92">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I92">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="J92">
-        <v>4</v>
+        <v>29</v>
       </c>
     </row>
     <row r="93" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B93" t="s">
+        <v>83</v>
+      </c>
+      <c r="C93" t="s">
+        <v>84</v>
+      </c>
+      <c r="D93">
+        <v>6</v>
+      </c>
+      <c r="E93">
+        <v>3</v>
+      </c>
+      <c r="F93">
+        <v>3</v>
+      </c>
+      <c r="I93">
+        <v>6</v>
+      </c>
+      <c r="J93">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B94" t="s">
         <v>107</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C94" t="s">
         <v>66</v>
       </c>
-      <c r="D93">
-        <v>3</v>
-      </c>
-      <c r="E93">
-        <v>3</v>
-      </c>
-      <c r="F93">
-        <v>3</v>
-      </c>
-      <c r="I93">
-        <v>5</v>
-      </c>
-      <c r="J93">
+      <c r="D94">
+        <v>3</v>
+      </c>
+      <c r="E94">
+        <v>3</v>
+      </c>
+      <c r="F94">
+        <v>3</v>
+      </c>
+      <c r="I94">
+        <v>5</v>
+      </c>
+      <c r="J94">
         <v>2</v>
       </c>
     </row>

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhmgo\Desktop\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DF0F9A6-2D4B-47FB-95E6-0C740B96E23D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5060FA89-9968-424A-8881-281CE5651277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4670" yWindow="5330" windowWidth="20900" windowHeight="13040" xr2:uid="{B57D1550-4E85-435D-BD6F-1B13E635EA51}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="117">
   <si>
     <t>野手・打者</t>
   </si>
@@ -450,6 +450,26 @@
   </si>
   <si>
     <t>ザイア・ホープ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アルバレス</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>リバーライアン</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>カミネロ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>PCA</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>B.スミス</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -832,7 +852,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C402B4-0E60-4338-B3CD-2DB7A1A076E1}">
-  <dimension ref="B2:N94"/>
+  <dimension ref="B2:N98"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="14.75" customWidth="1"/>
@@ -937,7 +957,7 @@
         <v>28</v>
       </c>
       <c r="K6">
-        <f t="shared" ref="K6:K38" si="0">SUM(D6:I6)</f>
+        <f t="shared" ref="K6:K44" si="0">SUM(D6:I6)</f>
         <v>62</v>
       </c>
     </row>
@@ -1489,10 +1509,10 @@
         <v>5</v>
       </c>
       <c r="H23" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I23" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J23" s="3">
         <v>8</v>
@@ -1510,10 +1530,10 @@
         <v>52</v>
       </c>
       <c r="D24" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E24" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F24" s="3">
         <v>5</v>
@@ -2026,8 +2046,8 @@
         <v>24</v>
       </c>
       <c r="K39">
-        <f>SUM(D39:J39)</f>
-        <v>87</v>
+        <f t="shared" si="0"/>
+        <v>63</v>
       </c>
     </row>
     <row r="40" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -2059,8 +2079,8 @@
         <v>4</v>
       </c>
       <c r="K40">
-        <f t="shared" ref="K40:K41" si="1">SUM(D40:J40)</f>
-        <v>26</v>
+        <f t="shared" si="0"/>
+        <v>22</v>
       </c>
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.55000000000000004">
@@ -2092,728 +2112,732 @@
         <v>4</v>
       </c>
       <c r="K41">
-        <f t="shared" si="1"/>
-        <v>33</v>
+        <f t="shared" si="0"/>
+        <v>29</v>
       </c>
     </row>
     <row r="42" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
-      <c r="J42" s="3"/>
+      <c r="B42" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D42" s="3">
+        <v>8</v>
+      </c>
+      <c r="E42" s="3">
+        <v>9</v>
+      </c>
+      <c r="F42" s="3">
+        <v>3</v>
+      </c>
+      <c r="G42" s="3">
+        <v>1</v>
+      </c>
+      <c r="H42" s="3">
+        <v>1</v>
+      </c>
+      <c r="I42" s="3">
+        <v>2</v>
+      </c>
+      <c r="J42" s="3">
+        <v>6</v>
+      </c>
+      <c r="K42">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
     </row>
     <row r="43" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D43" s="3">
+        <v>8</v>
+      </c>
+      <c r="E43" s="3">
+        <v>6</v>
+      </c>
+      <c r="F43" s="3">
+        <v>4</v>
+      </c>
+      <c r="G43" s="3">
+        <v>4</v>
+      </c>
+      <c r="H43" s="3">
+        <v>2</v>
+      </c>
+      <c r="I43" s="3">
+        <v>6</v>
+      </c>
+      <c r="J43" s="3">
+        <v>7</v>
+      </c>
+      <c r="K43">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B44" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D44" s="3">
+        <v>7</v>
+      </c>
+      <c r="E44" s="3">
+        <v>7</v>
+      </c>
+      <c r="F44" s="3">
+        <v>9</v>
+      </c>
+      <c r="G44" s="3">
+        <v>4</v>
+      </c>
+      <c r="H44" s="3">
+        <v>9</v>
+      </c>
+      <c r="I44" s="3">
+        <v>9</v>
+      </c>
+      <c r="J44" s="3">
+        <v>8</v>
+      </c>
+      <c r="K44">
+        <f t="shared" si="0"/>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B45" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J43" s="3"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B45" s="2" t="s">
+      <c r="J45" s="3"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B47" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="C47" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="D47" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="E47" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F45" s="2" t="s">
+      <c r="F47" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G45" s="2" t="s">
+      <c r="G47" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="H45" s="2" t="s">
+      <c r="H47" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="I45" s="2" t="s">
+      <c r="I47" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="J45" s="2" t="s">
+      <c r="J47" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="K45" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="L45" s="2" t="s">
+      <c r="K47" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="L47" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="M45" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N45" s="2" t="s">
+      <c r="M47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N47" s="2" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B46" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D46" s="3">
-        <v>165</v>
-      </c>
-      <c r="E46" s="3">
-        <v>9</v>
-      </c>
-      <c r="F46" s="3">
-        <v>5</v>
-      </c>
-      <c r="G46" s="3">
-        <v>8</v>
-      </c>
-      <c r="H46" s="3">
-        <v>8</v>
-      </c>
-      <c r="I46" s="3">
-        <v>6</v>
-      </c>
-      <c r="J46" s="3">
-        <v>8</v>
-      </c>
-      <c r="K46" s="3">
-        <v>7</v>
-      </c>
-      <c r="L46" s="3">
-        <v>6</v>
-      </c>
-      <c r="M46" s="3">
-        <v>9</v>
-      </c>
-      <c r="N46">
-        <f>SUM(E46:L46)</f>
-        <v>57</v>
-      </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B47" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D47" s="3">
-        <v>157</v>
-      </c>
-      <c r="E47" s="3">
-        <v>8</v>
-      </c>
-      <c r="F47" s="3">
-        <v>3</v>
-      </c>
-      <c r="G47" s="3">
-        <v>7</v>
-      </c>
-      <c r="H47" s="3">
-        <v>7</v>
-      </c>
-      <c r="I47" s="3">
-        <v>9</v>
-      </c>
-      <c r="J47" s="3">
-        <v>7</v>
-      </c>
-      <c r="K47" s="3">
-        <v>6</v>
-      </c>
-      <c r="L47" s="3">
-        <v>7</v>
-      </c>
-      <c r="M47" s="3">
-        <v>8</v>
-      </c>
-      <c r="N47">
-        <f t="shared" ref="N47:N83" si="2">SUM(E47:L47)</f>
-        <v>54</v>
       </c>
     </row>
     <row r="48" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B48" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D48" s="3">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="E48" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F48" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G48" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H48" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I48" s="3">
         <v>6</v>
       </c>
       <c r="J48" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K48" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L48" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M48" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N48">
-        <f t="shared" si="2"/>
-        <v>47</v>
+        <f>SUM(E48:L48)</f>
+        <v>57</v>
       </c>
     </row>
     <row r="49" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B49" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D49" s="3">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="E49" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F49" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G49" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H49" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I49" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J49" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K49" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L49" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M49" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N49">
-        <f t="shared" si="2"/>
-        <v>46</v>
+        <f t="shared" ref="N49:N87" si="1">SUM(E49:L49)</f>
+        <v>54</v>
       </c>
     </row>
     <row r="50" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B50" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C50" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D50" s="3">
+        <v>155</v>
+      </c>
+      <c r="E50" s="3">
+        <v>5</v>
+      </c>
+      <c r="F50" s="3">
+        <v>2</v>
+      </c>
+      <c r="G50" s="3">
         <v>10</v>
       </c>
-      <c r="D50" s="3">
-        <v>220</v>
-      </c>
-      <c r="E50" s="3">
-        <v>1</v>
-      </c>
-      <c r="F50" s="3">
-        <v>1</v>
-      </c>
-      <c r="G50" s="3">
-        <v>9</v>
-      </c>
       <c r="H50" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I50" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J50" s="3">
         <v>6</v>
       </c>
       <c r="K50" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L50" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M50" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N50">
-        <f t="shared" si="2"/>
-        <v>31</v>
+        <f t="shared" si="1"/>
+        <v>47</v>
       </c>
     </row>
     <row r="51" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B51" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D51" s="3">
-        <v>100</v>
+        <v>148</v>
       </c>
       <c r="E51" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F51" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G51" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H51" s="3">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I51" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J51" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K51" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L51" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M51" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N51">
-        <f t="shared" si="2"/>
-        <v>63</v>
+        <f t="shared" si="1"/>
+        <v>46</v>
       </c>
     </row>
     <row r="52" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B52" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D52" s="3">
-        <v>149</v>
+        <v>220</v>
       </c>
       <c r="E52" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F52" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G52" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H52" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I52" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J52" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K52" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L52" s="3">
         <v>6</v>
       </c>
       <c r="M52" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N52">
-        <f t="shared" si="2"/>
-        <v>48</v>
+        <f t="shared" si="1"/>
+        <v>31</v>
       </c>
     </row>
     <row r="53" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B53" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D53" s="3">
-        <v>158</v>
+        <v>100</v>
       </c>
       <c r="E53" s="3">
         <v>9</v>
       </c>
       <c r="F53" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G53" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H53" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I53" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J53" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K53" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L53" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M53" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N53">
-        <f t="shared" si="2"/>
-        <v>49</v>
+        <f t="shared" si="1"/>
+        <v>63</v>
       </c>
     </row>
     <row r="54" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B54" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D54" s="3">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="E54" s="3">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="F54" s="3">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="G54" s="3">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="H54" s="3">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I54" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="J54" s="3">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="K54" s="3">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="L54" s="3">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="M54" s="3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="N54">
-        <f t="shared" si="2"/>
-        <v>161</v>
+        <f t="shared" si="1"/>
+        <v>48</v>
       </c>
     </row>
     <row r="55" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B55" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D55" s="3">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="E55" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F55" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G55" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H55" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I55" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J55" s="3">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="K55" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L55" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M55" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N55">
-        <f t="shared" si="2"/>
-        <v>56</v>
+        <f t="shared" si="1"/>
+        <v>49</v>
       </c>
     </row>
     <row r="56" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B56" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D56" s="3">
-        <v>143</v>
+        <v>172</v>
       </c>
       <c r="E56" s="3">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F56" s="3">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G56" s="3">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="H56" s="3">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="I56" s="3">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="J56" s="3">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="K56" s="3">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="L56" s="3">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="M56" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="N56">
-        <f t="shared" si="2"/>
-        <v>49</v>
+        <f t="shared" si="1"/>
+        <v>161</v>
       </c>
     </row>
     <row r="57" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B57" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="D57" s="3">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E57" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F57" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G57" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H57" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I57" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J57" s="3">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K57" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L57" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M57" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N57">
-        <f t="shared" si="2"/>
-        <v>50</v>
+        <f t="shared" si="1"/>
+        <v>56</v>
       </c>
     </row>
     <row r="58" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B58" s="3" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="D58" s="3">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="E58" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F58" s="3">
+        <v>4</v>
+      </c>
+      <c r="G58" s="3">
+        <v>5</v>
+      </c>
+      <c r="H58" s="3">
+        <v>5</v>
+      </c>
+      <c r="I58" s="3">
         <v>10</v>
       </c>
-      <c r="G58" s="3">
-        <v>2</v>
-      </c>
-      <c r="H58" s="3">
-        <v>2</v>
-      </c>
-      <c r="I58" s="3">
-        <v>5</v>
-      </c>
       <c r="J58" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="K58" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L58" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M58" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N58">
-        <f t="shared" si="2"/>
-        <v>31</v>
+        <f t="shared" si="1"/>
+        <v>49</v>
       </c>
     </row>
     <row r="59" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B59" s="3" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D59" s="3">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="E59" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F59" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G59" s="3">
+        <v>5</v>
+      </c>
+      <c r="H59" s="3">
         <v>9</v>
       </c>
-      <c r="H59" s="3">
-        <v>7</v>
-      </c>
       <c r="I59" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J59" s="3">
         <v>9</v>
       </c>
       <c r="K59" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L59" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M59" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="N59">
-        <f t="shared" si="2"/>
-        <v>37</v>
+        <f t="shared" si="1"/>
+        <v>50</v>
       </c>
     </row>
     <row r="60" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B60" s="3" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D60" s="3">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="E60" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F60" s="3">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G60" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H60" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I60" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J60" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K60" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L60" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M60" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N60">
-        <f t="shared" si="2"/>
-        <v>37</v>
+        <f t="shared" si="1"/>
+        <v>31</v>
       </c>
     </row>
     <row r="61" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B61" s="3" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D61" s="3">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="E61" s="3">
         <v>2</v>
       </c>
       <c r="F61" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G61" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H61" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I61" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J61" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K61" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L61" s="3">
         <v>3</v>
@@ -2822,67 +2846,67 @@
         <v>3</v>
       </c>
       <c r="N61">
-        <f t="shared" si="2"/>
-        <v>35</v>
+        <f t="shared" si="1"/>
+        <v>37</v>
       </c>
     </row>
     <row r="62" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B62" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D62" s="3">
-        <v>125</v>
+        <v>165</v>
       </c>
       <c r="E62" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F62" s="3">
         <v>2</v>
       </c>
       <c r="G62" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H62" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I62" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J62" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K62" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L62" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M62" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N62">
-        <f t="shared" si="2"/>
-        <v>20</v>
+        <f t="shared" si="1"/>
+        <v>37</v>
       </c>
     </row>
     <row r="63" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B63" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D63" s="3">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="E63" s="3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F63" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G63" s="3">
         <v>5</v>
@@ -2891,196 +2915,196 @@
         <v>5</v>
       </c>
       <c r="I63" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J63" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K63" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L63" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M63" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N63">
-        <f t="shared" si="2"/>
-        <v>38</v>
+        <f t="shared" si="1"/>
+        <v>35</v>
       </c>
     </row>
     <row r="64" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B64" s="3" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D64" s="3">
-        <v>164</v>
+        <v>125</v>
       </c>
       <c r="E64" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F64" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G64" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H64" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I64" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J64" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K64" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L64" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M64" s="3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="N64">
-        <f t="shared" si="2"/>
-        <v>54</v>
+        <f t="shared" si="1"/>
+        <v>20</v>
       </c>
     </row>
     <row r="65" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B65" s="3" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D65" s="3">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E65" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F65" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G65" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H65" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I65" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J65" s="3">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K65" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L65" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M65" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N65">
-        <f t="shared" si="2"/>
-        <v>30</v>
+        <f t="shared" si="1"/>
+        <v>38</v>
       </c>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B66" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D66" s="3">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="E66" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F66" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G66" s="3">
         <v>8</v>
       </c>
       <c r="H66" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I66" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J66" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K66" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L66" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M66" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="N66">
-        <f t="shared" si="2"/>
-        <v>46</v>
+        <f t="shared" si="1"/>
+        <v>54</v>
       </c>
     </row>
     <row r="67" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B67" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D67" s="3">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="E67" s="3">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F67" s="3">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="G67" s="3">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="H67" s="3">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I67" s="3">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="J67" s="3">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="K67" s="3">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="L67" s="3">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="M67" s="3">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="N67">
-        <f t="shared" si="2"/>
-        <v>169</v>
+        <f t="shared" si="1"/>
+        <v>30</v>
       </c>
     </row>
     <row r="68" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B68" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>44</v>
@@ -3089,316 +3113,316 @@
         <v>155</v>
       </c>
       <c r="E68" s="3">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F68" s="3">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="G68" s="3">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="H68" s="3">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="I68" s="3">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="J68" s="3">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="K68" s="3">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L68" s="3">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="M68" s="3">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="N68">
-        <f t="shared" si="2"/>
-        <v>178</v>
+        <f t="shared" si="1"/>
+        <v>46</v>
       </c>
     </row>
     <row r="69" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B69" s="3" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D69" s="3">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="E69" s="3">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F69" s="3">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="G69" s="3">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="H69" s="3">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="I69" s="3">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="J69" s="3">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="K69" s="3">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="L69" s="3">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="M69" s="3">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="N69">
-        <f t="shared" si="2"/>
-        <v>34</v>
+        <f t="shared" si="1"/>
+        <v>169</v>
       </c>
     </row>
     <row r="70" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B70" s="3" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D70" s="3">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="E70" s="3">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="F70" s="3">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="G70" s="3">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="H70" s="3">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I70" s="3">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="J70" s="3">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="K70" s="3">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="L70" s="3">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M70" s="3">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="N70">
-        <f t="shared" si="2"/>
-        <v>55</v>
+        <f t="shared" si="1"/>
+        <v>178</v>
       </c>
     </row>
     <row r="71" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B71" s="3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D71" s="3">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="E71" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F71" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G71" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H71" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I71" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J71" s="3">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="K71" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L71" s="3">
         <v>3</v>
       </c>
       <c r="M71" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N71">
-        <f t="shared" si="2"/>
-        <v>54</v>
+        <f t="shared" si="1"/>
+        <v>34</v>
       </c>
     </row>
     <row r="72" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B72" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D72" s="3">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="E72" s="3">
+        <v>7</v>
+      </c>
+      <c r="F72" s="3">
+        <v>3</v>
+      </c>
+      <c r="G72" s="3">
         <v>9</v>
       </c>
-      <c r="F72" s="3">
-        <v>7</v>
-      </c>
-      <c r="G72" s="3">
-        <v>3</v>
-      </c>
       <c r="H72" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I72" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J72" s="3">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K72" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L72" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M72" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N72">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>55</v>
       </c>
     </row>
     <row r="73" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B73" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D73" s="3">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="E73" s="3">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F73" s="3">
         <v>1</v>
       </c>
       <c r="G73" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H73" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I73" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J73" s="3">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="K73" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L73" s="3">
         <v>3</v>
       </c>
       <c r="M73" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N73">
-        <f t="shared" si="2"/>
-        <v>22</v>
+        <f t="shared" si="1"/>
+        <v>54</v>
       </c>
     </row>
     <row r="74" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B74" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D74" s="3">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="E74" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F74" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G74" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H74" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I74" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="J74" s="3">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="K74" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L74" s="3">
         <v>3</v>
       </c>
       <c r="M74" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N74">
-        <f t="shared" si="2"/>
-        <v>25</v>
+        <f t="shared" si="1"/>
+        <v>55</v>
       </c>
     </row>
     <row r="75" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B75" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D75" s="3">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="E75" s="3">
         <v>3</v>
       </c>
       <c r="F75" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G75" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H75" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I75" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J75" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K75" s="3">
         <v>3</v>
@@ -3410,481 +3434,557 @@
         <v>1</v>
       </c>
       <c r="N75">
-        <f t="shared" si="2"/>
-        <v>26</v>
+        <f t="shared" si="1"/>
+        <v>22</v>
       </c>
     </row>
     <row r="76" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B76" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D76" s="3">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="E76" s="3">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F76" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G76" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H76" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I76" s="3">
         <v>3</v>
       </c>
       <c r="J76" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K76" s="3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L76" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M76" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N76">
-        <f t="shared" si="2"/>
-        <v>46</v>
+        <f t="shared" si="1"/>
+        <v>25</v>
       </c>
     </row>
     <row r="77" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B77" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D77" s="3">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E77" s="3">
         <v>3</v>
       </c>
       <c r="F77" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G77" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H77" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I77" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J77" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K77" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L77" s="3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="M77" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N77">
-        <f t="shared" si="2"/>
-        <v>41</v>
+        <f t="shared" si="1"/>
+        <v>26</v>
       </c>
     </row>
     <row r="78" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B78" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D78" s="3">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E78" s="3">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F78" s="3">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="G78" s="3">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="H78" s="3">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="I78" s="3">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="J78" s="3">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="K78" s="3">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="L78" s="3">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="M78" s="3">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="N78">
-        <f t="shared" si="2"/>
-        <v>167</v>
+        <f t="shared" si="1"/>
+        <v>46</v>
       </c>
     </row>
     <row r="79" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B79" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>52</v>
       </c>
       <c r="D79" s="3">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="E79" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F79" s="3">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="G79" s="3">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H79" s="3">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I79" s="3">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="J79" s="3">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="K79" s="3">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="L79" s="3">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="M79" s="3">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="N79">
-        <f t="shared" si="2"/>
-        <v>165</v>
+        <f t="shared" si="1"/>
+        <v>41</v>
       </c>
     </row>
     <row r="80" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B80" s="3" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D80" s="3">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E80" s="3">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F80" s="3">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="G80" s="3">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="H80" s="3">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I80" s="3">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="J80" s="3">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="K80" s="3">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="L80" s="3">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="M80" s="3">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="N80">
-        <f t="shared" si="2"/>
-        <v>53</v>
+        <f t="shared" si="1"/>
+        <v>167</v>
       </c>
     </row>
     <row r="81" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B81" s="3" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>52</v>
       </c>
       <c r="D81" s="3">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="E81" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F81" s="3">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="G81" s="3">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H81" s="3">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I81" s="3">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="J81" s="3">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="K81" s="3">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="L81" s="3">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="M81" s="3">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="N81">
-        <f t="shared" si="2"/>
-        <v>52</v>
+        <f t="shared" si="1"/>
+        <v>165</v>
       </c>
     </row>
     <row r="82" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B82" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D82" s="3">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="E82" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F82" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G82" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H82" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I82" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J82" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K82" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L82" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M82" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="N82">
-        <f t="shared" si="2"/>
-        <v>51</v>
+        <f t="shared" si="1"/>
+        <v>53</v>
       </c>
     </row>
     <row r="83" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B83" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D83" s="3">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="E83" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F83" s="3">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G83" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H83" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I83" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J83" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K83" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L83" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M83" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N83">
-        <f t="shared" si="2"/>
-        <v>41</v>
+        <f t="shared" si="1"/>
+        <v>52</v>
       </c>
     </row>
     <row r="84" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B84" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D84" s="3">
+        <v>151</v>
+      </c>
+      <c r="E84" s="3">
+        <v>4</v>
+      </c>
+      <c r="F84" s="3">
+        <v>10</v>
+      </c>
+      <c r="G84" s="3">
+        <v>10</v>
+      </c>
+      <c r="H84" s="3">
+        <v>10</v>
+      </c>
+      <c r="I84" s="3">
+        <v>2</v>
+      </c>
+      <c r="J84" s="3">
+        <v>10</v>
+      </c>
+      <c r="K84" s="3">
+        <v>4</v>
+      </c>
+      <c r="L84" s="3">
+        <v>1</v>
+      </c>
+      <c r="M84" s="3">
+        <v>2</v>
+      </c>
+      <c r="N84">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="85" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B85" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D85" s="3">
+        <v>148</v>
+      </c>
+      <c r="E85" s="3">
+        <v>5</v>
+      </c>
+      <c r="F85" s="3">
+        <v>3</v>
+      </c>
+      <c r="G85" s="3">
+        <v>5</v>
+      </c>
+      <c r="H85" s="3">
+        <v>4</v>
+      </c>
+      <c r="I85" s="3">
+        <v>6</v>
+      </c>
+      <c r="J85" s="3">
+        <v>4</v>
+      </c>
+      <c r="K85" s="3">
+        <v>5</v>
+      </c>
+      <c r="L85" s="3">
+        <v>9</v>
+      </c>
+      <c r="M85" s="3">
+        <v>4</v>
+      </c>
+      <c r="N85">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="86" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B86" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D86" s="3">
+        <v>162</v>
+      </c>
+      <c r="E86" s="3">
+        <v>4</v>
+      </c>
+      <c r="F86" s="3">
+        <v>3</v>
+      </c>
+      <c r="G86" s="3">
+        <v>6</v>
+      </c>
+      <c r="H86" s="3">
+        <v>6</v>
+      </c>
+      <c r="I86" s="3">
+        <v>3</v>
+      </c>
+      <c r="J86" s="3">
+        <v>8</v>
+      </c>
+      <c r="K86" s="3">
+        <v>4</v>
+      </c>
+      <c r="L86" s="3">
+        <v>5</v>
+      </c>
+      <c r="M86" s="3">
+        <v>4</v>
+      </c>
+      <c r="N86">
+        <f t="shared" si="1"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="87" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B87" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D87" s="3">
+        <v>158</v>
+      </c>
+      <c r="E87" s="3">
+        <v>3</v>
+      </c>
+      <c r="F87" s="3">
+        <v>1</v>
+      </c>
+      <c r="G87" s="3">
+        <v>8</v>
+      </c>
+      <c r="H87" s="3">
+        <v>5</v>
+      </c>
+      <c r="I87" s="3">
+        <v>3</v>
+      </c>
+      <c r="J87" s="3">
+        <v>6</v>
+      </c>
+      <c r="K87" s="3">
+        <v>4</v>
+      </c>
+      <c r="L87" s="3">
+        <v>5</v>
+      </c>
+      <c r="M87" s="3">
+        <v>3</v>
+      </c>
+      <c r="N87">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="88" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B88" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="85" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B85" s="2" t="s">
+    <row r="89" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B89" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C85" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E85" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G85" s="2"/>
-      <c r="H85" s="2"/>
-      <c r="I85" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J85" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K85" s="2"/>
-    </row>
-    <row r="86" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B86" t="s">
-        <v>70</v>
-      </c>
-      <c r="C86" t="s">
-        <v>66</v>
-      </c>
-      <c r="D86">
-        <v>8</v>
-      </c>
-      <c r="E86">
-        <v>2</v>
-      </c>
-      <c r="F86">
-        <v>3</v>
-      </c>
-      <c r="I86">
-        <v>8</v>
-      </c>
-      <c r="J86">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="87" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B87" t="s">
-        <v>67</v>
-      </c>
-      <c r="C87" t="s">
-        <v>66</v>
-      </c>
-      <c r="D87">
-        <v>4</v>
-      </c>
-      <c r="E87">
-        <v>6</v>
-      </c>
-      <c r="F87">
-        <v>4</v>
-      </c>
-      <c r="I87">
-        <v>7</v>
-      </c>
-      <c r="J87">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="88" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B88" t="s">
-        <v>68</v>
-      </c>
-      <c r="C88" t="s">
-        <v>66</v>
-      </c>
-      <c r="D88">
-        <v>24</v>
-      </c>
-      <c r="E88">
-        <v>16</v>
-      </c>
-      <c r="F88">
-        <v>5</v>
-      </c>
-      <c r="I88">
-        <v>21</v>
-      </c>
-      <c r="J88">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="89" spans="2:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="B89" t="s">
-        <v>69</v>
-      </c>
-      <c r="C89" t="s">
-        <v>66</v>
-      </c>
-      <c r="D89">
-        <v>3</v>
-      </c>
-      <c r="E89">
-        <v>4</v>
-      </c>
-      <c r="F89">
-        <v>4</v>
-      </c>
-      <c r="I89">
-        <v>10</v>
-      </c>
-      <c r="J89">
-        <v>4</v>
-      </c>
+      <c r="C89" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G89" s="2"/>
+      <c r="H89" s="2"/>
+      <c r="I89" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J89" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K89" s="2"/>
     </row>
     <row r="90" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B90" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="C90" t="s">
         <v>66</v>
       </c>
       <c r="D90">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E90">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F90">
         <v>3</v>
@@ -3893,73 +3993,73 @@
         <v>8</v>
       </c>
       <c r="J90">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B91" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C91" t="s">
         <v>66</v>
       </c>
       <c r="D91">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E91">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F91">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I91">
         <v>7</v>
       </c>
       <c r="J91">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B92" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C92" t="s">
         <v>66</v>
       </c>
       <c r="D92">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E92">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F92">
         <v>5</v>
       </c>
       <c r="I92">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J92">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="93" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B93" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C93" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="D93">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E93">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F93">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I93">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J93">
         <v>4</v>
@@ -3967,13 +4067,13 @@
     </row>
     <row r="94" spans="2:14" x14ac:dyDescent="0.55000000000000004">
       <c r="B94" t="s">
-        <v>107</v>
+        <v>58</v>
       </c>
       <c r="C94" t="s">
         <v>66</v>
       </c>
       <c r="D94">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E94">
         <v>3</v>
@@ -3982,9 +4082,101 @@
         <v>3</v>
       </c>
       <c r="I94">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J94">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B95" t="s">
+        <v>61</v>
+      </c>
+      <c r="C95" t="s">
+        <v>66</v>
+      </c>
+      <c r="D95">
+        <v>6</v>
+      </c>
+      <c r="E95">
+        <v>1</v>
+      </c>
+      <c r="F95">
+        <v>3</v>
+      </c>
+      <c r="I95">
+        <v>7</v>
+      </c>
+      <c r="J95">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="96" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+      <c r="B96" t="s">
+        <v>77</v>
+      </c>
+      <c r="C96" t="s">
+        <v>66</v>
+      </c>
+      <c r="D96">
+        <v>26</v>
+      </c>
+      <c r="E96">
+        <v>17</v>
+      </c>
+      <c r="F96">
+        <v>5</v>
+      </c>
+      <c r="I96">
+        <v>24</v>
+      </c>
+      <c r="J96">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="97" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B97" t="s">
+        <v>83</v>
+      </c>
+      <c r="C97" t="s">
+        <v>84</v>
+      </c>
+      <c r="D97">
+        <v>6</v>
+      </c>
+      <c r="E97">
+        <v>3</v>
+      </c>
+      <c r="F97">
+        <v>3</v>
+      </c>
+      <c r="I97">
+        <v>6</v>
+      </c>
+      <c r="J97">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+      <c r="B98" t="s">
+        <v>107</v>
+      </c>
+      <c r="C98" t="s">
+        <v>66</v>
+      </c>
+      <c r="D98">
+        <v>3</v>
+      </c>
+      <c r="E98">
+        <v>3</v>
+      </c>
+      <c r="F98">
+        <v>3</v>
+      </c>
+      <c r="I98">
+        <v>5</v>
+      </c>
+      <c r="J98">
         <v>2</v>
       </c>
     </row>

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhmgo\Desktop\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5060FA89-9968-424A-8881-281CE5651277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31D21628-AFDC-408C-B104-237E6077A050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4670" yWindow="5330" windowWidth="20900" windowHeight="13040" xr2:uid="{B57D1550-4E85-435D-BD6F-1B13E635EA51}"/>
+    <workbookView xWindow="2030" yWindow="4000" windowWidth="30970" windowHeight="13040" xr2:uid="{B57D1550-4E85-435D-BD6F-1B13E635EA51}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4027,10 +4027,10 @@
         <v>66</v>
       </c>
       <c r="D92">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="E92">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F92">
         <v>5</v>
@@ -4119,10 +4119,10 @@
         <v>66</v>
       </c>
       <c r="D96">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E96">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F96">
         <v>5</v>

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhmgo\Desktop\base\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomos\Desktop\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31D21628-AFDC-408C-B104-237E6077A050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{426A2983-3C87-4FAC-A98C-83D7280B3317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2030" yWindow="4000" windowWidth="30970" windowHeight="13040" xr2:uid="{B57D1550-4E85-435D-BD6F-1B13E635EA51}"/>
+    <workbookView xWindow="2730" yWindow="255" windowWidth="18105" windowHeight="15225" xr2:uid="{B57D1550-4E85-435D-BD6F-1B13E635EA51}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,15 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -853,17 +862,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C402B4-0E60-4338-B3CD-2DB7A1A076E1}">
   <dimension ref="B2:N98"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="14.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
@@ -895,7 +904,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B5" s="3" t="s">
         <v>9</v>
       </c>
@@ -928,7 +937,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B6" s="3" t="s">
         <v>11</v>
       </c>
@@ -948,7 +957,7 @@
         <v>3</v>
       </c>
       <c r="H6" s="3">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I6" s="3">
         <v>11</v>
@@ -958,10 +967,10 @@
       </c>
       <c r="K6">
         <f t="shared" ref="K6:K44" si="0">SUM(D6:I6)</f>
-        <v>62</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B7" s="3" t="s">
         <v>12</v>
       </c>
@@ -994,7 +1003,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B8" s="3" t="s">
         <v>13</v>
       </c>
@@ -1027,7 +1036,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B9" s="3" t="s">
         <v>14</v>
       </c>
@@ -1060,7 +1069,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B10" s="3" t="s">
         <v>15</v>
       </c>
@@ -1093,7 +1102,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B11" s="3" t="s">
         <v>16</v>
       </c>
@@ -1126,7 +1135,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B12" s="3" t="s">
         <v>18</v>
       </c>
@@ -1159,7 +1168,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B13" s="3" t="s">
         <v>19</v>
       </c>
@@ -1192,7 +1201,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B14" s="3" t="s">
         <v>20</v>
       </c>
@@ -1225,7 +1234,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B15" s="3" t="s">
         <v>21</v>
       </c>
@@ -1258,7 +1267,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B16" s="3" t="s">
         <v>45</v>
       </c>
@@ -1291,7 +1300,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B17" s="3" t="s">
         <v>46</v>
       </c>
@@ -1324,7 +1333,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B18" s="3" t="s">
         <v>47</v>
       </c>
@@ -1357,7 +1366,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B19" s="3" t="s">
         <v>48</v>
       </c>
@@ -1390,7 +1399,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B20" s="3" t="s">
         <v>49</v>
       </c>
@@ -1407,23 +1416,23 @@
         <v>8</v>
       </c>
       <c r="G20" s="3">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H20" s="3">
         <v>2</v>
       </c>
       <c r="I20" s="3">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J20" s="3">
         <v>25</v>
       </c>
       <c r="K20">
         <f t="shared" si="0"/>
-        <v>67</v>
-      </c>
-    </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B21" s="3" t="s">
         <v>55</v>
       </c>
@@ -1456,7 +1465,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B22" s="3" t="s">
         <v>61</v>
       </c>
@@ -1489,7 +1498,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B23" s="3" t="s">
         <v>59</v>
       </c>
@@ -1522,7 +1531,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B24" s="3" t="s">
         <v>62</v>
       </c>
@@ -1555,7 +1564,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B25" s="3" t="s">
         <v>63</v>
       </c>
@@ -1588,7 +1597,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="2:11" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B26" s="3" t="s">
         <v>90</v>
       </c>
@@ -1621,7 +1630,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B27" s="3" t="s">
         <v>78</v>
       </c>
@@ -1641,7 +1650,7 @@
         <v>3</v>
       </c>
       <c r="H27" s="3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I27" s="3">
         <v>10</v>
@@ -1651,10 +1660,10 @@
       </c>
       <c r="K27">
         <f t="shared" si="0"/>
-        <v>67</v>
-      </c>
-    </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B28" s="3" t="s">
         <v>80</v>
       </c>
@@ -1687,7 +1696,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B29" s="3" t="s">
         <v>81</v>
       </c>
@@ -1720,7 +1729,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B30" s="3" t="s">
         <v>82</v>
       </c>
@@ -1753,7 +1762,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B31" s="3" t="s">
         <v>74</v>
       </c>
@@ -1770,23 +1779,23 @@
         <v>5</v>
       </c>
       <c r="G31" s="3">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H31" s="3">
         <v>2</v>
       </c>
       <c r="I31" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J31" s="3">
         <v>25</v>
       </c>
       <c r="K31">
         <f t="shared" si="0"/>
-        <v>62</v>
-      </c>
-    </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.55000000000000004">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B32" s="3" t="s">
         <v>85</v>
       </c>
@@ -1819,7 +1828,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B33" s="3" t="s">
         <v>79</v>
       </c>
@@ -1852,7 +1861,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B34" s="3" t="s">
         <v>86</v>
       </c>
@@ -1885,7 +1894,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B35" s="3" t="s">
         <v>87</v>
       </c>
@@ -1918,7 +1927,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B36" s="3" t="s">
         <v>91</v>
       </c>
@@ -1951,7 +1960,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B37" s="3" t="s">
         <v>92</v>
       </c>
@@ -1984,7 +1993,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B38" s="3" t="s">
         <v>102</v>
       </c>
@@ -2001,23 +2010,23 @@
         <v>6</v>
       </c>
       <c r="G38" s="3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H38" s="3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I38" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J38" s="3">
         <v>26</v>
       </c>
       <c r="K38">
         <f t="shared" si="0"/>
-        <v>63</v>
-      </c>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B39" s="3" t="s">
         <v>104</v>
       </c>
@@ -2037,20 +2046,20 @@
         <v>3</v>
       </c>
       <c r="H39" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I39" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J39" s="3">
         <v>24</v>
       </c>
       <c r="K39">
         <f t="shared" si="0"/>
-        <v>63</v>
-      </c>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B40" s="3" t="s">
         <v>108</v>
       </c>
@@ -2083,7 +2092,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B41" s="3" t="s">
         <v>111</v>
       </c>
@@ -2116,7 +2125,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B42" s="3" t="s">
         <v>112</v>
       </c>
@@ -2149,7 +2158,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B43" s="3" t="s">
         <v>114</v>
       </c>
@@ -2182,7 +2191,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B44" s="3" t="s">
         <v>115</v>
       </c>
@@ -2215,13 +2224,13 @@
         <v>45</v>
       </c>
     </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B45" s="1" t="s">
         <v>22</v>
       </c>
       <c r="J45" s="3"/>
     </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B47" s="2" t="s">
         <v>1</v>
       </c>
@@ -2262,7 +2271,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B48" s="3" t="s">
         <v>32</v>
       </c>
@@ -2304,7 +2313,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="49" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B49" s="3" t="s">
         <v>33</v>
       </c>
@@ -2346,7 +2355,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="50" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B50" s="3" t="s">
         <v>34</v>
       </c>
@@ -2388,7 +2397,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="51" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B51" s="3" t="s">
         <v>35</v>
       </c>
@@ -2430,7 +2439,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="52" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B52" s="3" t="s">
         <v>36</v>
       </c>
@@ -2472,7 +2481,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="53" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B53" s="3" t="s">
         <v>37</v>
       </c>
@@ -2514,7 +2523,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="54" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B54" s="3" t="s">
         <v>38</v>
       </c>
@@ -2556,7 +2565,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="55" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B55" s="3" t="s">
         <v>39</v>
       </c>
@@ -2598,7 +2607,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="56" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B56" s="3" t="s">
         <v>40</v>
       </c>
@@ -2627,7 +2636,7 @@
         <v>32</v>
       </c>
       <c r="K56" s="3">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="L56" s="3">
         <v>16</v>
@@ -2637,10 +2646,10 @@
       </c>
       <c r="N56">
         <f t="shared" si="1"/>
-        <v>161</v>
-      </c>
-    </row>
-    <row r="57" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="57" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B57" s="3" t="s">
         <v>41</v>
       </c>
@@ -2682,7 +2691,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B58" s="3" t="s">
         <v>42</v>
       </c>
@@ -2724,7 +2733,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="59" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B59" s="3" t="s">
         <v>43</v>
       </c>
@@ -2766,7 +2775,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="60" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B60" s="3" t="s">
         <v>53</v>
       </c>
@@ -2808,7 +2817,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="61" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B61" s="3" t="s">
         <v>54</v>
       </c>
@@ -2850,7 +2859,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="62" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B62" s="3" t="s">
         <v>57</v>
       </c>
@@ -2892,7 +2901,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="63" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B63" s="3" t="s">
         <v>60</v>
       </c>
@@ -2934,7 +2943,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="64" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B64" s="3" t="s">
         <v>61</v>
       </c>
@@ -2976,7 +2985,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B65" s="3" t="s">
         <v>64</v>
       </c>
@@ -3018,7 +3027,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B66" s="3" t="s">
         <v>71</v>
       </c>
@@ -3060,7 +3069,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B67" s="3" t="s">
         <v>72</v>
       </c>
@@ -3102,7 +3111,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B68" s="3" t="s">
         <v>73</v>
       </c>
@@ -3144,7 +3153,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B69" s="3" t="s">
         <v>75</v>
       </c>
@@ -3173,7 +3182,7 @@
         <v>33</v>
       </c>
       <c r="K69" s="3">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="L69" s="3">
         <v>16</v>
@@ -3183,10 +3192,10 @@
       </c>
       <c r="N69">
         <f t="shared" si="1"/>
-        <v>169</v>
-      </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B70" s="3" t="s">
         <v>76</v>
       </c>
@@ -3215,7 +3224,7 @@
         <v>32</v>
       </c>
       <c r="K70" s="3">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="L70" s="3">
         <v>15</v>
@@ -3225,10 +3234,10 @@
       </c>
       <c r="N70">
         <f t="shared" si="1"/>
-        <v>178</v>
-      </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B71" s="3" t="s">
         <v>88</v>
       </c>
@@ -3270,7 +3279,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B72" s="3" t="s">
         <v>89</v>
       </c>
@@ -3312,7 +3321,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B73" s="3" t="s">
         <v>93</v>
       </c>
@@ -3354,7 +3363,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B74" s="3" t="s">
         <v>94</v>
       </c>
@@ -3396,7 +3405,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B75" s="3" t="s">
         <v>95</v>
       </c>
@@ -3438,7 +3447,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B76" s="3" t="s">
         <v>96</v>
       </c>
@@ -3480,7 +3489,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B77" s="3" t="s">
         <v>97</v>
       </c>
@@ -3522,7 +3531,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="78" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B78" s="3" t="s">
         <v>98</v>
       </c>
@@ -3564,7 +3573,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B79" s="3" t="s">
         <v>99</v>
       </c>
@@ -3606,7 +3615,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B80" s="3" t="s">
         <v>100</v>
       </c>
@@ -3635,7 +3644,7 @@
         <v>31</v>
       </c>
       <c r="K80" s="3">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="L80" s="3">
         <v>16</v>
@@ -3645,10 +3654,10 @@
       </c>
       <c r="N80">
         <f t="shared" si="1"/>
-        <v>167</v>
-      </c>
-    </row>
-    <row r="81" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="81" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B81" s="3" t="s">
         <v>101</v>
       </c>
@@ -3677,7 +3686,7 @@
         <v>33</v>
       </c>
       <c r="K81" s="3">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="L81" s="3">
         <v>15</v>
@@ -3687,10 +3696,10 @@
       </c>
       <c r="N81">
         <f t="shared" si="1"/>
-        <v>165</v>
-      </c>
-    </row>
-    <row r="82" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="82" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B82" s="3" t="s">
         <v>105</v>
       </c>
@@ -3732,7 +3741,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="83" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B83" s="3" t="s">
         <v>106</v>
       </c>
@@ -3774,7 +3783,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="84" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B84" s="3" t="s">
         <v>109</v>
       </c>
@@ -3816,7 +3825,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="85" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B85" s="3" t="s">
         <v>110</v>
       </c>
@@ -3858,7 +3867,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="86" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B86" s="3" t="s">
         <v>113</v>
       </c>
@@ -3900,7 +3909,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="87" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B87" s="3" t="s">
         <v>116</v>
       </c>
@@ -3942,12 +3951,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="88" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B88" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="89" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B89" s="2" t="s">
         <v>1</v>
       </c>
@@ -3973,7 +3982,7 @@
       </c>
       <c r="K89" s="2"/>
     </row>
-    <row r="90" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B90" t="s">
         <v>70</v>
       </c>
@@ -3996,7 +4005,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="91" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B91" t="s">
         <v>67</v>
       </c>
@@ -4019,7 +4028,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B92" t="s">
         <v>68</v>
       </c>
@@ -4036,13 +4045,13 @@
         <v>5</v>
       </c>
       <c r="I92">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J92">
         <v>27</v>
       </c>
     </row>
-    <row r="93" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B93" t="s">
         <v>69</v>
       </c>
@@ -4065,7 +4074,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="94" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B94" t="s">
         <v>58</v>
       </c>
@@ -4088,7 +4097,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B95" t="s">
         <v>61</v>
       </c>
@@ -4111,7 +4120,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="96" spans="2:14" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B96" t="s">
         <v>77</v>
       </c>
@@ -4128,13 +4137,13 @@
         <v>5</v>
       </c>
       <c r="I96">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="J96">
         <v>29</v>
       </c>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B97" t="s">
         <v>83</v>
       </c>
@@ -4157,7 +4166,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B98" t="s">
         <v>107</v>
       </c>

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tomos\Desktop\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{426A2983-3C87-4FAC-A98C-83D7280B3317}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDE571EF-732D-4921-9646-74BA05CA005B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2730" yWindow="255" windowWidth="18105" windowHeight="15225" xr2:uid="{B57D1550-4E85-435D-BD6F-1B13E635EA51}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="119">
   <si>
     <t>野手・打者</t>
   </si>
@@ -479,6 +479,14 @@
   </si>
   <si>
     <t>B.スミス</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>アンダーソン</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>T.スコット</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -861,7 +869,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47C402B4-0E60-4338-B3CD-2DB7A1A076E1}">
-  <dimension ref="B2:N98"/>
+  <dimension ref="B2:N100"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="14.75" customWidth="1"/>
@@ -2351,7 +2359,7 @@
         <v>8</v>
       </c>
       <c r="N49">
-        <f t="shared" ref="N49:N87" si="1">SUM(E49:L49)</f>
+        <f t="shared" ref="N49:N89" si="1">SUM(E49:L49)</f>
         <v>54</v>
       </c>
     </row>
@@ -3080,22 +3088,22 @@
         <v>157</v>
       </c>
       <c r="E67" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F67" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G67" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H67" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I67" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J67" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K67" s="3">
         <v>5</v>
@@ -3108,7 +3116,7 @@
       </c>
       <c r="N67">
         <f t="shared" si="1"/>
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="68" spans="2:14" x14ac:dyDescent="0.4">
@@ -3911,281 +3919,365 @@
     </row>
     <row r="87" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B87" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>44</v>
       </c>
       <c r="D87" s="3">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E87" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F87" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G87" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H87" s="3">
         <v>5</v>
       </c>
       <c r="I87" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J87" s="3">
         <v>6</v>
       </c>
       <c r="K87" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L87" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M87" s="3">
         <v>3</v>
       </c>
       <c r="N87">
         <f t="shared" si="1"/>
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="88" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B88" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D88" s="3">
+        <v>160</v>
+      </c>
+      <c r="E88" s="3">
+        <v>3</v>
+      </c>
+      <c r="F88" s="3">
+        <v>9</v>
+      </c>
+      <c r="G88" s="3">
+        <v>3</v>
+      </c>
+      <c r="H88" s="3">
+        <v>9</v>
+      </c>
+      <c r="I88" s="3">
+        <v>7</v>
+      </c>
+      <c r="J88" s="3">
+        <v>9</v>
+      </c>
+      <c r="K88" s="3">
+        <v>7</v>
+      </c>
+      <c r="L88" s="3">
+        <v>4</v>
+      </c>
+      <c r="M88" s="3">
+        <v>3</v>
+      </c>
+      <c r="N88">
+        <f t="shared" si="1"/>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="89" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B89" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D89" s="3">
+        <v>158</v>
+      </c>
+      <c r="E89" s="3">
+        <v>3</v>
+      </c>
+      <c r="F89" s="3">
+        <v>1</v>
+      </c>
+      <c r="G89" s="3">
+        <v>8</v>
+      </c>
+      <c r="H89" s="3">
+        <v>5</v>
+      </c>
+      <c r="I89" s="3">
+        <v>3</v>
+      </c>
+      <c r="J89" s="3">
+        <v>6</v>
+      </c>
+      <c r="K89" s="3">
+        <v>4</v>
+      </c>
+      <c r="L89" s="3">
+        <v>5</v>
+      </c>
+      <c r="M89" s="3">
+        <v>3</v>
+      </c>
+      <c r="N89">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="90" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B90" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="89" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B89" s="2" t="s">
+    <row r="91" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B91" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C89" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G89" s="2"/>
-      <c r="H89" s="2"/>
-      <c r="I89" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J89" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K89" s="2"/>
-    </row>
-    <row r="90" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B90" t="s">
-        <v>70</v>
-      </c>
-      <c r="C90" t="s">
-        <v>66</v>
-      </c>
-      <c r="D90">
-        <v>8</v>
-      </c>
-      <c r="E90">
-        <v>2</v>
-      </c>
-      <c r="F90">
-        <v>3</v>
-      </c>
-      <c r="I90">
-        <v>8</v>
-      </c>
-      <c r="J90">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="91" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B91" t="s">
-        <v>67</v>
-      </c>
-      <c r="C91" t="s">
-        <v>66</v>
-      </c>
-      <c r="D91">
-        <v>4</v>
-      </c>
-      <c r="E91">
-        <v>6</v>
-      </c>
-      <c r="F91">
-        <v>4</v>
-      </c>
-      <c r="I91">
-        <v>7</v>
-      </c>
-      <c r="J91">
-        <v>5</v>
-      </c>
+      <c r="C91" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G91" s="2"/>
+      <c r="H91" s="2"/>
+      <c r="I91" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J91" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K91" s="2"/>
     </row>
     <row r="92" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B92" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C92" t="s">
         <v>66</v>
       </c>
       <c r="D92">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E92">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F92">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I92">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J92">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B93" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C93" t="s">
         <v>66</v>
       </c>
       <c r="D93">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E93">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F93">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I93">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J93">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B94" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C94" t="s">
         <v>66</v>
       </c>
       <c r="D94">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E94">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F94">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I94">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J94">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="95" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B95" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C95" t="s">
         <v>66</v>
       </c>
       <c r="D95">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E95">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F95">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I95">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J95">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="96" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B96" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="C96" t="s">
         <v>66</v>
       </c>
       <c r="D96">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E96">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F96">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I96">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J96">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="97" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B97" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="C97" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="D97">
         <v>6</v>
       </c>
       <c r="E97">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F97">
         <v>3</v>
       </c>
       <c r="I97">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J97">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B98" t="s">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="C98" t="s">
         <v>66</v>
       </c>
       <c r="D98">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="E98">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="F98">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I98">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="J98">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="99" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B99" t="s">
+        <v>83</v>
+      </c>
+      <c r="C99" t="s">
+        <v>84</v>
+      </c>
+      <c r="D99">
+        <v>6</v>
+      </c>
+      <c r="E99">
+        <v>3</v>
+      </c>
+      <c r="F99">
+        <v>3</v>
+      </c>
+      <c r="I99">
+        <v>6</v>
+      </c>
+      <c r="J99">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B100" t="s">
+        <v>107</v>
+      </c>
+      <c r="C100" t="s">
+        <v>66</v>
+      </c>
+      <c r="D100">
+        <v>3</v>
+      </c>
+      <c r="E100">
+        <v>3</v>
+      </c>
+      <c r="F100">
+        <v>3</v>
+      </c>
+      <c r="I100">
+        <v>5</v>
+      </c>
+      <c r="J100">
         <v>2</v>
       </c>
     </row>
